--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L108"/>
+  <dimension ref="A1:L93"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Tu recuerdo</v>
+        <v>Hit the Wall</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/tu-recuerdo/6763660843</v>
+        <v>https://music.apple.com/us/song/hit-the-wall/6766750846</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-15</v>
@@ -451,36 +451,36 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>Loco X Volver</v>
+        <v>Daughter from Hell</v>
       </c>
       <c r="G2" t="str">
-        <v>3:55</v>
+        <v>3:14</v>
       </c>
       <c r="H2" t="str">
-        <v>Maluma</v>
+        <v>Gracie Abrams</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/gracie-abrams/1450554836</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/tu-recuerdo/1895423065</v>
+        <v>https://music.apple.com/us/album/hit-the-wall/6766750836</v>
       </c>
       <c r="L2" t="str">
-        <v>Tu recuerdo - Maluma</v>
+        <v>Hit the Wall - Gracie Abrams</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Hardy (feat. Clairo)</v>
+        <v>Ran To Atlanta</v>
       </c>
       <c r="B3" t="str">
         <v/>
       </c>
       <c r="C3" t="str">
-        <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
+        <v>https://music.apple.com/us/song/ran-to-atlanta/6769568597</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-15</v>
@@ -489,36 +489,36 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>American Stories</v>
+        <v>ICEMAN</v>
       </c>
       <c r="G3" t="str">
-        <v>3:53</v>
+        <v>4:07</v>
       </c>
       <c r="H3" t="str">
-        <v>Rostam</v>
+        <v>Drake</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K3" t="str">
-        <v>https://music.apple.com/us/album/hardy-feat-clairo/1876952750</v>
+        <v>https://music.apple.com/us/album/ran-to-atlanta/6769568449</v>
       </c>
       <c r="L3" t="str">
-        <v>Hardy (feat. Clairo) - Rostam</v>
+        <v>Ran To Atlanta - Drake</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Una A La Vez</v>
+        <v>Hoe Phase</v>
       </c>
       <c r="B4" t="str">
         <v/>
       </c>
       <c r="C4" t="str">
-        <v>https://music.apple.com/us/song/una-a-la-vez/1890287855</v>
+        <v>https://music.apple.com/us/song/hoe-phase/6769556949</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-15</v>
@@ -527,36 +527,36 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>OMERTA</v>
+        <v>MAID OF HONOUR</v>
       </c>
       <c r="G4" t="str">
-        <v>2:32</v>
+        <v>3:23</v>
       </c>
       <c r="H4" t="str">
-        <v>J Balvin</v>
+        <v>Drake</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K4" t="str">
-        <v>https://music.apple.com/us/album/una-a-la-vez/1890287852</v>
+        <v>https://music.apple.com/us/album/hoe-phase/6769556940</v>
       </c>
       <c r="L4" t="str">
-        <v>Una A La Vez - J Balvin</v>
+        <v>Hoe Phase - Drake</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Rock Music</v>
+        <v>I’m Spent</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>https://music.apple.com/us/song/rock-music/6766314234</v>
+        <v>https://music.apple.com/us/song/im-spent/6769551476</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-15</v>
@@ -565,36 +565,36 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>Rock Music - Single</v>
+        <v>HABIBTI</v>
       </c>
       <c r="G5" t="str">
-        <v>1:55</v>
+        <v>2:24</v>
       </c>
       <c r="H5" t="str">
-        <v>Charli xcx</v>
+        <v>Drake</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
-        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K5" t="str">
-        <v>https://music.apple.com/us/album/rock-music/6766314069</v>
+        <v>https://music.apple.com/us/album/im-spent/6769551464</v>
       </c>
       <c r="L5" t="str">
-        <v>Rock Music - Charli xcx</v>
+        <v>I’m Spent - Drake</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>TNT</v>
+        <v>Abracadabra (Apple Music Live)</v>
       </c>
       <c r="B6" t="str">
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>https://music.apple.com/us/song/tnt/1887671066</v>
+        <v>https://music.apple.com/us/song/abracadabra-apple-music-live/6768201780</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-15</v>
@@ -603,36 +603,36 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>GREENGREEN - EP</v>
+        <v>Apple Music Live: MAYHEM Requiem</v>
       </c>
       <c r="G6" t="str">
-        <v>2:02</v>
+        <v>4:04</v>
       </c>
       <c r="H6" t="str">
-        <v>CORTIS</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
-        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
+        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
       </c>
       <c r="K6" t="str">
-        <v>https://music.apple.com/us/album/tnt/1887671065</v>
+        <v>https://music.apple.com/us/album/abracadabra-apple-music-live/6768201775</v>
       </c>
       <c r="L6" t="str">
-        <v>TNT - CORTIS</v>
+        <v>Abracadabra (Apple Music Live) - Lady Gaga</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Go</v>
+        <v>Falling out of Love</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>https://music.apple.com/us/song/go/6765588421</v>
+        <v>https://music.apple.com/us/song/falling-out-of-love/1891161448</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-15</v>
@@ -641,36 +641,36 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>Go - Single</v>
+        <v>Reality Awaits</v>
       </c>
       <c r="G7" t="str">
-        <v>2:24</v>
+        <v>6:21</v>
       </c>
       <c r="H7" t="str">
-        <v>Key Glock</v>
+        <v>The Strokes</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
-        <v>https://music.apple.com/us/artist/key-glock/1199258326</v>
+        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
       </c>
       <c r="K7" t="str">
-        <v>https://music.apple.com/us/album/go/1896001876</v>
+        <v>https://music.apple.com/us/album/falling-out-of-love/1891161441</v>
       </c>
       <c r="L7" t="str">
-        <v>Go - Key Glock</v>
+        <v>Falling out of Love - The Strokes</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>For The Moment</v>
+        <v>Dai Dai</v>
       </c>
       <c r="B8" t="str">
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>https://music.apple.com/us/song/for-the-moment/6764419271</v>
+        <v>https://music.apple.com/us/song/dai-dai/6768469976</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-15</v>
@@ -679,36 +679,36 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>BROWN</v>
+        <v>Dai Dai - Single</v>
       </c>
       <c r="G8" t="str">
-        <v>3:26</v>
+        <v>3:43</v>
       </c>
       <c r="H8" t="str">
-        <v>Chris Brown</v>
+        <v>Shakira</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
-        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
+        <v>https://music.apple.com/us/artist/shakira/889327</v>
       </c>
       <c r="K8" t="str">
-        <v>https://music.apple.com/us/album/for-the-moment/1895772091</v>
+        <v>https://music.apple.com/us/album/dai-dai/6768469975</v>
       </c>
       <c r="L8" t="str">
-        <v>For The Moment - Chris Brown</v>
+        <v>Dai Dai - Shakira</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Smoking pt. 2</v>
+        <v>Tu recuerdo</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>https://music.apple.com/us/song/smoking-pt-2/1894333434</v>
+        <v>https://music.apple.com/us/song/tu-recuerdo/6763660843</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-15</v>
@@ -717,36 +717,36 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>Wave Gods 2: Cosmos Brothers</v>
+        <v>Loco X Volver</v>
       </c>
       <c r="G9" t="str">
-        <v>3:21</v>
+        <v>3:55</v>
       </c>
       <c r="H9" t="str">
-        <v>French Montana</v>
+        <v>Maluma</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
-        <v>https://music.apple.com/us/artist/french-montana/475816358</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K9" t="str">
-        <v>https://music.apple.com/us/album/smoking-pt-2/1894333428</v>
+        <v>https://music.apple.com/us/album/tu-recuerdo/1895423065</v>
       </c>
       <c r="L9" t="str">
-        <v>Smoking pt. 2 - French Montana</v>
+        <v>Tu recuerdo - Maluma</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Dirty Rosie</v>
+        <v>Traitor (Roles Reversed)</v>
       </c>
       <c r="B10" t="str">
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>https://music.apple.com/us/song/dirty-rosie/6767044374</v>
+        <v>https://music.apple.com/us/song/traitor-roles-reversed/6767665959</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-15</v>
@@ -755,36 +755,36 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>Little Miss Twain</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G10" t="str">
-        <v>2:46</v>
+        <v>3:27</v>
       </c>
       <c r="H10" t="str">
-        <v>Shania Twain</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
-        <v>https://music.apple.com/us/artist/shania-twain/129974</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K10" t="str">
-        <v>https://music.apple.com/us/album/dirty-rosie/1896356105</v>
+        <v>https://music.apple.com/us/album/traitor-roles-reversed/6767665713</v>
       </c>
       <c r="L10" t="str">
-        <v>Dirty Rosie - Shania Twain</v>
+        <v>Traitor (Roles Reversed) - Megan Moroney</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Therapy at the Club</v>
+        <v>Dirty Rosie</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>https://music.apple.com/us/song/therapy-at-the-club/6764050150</v>
+        <v>https://music.apple.com/us/song/dirty-rosie/6767044374</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-15</v>
@@ -793,25 +793,25 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>THERAPY AT THE CLUB</v>
+        <v>Little Miss Twain</v>
       </c>
       <c r="G11" t="str">
-        <v>2:47</v>
+        <v>2:46</v>
       </c>
       <c r="H11" t="str">
-        <v>FLO</v>
+        <v>Shania Twain</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
-        <v>https://music.apple.com/us/artist/flo/1615611716</v>
+        <v>https://music.apple.com/us/artist/shania-twain/129974</v>
       </c>
       <c r="K11" t="str">
-        <v>https://music.apple.com/us/album/therapy-at-the-club/1895613904</v>
+        <v>https://music.apple.com/us/album/dirty-rosie/1896356105</v>
       </c>
       <c r="L11" t="str">
-        <v>Therapy at the Club - FLO</v>
+        <v>Dirty Rosie - Shania Twain</v>
       </c>
     </row>
     <row r="12">
@@ -854,13 +854,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>linknb</v>
+        <v>Hardy (feat. Clairo)</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/linknb/1888561848</v>
+        <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-15</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>new avatar</v>
+        <v>American Stories</v>
       </c>
       <c r="G13" t="str">
-        <v>1:55</v>
+        <v>3:53</v>
       </c>
       <c r="H13" t="str">
-        <v>Kelela</v>
+        <v>Rostam</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/kelela/549186342</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/linknb/1888561538</v>
+        <v>https://music.apple.com/us/album/hardy-feat-clairo/1876952750</v>
       </c>
       <c r="L13" t="str">
-        <v>linknb - Kelela</v>
+        <v>Hardy (feat. Clairo) - Rostam</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Robotic Love</v>
+        <v>2 Hard 4 The Radio</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/robotic-love/6763638857</v>
+        <v>https://music.apple.com/us/song/2-hard-4-the-radio/6769568610</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-15</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>Robotic Love - Single</v>
+        <v>ICEMAN</v>
       </c>
       <c r="G14" t="str">
-        <v>3:25</v>
+        <v>3:03</v>
       </c>
       <c r="H14" t="str">
-        <v>elkan</v>
+        <v>Drake</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/elkan/1805013361</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/robotic-love/1895412608</v>
+        <v>https://music.apple.com/us/album/2-hard-4-the-radio/6769568449</v>
       </c>
       <c r="L14" t="str">
-        <v>Robotic Love - elkan</v>
+        <v>2 Hard 4 The Radio - Drake</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Baby</v>
+        <v>Cheetah Print</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/baby/6763651180</v>
+        <v>https://music.apple.com/us/song/cheetah-print/6769557055</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-15</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>Baby - Single</v>
+        <v>MAID OF HONOUR</v>
       </c>
       <c r="G15" t="str">
-        <v>3:13</v>
+        <v>3:22</v>
       </c>
       <c r="H15" t="str">
-        <v>Prospa</v>
+        <v>Drake</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/baby/1895418297</v>
+        <v>https://music.apple.com/us/album/cheetah-print/6769556940</v>
       </c>
       <c r="L15" t="str">
-        <v>Baby - Prospa</v>
+        <v>Cheetah Print - Drake</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Boots (feat. Fetty Wap)</v>
+        <v>WNBA</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/boots-feat-fetty-wap/6763152116</v>
+        <v>https://music.apple.com/us/song/wnba/6769551471</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-15</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>Boots (feat. Fetty Wap) - Single</v>
+        <v>HABIBTI</v>
       </c>
       <c r="G16" t="str">
-        <v>2:39</v>
+        <v>2:58</v>
       </c>
       <c r="H16" t="str">
-        <v>Russell Dickerson</v>
+        <v>Drake</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/russell-dickerson/415673786</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/boots-feat-fetty-wap/1895187005</v>
+        <v>https://music.apple.com/us/album/wnba/6769551464</v>
       </c>
       <c r="L16" t="str">
-        <v>Boots (feat. Fetty Wap) - Russell Dickerson</v>
+        <v>WNBA - Drake</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Bed of Roses</v>
+        <v>Shadow Of A Man (Apple Music Live)</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/bed-of-roses/6765599768</v>
+        <v>https://music.apple.com/us/song/shadow-of-a-man-apple-music-live/6768201925</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-15</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>Bed of Roses - Single</v>
+        <v>Apple Music Live: MAYHEM Requiem</v>
       </c>
       <c r="G17" t="str">
-        <v>3:05</v>
+        <v>3:36</v>
       </c>
       <c r="H17" t="str">
-        <v>Teyana Taylor</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/teyana-taylor/216698214</v>
+        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/bed-of-roses/1896005623</v>
+        <v>https://music.apple.com/us/album/shadow-of-a-man-apple-music-live/6768201775</v>
       </c>
       <c r="L17" t="str">
-        <v>Bed of Roses - Teyana Taylor</v>
+        <v>Shadow Of A Man (Apple Music Live) - Lady Gaga</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Lo Arriesgo Todo</v>
+        <v>EPA</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/lo-arriesgo-todo/6766999307</v>
+        <v>https://music.apple.com/us/song/epa/6768420253</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-15</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Lo Arriesgo Todo - Single</v>
+        <v>EPA - Single</v>
       </c>
       <c r="G18" t="str">
-        <v>3:24</v>
+        <v>3:22</v>
       </c>
       <c r="H18" t="str">
-        <v>Bruno Mars</v>
+        <v>Becky G</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/lo-arriesgo-todo/6766999303</v>
+        <v>https://music.apple.com/us/album/epa/6768420251</v>
       </c>
       <c r="L18" t="str">
-        <v>Lo Arriesgo Todo - Bruno Mars</v>
+        <v>EPA - Becky G</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Big Dog</v>
+        <v>I’m your girl right?</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/big-dog/6762481627</v>
+        <v>https://music.apple.com/us/song/im-your-girl-right/6766440186</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-15</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>Big Dog - Single</v>
+        <v>ESTRUS</v>
       </c>
       <c r="G19" t="str">
-        <v>2:59</v>
+        <v>2:49</v>
       </c>
       <c r="H19" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Tove Lo</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/the-last-dinner-party/1680519203</v>
+        <v>https://music.apple.com/us/artist/tove-lo/570136838</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/big-dog/1894318010</v>
+        <v>https://music.apple.com/us/album/im-your-girl-right/6766440172</v>
       </c>
       <c r="L19" t="str">
-        <v>Big Dog - The Last Dinner Party</v>
+        <v>I’m your girl right? - Tove Lo</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Eastside Girls</v>
+        <v>fuëgo</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/eastside-girls/1870703307</v>
+        <v>https://music.apple.com/us/song/fu%C3%ABgo/6767661766</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-15</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>Dancing On The Wall</v>
+        <v>fuëgo - Single</v>
       </c>
       <c r="G20" t="str">
-        <v>3:50</v>
+        <v>3:46</v>
       </c>
       <c r="H20" t="str">
-        <v>MUNA</v>
+        <v>BNYX®</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/bnyx/1438325287</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/eastside-girls/1870702692</v>
+        <v>https://music.apple.com/us/album/fu%C3%ABgo/6767661604</v>
       </c>
       <c r="L20" t="str">
-        <v>Eastside Girls - MUNA</v>
+        <v>fuëgo - BNYX®</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>In The Stars</v>
+        <v>jajaja</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/in-the-stars/6764865395</v>
+        <v>https://music.apple.com/us/song/jajaja/6766341319</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-15</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>Foreign Tongues</v>
+        <v>jajaja - Single</v>
       </c>
       <c r="G21" t="str">
-        <v>4:13</v>
+        <v>2:45</v>
       </c>
       <c r="H21" t="str">
-        <v>The Rolling Stones</v>
+        <v>Chino Pacas</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/the-rolling-stones/1249595</v>
+        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/in-the-stars/1895941732</v>
+        <v>https://music.apple.com/us/album/jajaja/6766341318</v>
       </c>
       <c r="L21" t="str">
-        <v>In The Stars - The Rolling Stones</v>
+        <v>jajaja - Chino Pacas</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Home to Us</v>
+        <v>FIND GOD (feat. Dominic Fike)</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/home-to-us/1887403096</v>
+        <v>https://music.apple.com/us/song/find-god-feat-dominic-fike/1894315529</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-15</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>BULLDAWG</v>
       </c>
       <c r="G22" t="str">
-        <v>3:11</v>
+        <v>3:59</v>
       </c>
       <c r="H22" t="str">
-        <v>Paul McCartney</v>
+        <v>Kenny Mason</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v>https://music.apple.com/us/artist/kenny-mason/79382206</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/home-to-us/1887402919</v>
+        <v>https://music.apple.com/us/album/find-god-feat-dominic-fike/1894315301</v>
       </c>
       <c r="L22" t="str">
-        <v>Home to Us - Paul McCartney</v>
+        <v>FIND GOD (feat. Dominic Fike) - Kenny Mason</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Hurts Like You</v>
+        <v>FOOL ME ONCE (feat. Leon Thomas)</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/hurts-like-you/6765521189</v>
+        <v>https://music.apple.com/us/song/fool-me-once-feat-leon-thomas/1891467239</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-15</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>The Night Champion</v>
+        <v>BELOVED: ACT II</v>
       </c>
       <c r="G23" t="str">
-        <v>3:15</v>
+        <v>3:18</v>
       </c>
       <c r="H23" t="str">
-        <v>Koe Wetzel</v>
+        <v>GIVĒON</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
+        <v>https://music.apple.com/us/artist/giv%C4%93on/1070668868</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/hurts-like-you/1895978438</v>
+        <v>https://music.apple.com/us/album/fool-me-once-feat-leon-thomas/1891467233</v>
       </c>
       <c r="L23" t="str">
-        <v>Hurts Like You - Koe Wetzel</v>
+        <v>FOOL ME ONCE (feat. Leon Thomas) - GIVĒON</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Find Us Again</v>
+        <v>Shabang</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/find-us-again/6764638179</v>
+        <v>https://music.apple.com/us/song/shabang/6769568598</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-15</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>Find Us Again - Single</v>
+        <v>ICEMAN</v>
       </c>
       <c r="G24" t="str">
-        <v>2:58</v>
+        <v>3:08</v>
       </c>
       <c r="H24" t="str">
-        <v>Xavi</v>
+        <v>Drake</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/find-us-again/1895860349</v>
+        <v>https://music.apple.com/us/album/shabang/6769568449</v>
       </c>
       <c r="L24" t="str">
-        <v>Find Us Again - Xavi</v>
+        <v>Shabang - Drake</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Tied Up</v>
+        <v>Road Trips</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/tied-up/6765699130</v>
+        <v>https://music.apple.com/us/song/road-trips/6769557053</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-15</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Tied Up - Single</v>
+        <v>MAID OF HONOUR</v>
       </c>
       <c r="G25" t="str">
-        <v>2:56</v>
+        <v>4:03</v>
       </c>
       <c r="H25" t="str">
-        <v>Khalid</v>
+        <v>Drake</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/khalid/82842423</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/tied-up/1896041630</v>
+        <v>https://music.apple.com/us/album/road-trips/6769556940</v>
       </c>
       <c r="L25" t="str">
-        <v>Tied Up - Khalid</v>
+        <v>Road Trips - Drake</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Antes De Ti</v>
+        <v>Fortworth</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/antes-de-ti/1891167102</v>
+        <v>https://music.apple.com/us/song/fortworth/6769551482</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-15</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>Antes De Ti - Single</v>
+        <v>HABIBTI</v>
       </c>
       <c r="G26" t="str">
-        <v>2:56</v>
+        <v>3:51</v>
       </c>
       <c r="H26" t="str">
-        <v>Silvana Estrada</v>
+        <v>Drake</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/silvana-estrada/1277235729</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/antes-de-ti/1891167099</v>
+        <v>https://music.apple.com/us/album/fortworth/6769551464</v>
       </c>
       <c r="L26" t="str">
-        <v>Antes De Ti - Silvana Estrada</v>
+        <v>Fortworth - Drake</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>En La Misma Cama</v>
+        <v>Repeat It</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/en-la-misma-cama/6763670999</v>
+        <v>https://music.apple.com/us/song/repeat-it/6764277864</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-15</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>MUDA</v>
+        <v>Repeat It - Single</v>
       </c>
       <c r="G27" t="str">
-        <v>2:51</v>
+        <v>3:11</v>
       </c>
       <c r="H27" t="str">
-        <v>Carín León</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
+        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/en-la-misma-cama/1895429814</v>
+        <v>https://music.apple.com/us/album/repeat-it/1895713789</v>
       </c>
       <c r="L27" t="str">
-        <v>En La Misma Cama - Carín León</v>
+        <v>Repeat It - Martin Garrix</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>lovergirl</v>
+        <v>Fool Proof</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/lovergirl/6766366578</v>
+        <v>https://music.apple.com/us/song/fool-proof/1892466004</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-15</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>locket deluxe</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G28" t="str">
-        <v>3:21</v>
+        <v>2:36</v>
       </c>
       <c r="H28" t="str">
-        <v>Madison Beer</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/madison-beer/696146587</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/lovergirl/6766366564</v>
+        <v>https://music.apple.com/us/album/fool-proof/1892465981</v>
       </c>
       <c r="L28" t="str">
-        <v>lovergirl - Madison Beer</v>
+        <v>Fool Proof - Cody Johnson</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>PANIKI</v>
+        <v>Crisco</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/paniki/1892534080</v>
+        <v>https://music.apple.com/us/song/crisco/6763369506</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-15</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>Los Locos Nunca Mueren</v>
+        <v>Crisco - Single</v>
       </c>
       <c r="G29" t="str">
-        <v>2:36</v>
+        <v>2:56</v>
       </c>
       <c r="H29" t="str">
-        <v>Chuyin</v>
+        <v>Miranda Lambert</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/chuyin/1766532018</v>
+        <v>https://music.apple.com/us/artist/miranda-lambert/18732261</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/paniki/1892533803</v>
+        <v>https://music.apple.com/us/album/crisco/1895284236</v>
       </c>
       <c r="L29" t="str">
-        <v>PANIKI - Chuyin</v>
+        <v>Crisco - Miranda Lambert</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>DesOrden</v>
+        <v>Absolution</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/desorden/6765776443</v>
+        <v>https://music.apple.com/us/song/absolution/1884987651</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-15</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>DesOrden - Single</v>
+        <v>Forever Now</v>
       </c>
       <c r="G30" t="str">
-        <v>2:36</v>
+        <v>4:05</v>
       </c>
       <c r="H30" t="str">
-        <v>Alleh</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/alleh/1644755393</v>
+        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/desorden/1896069663</v>
+        <v>https://music.apple.com/us/album/absolution/1884987638</v>
       </c>
       <c r="L30" t="str">
-        <v>DesOrden - Alleh</v>
+        <v>Absolution - Switchfoot</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>LA Nights</v>
+        <v>JESUS IS ALIVE</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/la-nights/6763580223</v>
+        <v>https://music.apple.com/us/song/jesus-is-alive/6767694896</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-15</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>The Ville</v>
+        <v>JESUS IS ALIVE - Single</v>
       </c>
       <c r="G31" t="str">
-        <v>2:18</v>
+        <v>2:08</v>
       </c>
       <c r="H31" t="str">
-        <v>Trap Dickey</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/la-nights/1895384937</v>
+        <v>https://music.apple.com/us/album/jesus-is-alive/6767694895</v>
       </c>
       <c r="L31" t="str">
-        <v>LA Nights - Trap Dickey</v>
+        <v>JESUS IS ALIVE - Forrest Frank</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>The Payoff</v>
+        <v>Something To Lose</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/the-payoff/1891518506</v>
+        <v>https://music.apple.com/us/song/something-to-lose/6766964605</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-15</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>The Payoff - Single</v>
+        <v>Is This Heaven? - EP</v>
       </c>
       <c r="G32" t="str">
-        <v>5:51</v>
+        <v>2:55</v>
       </c>
       <c r="H32" t="str">
-        <v>Father John Misty</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/father-john-misty/514361724</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/the-payoff/1891518505</v>
+        <v>https://music.apple.com/us/album/something-to-lose/6766964604</v>
       </c>
       <c r="L32" t="str">
-        <v>The Payoff - Father John Misty</v>
+        <v>Something To Lose - STELLA LEFTY</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>The Weak</v>
+        <v>Too Busy Missing You</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/the-weak/1880484489</v>
+        <v>https://music.apple.com/us/song/too-busy-missing-you/6766604915</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-15</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>For Love of Grace &amp; the Hereafter</v>
+        <v>Off Campus: The Mixtape</v>
       </c>
       <c r="G33" t="str">
-        <v>3:15</v>
+        <v>3:25</v>
       </c>
       <c r="H33" t="str">
-        <v>Iceage</v>
+        <v>Asha Banks</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/the-weak/1880484160</v>
+        <v>https://music.apple.com/us/album/too-busy-missing-you/6766604455</v>
       </c>
       <c r="L33" t="str">
-        <v>The Weak - Iceage</v>
+        <v>Too Busy Missing You - Asha Banks</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Life Of The Faaji</v>
+        <v>F-Stop Blues (4-track)</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/life-of-the-faaji/1893417486</v>
+        <v>https://music.apple.com/us/song/f-stop-blues-4-track/1883173173</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-15</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>Fuji Xtra</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G34" t="str">
-        <v>2:29</v>
+        <v>3:00</v>
       </c>
       <c r="H34" t="str">
-        <v>Adekunle Gold</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/life-of-the-faaji/1893417480</v>
+        <v>https://music.apple.com/us/album/f-stop-blues-4-track/1883172879</v>
       </c>
       <c r="L34" t="str">
-        <v>Life Of The Faaji - Adekunle Gold</v>
+        <v>F-Stop Blues (4-track) - Jack Johnson</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Satisfy</v>
+        <v>PA' LO BONITO</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/satisfy/1894316978</v>
+        <v>https://music.apple.com/us/song/pa-lo-bonito/1886496944</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-15</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>Satisfy - Single</v>
+        <v>PA' LO BONITO - Single</v>
       </c>
       <c r="G35" t="str">
-        <v>3:06</v>
+        <v>3:04</v>
       </c>
       <c r="H35" t="str">
-        <v>Calvin Harris</v>
+        <v>Lenny Tavárez</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/calvin-harris/201955086</v>
+        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/satisfy/1894316975</v>
+        <v>https://music.apple.com/us/album/pa-lo-bonito/1886496943</v>
       </c>
       <c r="L35" t="str">
-        <v>Satisfy - Calvin Harris</v>
+        <v>PA' LO BONITO - Lenny Tavárez</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!)</v>
+        <v>LONELY</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/aftertaste-from-original-motion-picture-soundtrack-k-pops/6766316768</v>
+        <v>https://music.apple.com/us/song/lonely/6768757857</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-15</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!) - Single</v>
+        <v>DESEO</v>
       </c>
       <c r="G36" t="str">
-        <v>3:03</v>
+        <v>2:58</v>
       </c>
       <c r="H36" t="str">
-        <v>DEAN</v>
+        <v>Katteyes</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/dean/2770824</v>
+        <v>https://music.apple.com/us/artist/katteyes/1648818255</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/aftertaste-from-original-motion-picture-soundtrack-k-pops/6766316765</v>
+        <v>https://music.apple.com/us/album/lonely/6768757414</v>
       </c>
       <c r="L36" t="str">
-        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!) - DEAN</v>
+        <v>LONELY - Katteyes</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Ashin' the Blunt</v>
+        <v>Lockup</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/ashin-the-blunt/1884792300</v>
+        <v>https://music.apple.com/us/song/lockup/1894298102</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-15</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>Pure Devotion</v>
       </c>
       <c r="G37" t="str">
-        <v>3:48</v>
+        <v>4:31</v>
       </c>
       <c r="H37" t="str">
-        <v>6LACK</v>
+        <v>Overmono</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/overmono/1129806758</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/ashin-the-blunt/1884792154</v>
+        <v>https://music.apple.com/us/album/lockup/1894298100</v>
       </c>
       <c r="L37" t="str">
-        <v>Ashin' the Blunt - 6LACK</v>
+        <v>Lockup - Overmono</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>I Wanna Rock</v>
+        <v>Young</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/i-wanna-rock/1889577010</v>
+        <v>https://music.apple.com/us/song/young/6767698952</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-15</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>I Wanna Rock - Single</v>
+        <v>Young</v>
       </c>
       <c r="G38" t="str">
-        <v>3:44</v>
+        <v>2:46</v>
       </c>
       <c r="H38" t="str">
-        <v>Cash Cobain</v>
+        <v>Dan + Shay</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/cash-cobain/953108105</v>
+        <v>https://music.apple.com/us/artist/dan-shay/690319057</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/i-wanna-rock/1889577009</v>
+        <v>https://music.apple.com/us/album/young/6767698951</v>
       </c>
       <c r="L38" t="str">
-        <v>I Wanna Rock - Cash Cobain</v>
+        <v>Young - Dan + Shay</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Trying Times - A COLORS SHOW</v>
+        <v>Parachute</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/trying-times-a-colors-show/6764557224</v>
+        <v>https://music.apple.com/us/song/parachute/6764119241</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-15</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>Trying Times - A COLORS SHOW - Single</v>
+        <v>Parachute - Single</v>
       </c>
       <c r="G39" t="str">
-        <v>4:33</v>
+        <v>2:52</v>
       </c>
       <c r="H39" t="str">
-        <v>James Blake</v>
+        <v>Maren Morris</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/maren-morris/262260873</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/trying-times-a-colors-show/1895832124</v>
+        <v>https://music.apple.com/us/album/parachute/1895648983</v>
       </c>
       <c r="L39" t="str">
-        <v>Trying Times - A COLORS SHOW - James Blake</v>
+        <v>Parachute - Maren Morris</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>One Two Police</v>
+        <v>Little Things</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/one-two-police/6766293223</v>
+        <v>https://music.apple.com/us/song/little-things/6766351153</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-15</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>One Two Police - Single</v>
+        <v>Little Things - Single</v>
       </c>
       <c r="G40" t="str">
-        <v>2:46</v>
+        <v>2:55</v>
       </c>
       <c r="H40" t="str">
-        <v>BUNT.</v>
+        <v>Kevin Jonas</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/kevin-jonas/21138190</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/one-two-police/1896268827</v>
+        <v>https://music.apple.com/us/album/little-things/6766350882</v>
       </c>
       <c r="L40" t="str">
-        <v>One Two Police - BUNT.</v>
+        <v>Little Things - Kevin Jonas</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>HOME TO MOTHER</v>
+        <v>Fish Hunt Golf Drink</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/home-to-mother/1880198197</v>
+        <v>https://music.apple.com/us/song/fish-hunt-golf-drink/6766651884</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-15</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>Signs</v>
       </c>
       <c r="G41" t="str">
-        <v>3:16</v>
+        <v>2:34</v>
       </c>
       <c r="H41" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/home-to-mother/1880197844</v>
+        <v>https://music.apple.com/us/album/fish-hunt-golf-drink/6766651878</v>
       </c>
       <c r="L41" t="str">
-        <v>HOME TO MOTHER - Stephen Sanchez</v>
+        <v>Fish Hunt Golf Drink - Luke Bryan</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Illuminate</v>
+        <v>PAGEANT STAGE</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/illuminate/6764646733</v>
+        <v>https://music.apple.com/us/song/pageant-stage/6764125889</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-15</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Illuminate (FIFA World Cup 2026™) - Single</v>
+        <v>THE EDGE</v>
       </c>
       <c r="G42" t="str">
-        <v>3:03</v>
+        <v>2:52</v>
       </c>
       <c r="H42" t="str">
-        <v>Jessie Reyez</v>
+        <v>Tone Stith</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/tone-stith/1167717310</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/illuminate/1895862895</v>
+        <v>https://music.apple.com/us/album/pageant-stage/1895651504</v>
       </c>
       <c r="L42" t="str">
-        <v>Illuminate - Jessie Reyez</v>
+        <v>PAGEANT STAGE - Tone Stith</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>OKAY!</v>
+        <v>Firestorm</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/okay/6765792669</v>
+        <v>https://music.apple.com/us/song/firestorm/1868827004</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-15</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>OKAY! - Single</v>
+        <v>Of Earth &amp; Wires</v>
       </c>
       <c r="G43" t="str">
-        <v>4:34</v>
+        <v>2:29</v>
       </c>
       <c r="H43" t="str">
-        <v>Forrest Frank</v>
+        <v>Dua Saleh</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
+        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/okay/1896077066</v>
+        <v>https://music.apple.com/us/album/firestorm/1868826829</v>
       </c>
       <c r="L43" t="str">
-        <v>OKAY! - Forrest Frank</v>
+        <v>Firestorm - Dua Saleh</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>FLOW</v>
+        <v>girl next door</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/flow/6765469196</v>
+        <v>https://music.apple.com/us/song/girl-next-door/6768077610</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-15</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>FLOW - Single</v>
+        <v>girl next door - Single</v>
       </c>
       <c r="G44" t="str">
-        <v>4:20</v>
+        <v>3:18</v>
       </c>
       <c r="H44" t="str">
-        <v>iZaak</v>
+        <v>mgk</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/izaak/1295819563</v>
+        <v>https://music.apple.com/us/artist/mgk/465954501</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/flow/1895961693</v>
+        <v>https://music.apple.com/us/album/girl-next-door/6768077609</v>
       </c>
       <c r="L44" t="str">
-        <v>FLOW - iZaak</v>
+        <v>girl next door - mgk</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>aiaiaiaiai</v>
+        <v>BIG DOG</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/aiaiaiaiai/6764338271</v>
+        <v>https://music.apple.com/us/song/big-dog/1887197046</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-15</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>aiaiaiaiai - Single</v>
+        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
       </c>
       <c r="G45" t="str">
-        <v>2:20</v>
+        <v>3:36</v>
       </c>
       <c r="H45" t="str">
-        <v>Mau y Ricky</v>
+        <v>Genesis Owusu</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/aiaiaiaiai/1895739038</v>
+        <v>https://music.apple.com/us/album/big-dog/1887196431</v>
       </c>
       <c r="L45" t="str">
-        <v>aiaiaiaiai - Mau y Ricky</v>
+        <v>BIG DOG - Genesis Owusu</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Control</v>
+        <v>idea of love - A COLORS SHOW</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/control/6765502013</v>
+        <v>https://music.apple.com/us/song/idea-of-love-a-colors-show/6767667046</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-15</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>God Must Really Love Me</v>
+        <v>idea of love - A COLORS SHOW - Single</v>
       </c>
       <c r="G46" t="str">
-        <v>2:32</v>
+        <v>2:34</v>
       </c>
       <c r="H46" t="str">
-        <v>Tori Kelly</v>
+        <v>kwn</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/tori-kelly/437581991</v>
+        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/control/1895974889</v>
+        <v>https://music.apple.com/us/album/idea-of-love-a-colors-show/6767666835</v>
       </c>
       <c r="L46" t="str">
-        <v>Control - Tori Kelly</v>
+        <v>idea of love - A COLORS SHOW - kwn</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ORIGAMI!</v>
+        <v>Heavy Serenade</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/origami/1892544033</v>
+        <v>https://music.apple.com/us/song/heavy-serenade/1892154309</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-15</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>ORIGAMI! - Single</v>
+        <v>Heavy Serenade - EP</v>
       </c>
       <c r="G47" t="str">
-        <v>2:34</v>
+        <v>3:00</v>
       </c>
       <c r="H47" t="str">
-        <v>Kesha</v>
+        <v>NMIXX</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/kesha/334854763</v>
+        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/origami/1892544026</v>
+        <v>https://music.apple.com/us/album/heavy-serenade/1892154305</v>
       </c>
       <c r="L47" t="str">
-        <v>ORIGAMI! - Kesha</v>
+        <v>Heavy Serenade - NMIXX</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Love Is Kind</v>
+        <v>ddok ddok ddok</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/love-is-kind/1894074886</v>
+        <v>https://music.apple.com/us/song/ddok-ddok-ddok/6764203482</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-15</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>Love Is Kind - EP</v>
+        <v>ddok ddok ddok - Single</v>
       </c>
       <c r="G48" t="str">
-        <v>4:07</v>
+        <v>2:35</v>
       </c>
       <c r="H48" t="str">
-        <v>The Chainsmokers</v>
+        <v>BOYNEXTDOOR</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
+        <v>https://music.apple.com/us/artist/boynextdoor/1687612559</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/love-is-kind/1894074877</v>
+        <v>https://music.apple.com/us/album/ddok-ddok-ddok/6764203481</v>
       </c>
       <c r="L48" t="str">
-        <v>Love Is Kind - The Chainsmokers</v>
+        <v>ddok ddok ddok - BOYNEXTDOOR</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Feathers In A Storm</v>
+        <v>Shut It Down</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/feathers-in-a-storm/1864390075</v>
+        <v>https://music.apple.com/us/song/shut-it-down/6763631128</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-15</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>Let It Die Here</v>
+        <v>Shut It Down - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>4:00</v>
+        <v>3:32</v>
       </c>
       <c r="H49" t="str">
-        <v>Linda Perry</v>
+        <v>Boys Noize</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/boys-noize/60393190</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/feathers-in-a-storm/1864389779</v>
+        <v>https://music.apple.com/us/album/shut-it-down/1895408470</v>
       </c>
       <c r="L49" t="str">
-        <v>Feathers In A Storm - Linda Perry</v>
+        <v>Shut It Down - Boys Noize</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Playing God</v>
+        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss)</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/playing-god/6765780293</v>
+        <v>https://music.apple.com/us/song/together-feat-nikki-nair-jessy-lanza-prentiss/6763207821</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-15</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Decades</v>
+        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss) - Single</v>
       </c>
       <c r="G50" t="str">
-        <v>3:39</v>
+        <v>3:18</v>
       </c>
       <c r="H50" t="str">
-        <v>Motionless In White</v>
+        <v>The Avalanches</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
+        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/playing-god/1896071360</v>
+        <v>https://music.apple.com/us/album/together-feat-nikki-nair-jessy-lanza-prentiss/1895215105</v>
       </c>
       <c r="L50" t="str">
-        <v>Playing God - Motionless In White</v>
+        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss) - The Avalanches</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Cut</v>
+        <v>Can’t Miss You</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/cut/1879494712</v>
+        <v>https://music.apple.com/us/song/cant-miss-you/1886810999</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-15</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>VINDICATE</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="G51" t="str">
-        <v>3:59</v>
+        <v>2:32</v>
       </c>
       <c r="H51" t="str">
-        <v>Black Veil Brides</v>
+        <v>Sublime</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/black-veil-brides/276789923</v>
+        <v>https://music.apple.com/us/artist/sublime/63480</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/cut/1879494510</v>
+        <v>https://music.apple.com/us/album/cant-miss-you/1886810990</v>
       </c>
       <c r="L51" t="str">
-        <v>Cut - Black Veil Brides</v>
+        <v>Can’t Miss You - Sublime</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Freaking Out</v>
+        <v>Razorblades And Runways</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/freaking-out/1894067912</v>
+        <v>https://music.apple.com/us/song/razorblades-and-runways/1888004809</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-15</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>Over Before You Know It</v>
+        <v>Get It Honest</v>
       </c>
       <c r="G52" t="str">
-        <v>3:03</v>
+        <v>3:33</v>
       </c>
       <c r="H52" t="str">
-        <v>Michigander</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/michigander/1096482927</v>
+        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/freaking-out/1894067897</v>
+        <v>https://music.apple.com/us/album/razorblades-and-runways/1888004802</v>
       </c>
       <c r="L52" t="str">
-        <v>Freaking Out - Michigander</v>
+        <v>Razorblades And Runways - The Revivalists</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>FIYAH</v>
+        <v>Massacre</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/fiyah/6764321306</v>
+        <v>https://music.apple.com/us/song/massacre/1892127745</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-15</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>FIYAH - Single</v>
+        <v>Massacre - Single</v>
       </c>
       <c r="G53" t="str">
-        <v>3:12</v>
+        <v>2:55</v>
       </c>
       <c r="H53" t="str">
-        <v>YG Marley</v>
+        <v>Murex</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/yg-marley/1496864889</v>
+        <v>https://music.apple.com/us/artist/murex/1607430925</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/fiyah/1895732105</v>
+        <v>https://music.apple.com/us/album/massacre/1892127742</v>
       </c>
       <c r="L53" t="str">
-        <v>FIYAH - YG Marley</v>
+        <v>Massacre - Murex</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Ten to Midnight</v>
+        <v>Better That Way</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/ten-to-midnight/1885047105</v>
+        <v>https://music.apple.com/us/song/better-that-way/6766273199</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-15</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>Wild</v>
+        <v>Christian Name</v>
       </c>
       <c r="G54" t="str">
-        <v>3:12</v>
+        <v>3:45</v>
       </c>
       <c r="H54" t="str">
-        <v>Ashley McBryde</v>
+        <v>Charles Wesley Godwin</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/charles-wesley-godwin/1441994025</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/ten-to-midnight/1885046822</v>
+        <v>https://music.apple.com/us/album/better-that-way/1896261802</v>
       </c>
       <c r="L54" t="str">
-        <v>Ten to Midnight - Ashley McBryde</v>
+        <v>Better That Way - Charles Wesley Godwin</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Carry On</v>
+        <v>Apollo</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/carry-on/1893511608</v>
+        <v>https://music.apple.com/us/song/apollo/6765602431</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-15</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Carry On - Single</v>
+        <v>Apollo - Single</v>
       </c>
       <c r="G55" t="str">
-        <v>3:00</v>
+        <v>3:35</v>
       </c>
       <c r="H55" t="str">
-        <v>Kenny Chesney</v>
+        <v>Bryant Barnes</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/kenny-chesney/205322</v>
+        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/carry-on/1893511607</v>
+        <v>https://music.apple.com/us/album/apollo/6765602369</v>
       </c>
       <c r="L55" t="str">
-        <v>Carry On - Kenny Chesney</v>
+        <v>Apollo - Bryant Barnes</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>[PRESS]</v>
+        <v>Infinity (123)</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/press/6764735125</v>
+        <v>https://music.apple.com/us/song/infinity-123/6763447312</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-15</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>[PRESS] - Single</v>
+        <v>Infinity (123) - Single</v>
       </c>
       <c r="G56" t="str">
-        <v>1:40</v>
+        <v>2:19</v>
       </c>
       <c r="H56" t="str">
-        <v>Armani White</v>
+        <v>December 10</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/armani-white/1129439109</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/press/1895898254</v>
+        <v>https://music.apple.com/us/album/infinity-123/1895320456</v>
       </c>
       <c r="L56" t="str">
-        <v>[PRESS] - Armani White</v>
+        <v>Infinity (123) - December 10</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Hold Me In The Dark</v>
+        <v>Ain't Over Me Yet</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/hold-me-in-the-dark/1886119371</v>
+        <v>https://music.apple.com/us/song/aint-over-me-yet/6767283811</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-15</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>My Mess, My Heart, My Life.</v>
+        <v>Cherry Valley Forever</v>
       </c>
       <c r="G57" t="str">
-        <v>3:17</v>
+        <v>3:24</v>
       </c>
       <c r="H57" t="str">
-        <v>Myles Smith</v>
+        <v>Carter Faith</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
+        <v>https://music.apple.com/us/artist/carter-faith/1489205896</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/hold-me-in-the-dark/1886119367</v>
+        <v>https://music.apple.com/us/album/aint-over-me-yet/1896458169</v>
       </c>
       <c r="L57" t="str">
-        <v>Hold Me In The Dark - Myles Smith</v>
+        <v>Ain't Over Me Yet - Carter Faith</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Lo Que Me Pasa Con Vos</v>
+        <v>Where Did You Go</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/lo-que-me-pasa-con-vos/6765831961</v>
+        <v>https://music.apple.com/us/song/where-did-you-go/1877958504</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-15</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>Lo Que Me Pasa Con Vos - Single</v>
+        <v>Growing Pains (Deluxe)</v>
       </c>
       <c r="G58" t="str">
-        <v>2:53</v>
+        <v>2:47</v>
       </c>
       <c r="H58" t="str">
-        <v>Sebastián Yatra</v>
+        <v>Trousdale</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/sebasti%C3%A1n-yatra/722264654</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/lo-que-me-pasa-con-vos/1896093008</v>
+        <v>https://music.apple.com/us/album/where-did-you-go/1877958112</v>
       </c>
       <c r="L58" t="str">
-        <v>Lo Que Me Pasa Con Vos - Sebastián Yatra</v>
+        <v>Where Did You Go - Trousdale</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Wide Eyed</v>
+        <v>I LOVE YOU</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/wide-eyed/1884734079</v>
+        <v>https://music.apple.com/us/song/i-love-you/6766999950</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-15</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>Wide Eyed</v>
+        <v>I LOVE YOU - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>3:22</v>
+        <v>3:11</v>
       </c>
       <c r="H59" t="str">
-        <v>Mack Keane</v>
+        <v>Noga Erez</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/mack-keane/899781096</v>
+        <v>https://music.apple.com/us/artist/noga-erez/1166657901</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/wide-eyed/1884733813</v>
+        <v>https://music.apple.com/us/album/i-love-you/6766999949</v>
       </c>
       <c r="L59" t="str">
-        <v>Wide Eyed - Mack Keane</v>
+        <v>I LOVE YOU - Noga Erez</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Changes</v>
+        <v>Housekeeping</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/changes/6763650807</v>
+        <v>https://music.apple.com/us/song/housekeeping/6766290834</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-15</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Changes - Single</v>
+        <v>Housekeeping - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>3:18</v>
+        <v>3:25</v>
       </c>
       <c r="H60" t="str">
-        <v>Tommy Richman</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/tommy-richman/1447723583</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/changes/1895418156</v>
+        <v>https://music.apple.com/us/album/housekeeping/6766290823</v>
       </c>
       <c r="L60" t="str">
-        <v>Changes - Tommy Richman</v>
+        <v>Housekeeping - Ally Salort</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Don't Say Goodbye</v>
+        <v>Surprise Surprise</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/dont-say-goodbye/6765758054</v>
+        <v>https://music.apple.com/us/song/surprise-surprise/6764842119</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-15</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>The Story of Michael and Tanya</v>
+        <v>Surprise Surprise - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>4:33</v>
+        <v>2:55</v>
       </c>
       <c r="H61" t="str">
-        <v>The War And Treaty</v>
+        <v>Chloe Qisha</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/the-war-and-treaty/951165936</v>
+        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/dont-say-goodbye/1896061742</v>
+        <v>https://music.apple.com/us/album/surprise-surprise/1895934408</v>
       </c>
       <c r="L61" t="str">
-        <v>Don't Say Goodbye - The War And Treaty</v>
+        <v>Surprise Surprise - Chloe Qisha</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>depressed on the internet</v>
+        <v>Dog</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/depressed-on-the-internet/6763440792</v>
+        <v>https://music.apple.com/us/song/dog/1885967384</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-15</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>depressed on the internet - Single</v>
+        <v>Gentleman</v>
       </c>
       <c r="G62" t="str">
-        <v>2:57</v>
+        <v>3:08</v>
       </c>
       <c r="H62" t="str">
-        <v>Bea Miller</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/bea-miller/706171903</v>
+        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/depressed-on-the-internet/1895316228</v>
+        <v>https://music.apple.com/us/album/dog/1885967368</v>
       </c>
       <c r="L62" t="str">
-        <v>depressed on the internet - Bea Miller</v>
+        <v>Dog - Towa Bird</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Dear Burt</v>
+        <v>I Never See Her</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/dear-burt/1886736665</v>
+        <v>https://music.apple.com/us/song/i-never-see-her/6764149225</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-15</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Scenes from a Velvet Room</v>
+        <v>I Never See Her - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>2:53</v>
+        <v>3:04</v>
       </c>
       <c r="H63" t="str">
-        <v>Stephan Moccio</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
+        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/dear-burt/1886736650</v>
+        <v>https://music.apple.com/us/album/i-never-see-her/1895660748</v>
       </c>
       <c r="L63" t="str">
-        <v>Dear Burt - Stephan Moccio</v>
+        <v>I Never See Her - Spacey Jane</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Alla Blues</v>
+        <v>No God</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/alla-blues/6764654322</v>
+        <v>https://music.apple.com/us/song/no-god/1891187414</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-15</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Black Mozart</v>
+        <v>Alone Together</v>
       </c>
       <c r="G64" t="str">
-        <v>2:50</v>
+        <v>2:45</v>
       </c>
       <c r="H64" t="str">
-        <v>Jon Batiste</v>
+        <v>Show Me the Body</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
+        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/alla-blues/1895866355</v>
+        <v>https://music.apple.com/us/album/no-god/1891187411</v>
       </c>
       <c r="L64" t="str">
-        <v>Alla Blues - Jon Batiste</v>
+        <v>No God - Show Me the Body</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Think About Me</v>
+        <v>burden</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/think-about-me/6765783932</v>
+        <v>https://music.apple.com/us/song/burden/6767688180</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-15</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Think About Me - Single</v>
+        <v>burden - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>2:39</v>
+        <v>3:24</v>
       </c>
       <c r="H65" t="str">
-        <v>Gabriella Rose</v>
+        <v>Abe Parker</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
+        <v>https://music.apple.com/us/artist/abe-parker/490444584</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/think-about-me/1896073124</v>
+        <v>https://music.apple.com/us/album/burden/6767688179</v>
       </c>
       <c r="L65" t="str">
-        <v>Think About Me - Gabriella Rose</v>
+        <v>burden - Abe Parker</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Meet Again</v>
+        <v>Chico Raro</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/meet-again/6764129305</v>
+        <v>https://music.apple.com/us/song/chico-raro/6767713536</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-15</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Meet Again - Single</v>
+        <v>Chico Raro - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>3:26</v>
+        <v>3:17</v>
       </c>
       <c r="H66" t="str">
-        <v>Kaskade</v>
+        <v>Arón Piper</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/kaskade/2827464</v>
+        <v>https://music.apple.com/us/artist/ar%C3%B3n-piper/691972942</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/meet-again/1895652592</v>
+        <v>https://music.apple.com/us/album/chico-raro/6767713527</v>
       </c>
       <c r="L66" t="str">
-        <v>Meet Again - Kaskade</v>
+        <v>Chico Raro - Arón Piper</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Happy Now</v>
+        <v>What's Done Is Done</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/happy-now/1857952261</v>
+        <v>https://music.apple.com/us/song/whats-done-is-done/6763088629</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-15</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>The Afterparty</v>
+        <v>What's Done Is Done - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>2:42</v>
+        <v>2:53</v>
       </c>
       <c r="H67" t="str">
-        <v>Lykke Li</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
+        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/happy-now/1857952252</v>
+        <v>https://music.apple.com/us/album/whats-done-is-done/1895156626</v>
       </c>
       <c r="L67" t="str">
-        <v>Happy Now - Lykke Li</v>
+        <v>What's Done Is Done - Jorja Smith</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Oblivion</v>
+        <v>round and round</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/oblivion/1888236202</v>
+        <v>https://music.apple.com/us/song/round-and-round/1885665987</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-15</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Oblivion - Single</v>
+        <v>round and round - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>2:21</v>
+        <v>2:47</v>
       </c>
       <c r="H68" t="str">
-        <v>Agents Of Time</v>
+        <v>bbno$</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/agents-of-time/794971951</v>
+        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/oblivion/1888236199</v>
+        <v>https://music.apple.com/us/album/round-and-round/1885665982</v>
       </c>
       <c r="L68" t="str">
-        <v>Oblivion - Agents Of Time</v>
+        <v>round and round - bbno$</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>See U in Hell (From the Netflix Series "Devil May Cry")</v>
+        <v>Ain’t That Deep</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/see-u-in-hell-from-the-netflix-series-devil-may-cry/1894386678</v>
+        <v>https://music.apple.com/us/song/aint-that-deep/1882831449</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-15</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>See U in Hell (From the Netflix Series "Devil May Cry") - Single</v>
+        <v>The Last Balloon</v>
       </c>
       <c r="G69" t="str">
-        <v>4:03</v>
+        <v>2:39</v>
       </c>
       <c r="H69" t="str">
-        <v>Papa Roach</v>
+        <v>Tank and the Bangas</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
+        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/see-u-in-hell-from-the-netflix-series-devil-may-cry/1894386676</v>
+        <v>https://music.apple.com/us/album/aint-that-deep/1882831446</v>
       </c>
       <c r="L69" t="str">
-        <v>See U in Hell (From the Netflix Series "Devil May Cry") - Papa Roach</v>
+        <v>Ain’t That Deep - Tank and the Bangas</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Top of the Hill</v>
+        <v>Emily</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/top-of-the-hill/6766614503</v>
+        <v>https://music.apple.com/us/song/emily/1893405442</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-15</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Top of the Hill - Single</v>
+        <v>So Much To Say - EP</v>
       </c>
       <c r="G70" t="str">
-        <v>1:50</v>
+        <v>2:35</v>
       </c>
       <c r="H70" t="str">
-        <v>DDG</v>
+        <v>Daisy Grenade</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/ddg/3954994</v>
+        <v>https://music.apple.com/us/artist/daisy-grenade/1611437131</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/top-of-the-hill/6766614303</v>
+        <v>https://music.apple.com/us/album/emily/1893405440</v>
       </c>
       <c r="L70" t="str">
-        <v>Top of the Hill - DDG</v>
+        <v>Emily - Daisy Grenade</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Oh Savannah</v>
+        <v>Hold</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/oh-savannah/1869140944</v>
+        <v>https://music.apple.com/us/song/hold/6767296480</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-15</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Change Of Plans</v>
+        <v>Hold - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>3:05</v>
+        <v>4:07</v>
       </c>
       <c r="H71" t="str">
-        <v>49 Winchester</v>
+        <v>Sabrina Sterling</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/49-winchester/869425058</v>
+        <v>https://music.apple.com/us/artist/sabrina-sterling/1577892147</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/oh-savannah/1869140544</v>
+        <v>https://music.apple.com/us/album/hold/1896462063</v>
       </c>
       <c r="L71" t="str">
-        <v>Oh Savannah - 49 Winchester</v>
+        <v>Hold - Sabrina Sterling</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Game On (feat. JT)</v>
+        <v>Flying Monkey</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/game-on-feat-jt/6763271985</v>
+        <v>https://music.apple.com/us/song/flying-monkey/1894351228</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-15</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Sugar Girl - EP</v>
+        <v>Flying Monkey - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>2:29</v>
+        <v>4:09</v>
       </c>
       <c r="H72" t="str">
-        <v>Little Simz</v>
+        <v>Blue Medusa</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/little-simz/627674564</v>
+        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/game-on-feat-jt/1895242144</v>
+        <v>https://music.apple.com/us/album/flying-monkey/1894351227</v>
       </c>
       <c r="L72" t="str">
-        <v>Game On (feat. JT) - Little Simz</v>
+        <v>Flying Monkey - Blue Medusa</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>How to Forget</v>
+        <v>Anything Goes</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/how-to-forget/1874100607</v>
+        <v>https://music.apple.com/us/song/anything-goes/1891118972</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-15</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>ARCADE</v>
+        <v>Anything Goes</v>
       </c>
       <c r="G73" t="str">
-        <v>4:01</v>
+        <v>3:00</v>
       </c>
       <c r="H73" t="str">
-        <v>Deb Never</v>
+        <v>Kaleena Zanders</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/how-to-forget/1874100412</v>
+        <v>https://music.apple.com/us/album/anything-goes/1891118971</v>
       </c>
       <c r="L73" t="str">
-        <v>How to Forget - Deb Never</v>
+        <v>Anything Goes - Kaleena Zanders</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Ne Plus Ultra</v>
+        <v>We Are</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/ne-plus-ultra/6765530891</v>
+        <v>https://music.apple.com/us/song/we-are/1894252873</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-15</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>Ne Plus Ultra - Single</v>
+        <v>We Are - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>2:49</v>
+        <v>3:33</v>
       </c>
       <c r="H74" t="str">
-        <v>ear</v>
+        <v>Adam Ten</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/ear/1829661500</v>
+        <v>https://music.apple.com/us/artist/adam-ten/1472226854</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/ne-plus-ultra/1895982136</v>
+        <v>https://music.apple.com/us/album/we-are/1894252870</v>
       </c>
       <c r="L74" t="str">
-        <v>Ne Plus Ultra - ear</v>
+        <v>We Are - Adam Ten</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Mirror</v>
+        <v>It's For the Kids</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/mirror/6763620093</v>
+        <v>https://music.apple.com/us/song/its-for-the-kids/1867327679</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-15</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Mirror - Single</v>
+        <v>Cursum Perficio</v>
       </c>
       <c r="G75" t="str">
-        <v>3:19</v>
+        <v>4:20</v>
       </c>
       <c r="H75" t="str">
-        <v>MOD SUN</v>
+        <v>Anthrax</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/mod-sun/373888452</v>
+        <v>https://music.apple.com/us/artist/anthrax/80417</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/mirror/1895402181</v>
+        <v>https://music.apple.com/us/album/its-for-the-kids/1867327673</v>
       </c>
       <c r="L75" t="str">
-        <v>Mirror - MOD SUN</v>
+        <v>It's For the Kids - Anthrax</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Miel Con Licor</v>
+        <v>Pure Ecstasy</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/miel-con-licor/6763085043</v>
+        <v>https://music.apple.com/us/song/pure-ecstasy/6762228978</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-15</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Bandera Blanca</v>
+        <v>Pure Ecstasy</v>
       </c>
       <c r="G76" t="str">
-        <v>3:27</v>
+        <v>3:05</v>
       </c>
       <c r="H76" t="str">
-        <v>Christian Nodal</v>
+        <v>Beartooth</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
+        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/miel-con-licor/1895154946</v>
+        <v>https://music.apple.com/us/album/pure-ecstasy/1893453878</v>
       </c>
       <c r="L76" t="str">
-        <v>Miel Con Licor - Christian Nodal</v>
+        <v>Pure Ecstasy - Beartooth</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Macramé (feat. Mei Semones)</v>
+        <v>Something Wicked</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/macram%C3%A9-feat-mei-semones/6763155997</v>
+        <v>https://music.apple.com/us/song/something-wicked/6766252959</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-15</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Macramé (feat. Mei Semones) - Single</v>
+        <v>Something Wicked - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>3:31</v>
+        <v>3:28</v>
       </c>
       <c r="H77" t="str">
-        <v>aron!</v>
+        <v>Breaking Benjamin</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/aron/1673838787</v>
+        <v>https://music.apple.com/us/artist/breaking-benjamin/3299379</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/macram%C3%A9-feat-mei-semones/1895189295</v>
+        <v>https://music.apple.com/us/album/something-wicked/1896253678</v>
       </c>
       <c r="L77" t="str">
-        <v>Macramé (feat. Mei Semones) - aron!</v>
+        <v>Something Wicked - Breaking Benjamin</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Nighttime (feat. Austin Brown &amp; David Shaw)</v>
+        <v>Feel The Funk</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/nighttime-feat-austin-brown-david-shaw/1882831738</v>
+        <v>https://music.apple.com/us/song/feel-the-funk/6763294007</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-15</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>The Last Balloon</v>
+        <v>The Funk EP - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>3:14</v>
+        <v>3:26</v>
       </c>
       <c r="H78" t="str">
-        <v>Tank and the Bangas</v>
+        <v>Riordan</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
+        <v>https://music.apple.com/us/artist/riordan/1517575029</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/nighttime-feat-austin-brown-david-shaw/1882831446</v>
+        <v>https://music.apple.com/us/album/feel-the-funk/1895251685</v>
       </c>
       <c r="L78" t="str">
-        <v>Nighttime (feat. Austin Brown &amp; David Shaw) - Tank and the Bangas</v>
+        <v>Feel The Funk - Riordan</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>They Found One Of My Graves</v>
+        <v>Everglades (Remix)</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/they-found-one-of-my-graves/1881564857</v>
+        <v>https://music.apple.com/us/song/everglades-remix/6767719584</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-15</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Pre-Historic Metal</v>
+        <v>Everglades (Remix) - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>5:14</v>
+        <v>2:42</v>
       </c>
       <c r="H79" t="str">
-        <v>Darkthrone</v>
+        <v>Aziedoesntexist</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/darkthrone/112417640</v>
+        <v>https://music.apple.com/us/artist/aziedoesntexist/1831152556</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/they-found-one-of-my-graves/1881564845</v>
+        <v>https://music.apple.com/us/album/everglades-remix/6767719577</v>
       </c>
       <c r="L79" t="str">
-        <v>They Found One Of My Graves - Darkthrone</v>
+        <v>Everglades (Remix) - Aziedoesntexist</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Cloudfall</v>
+        <v>Walk</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/cloudfall/1892921580</v>
+        <v>https://music.apple.com/us/song/walk/1892180098</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-15</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Cycles in the Infinite Dream</v>
+        <v>Walk - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>4:06</v>
+        <v>2:25</v>
       </c>
       <c r="H80" t="str">
-        <v>REZN</v>
+        <v>Melodicb</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/rezn/1441800527</v>
+        <v>https://music.apple.com/us/artist/melodicb/1440206517</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/cloudfall/1892921394</v>
+        <v>https://music.apple.com/us/album/walk/1892180097</v>
       </c>
       <c r="L80" t="str">
-        <v>Cloudfall - REZN</v>
+        <v>Walk - Melodicb</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Doom in Bloom</v>
+        <v>Volver a Ti</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/doom-in-bloom/1883081839</v>
+        <v>https://music.apple.com/us/song/volver-a-ti/6766258204</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-15</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Hum of Hurt</v>
+        <v>Norteña</v>
       </c>
       <c r="G81" t="str">
-        <v>3:17</v>
+        <v>3:47</v>
       </c>
       <c r="H81" t="str">
-        <v>Converge</v>
+        <v>Julieta Venegas</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/julieta-venegas/302960</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/doom-in-bloom/1883081837</v>
+        <v>https://music.apple.com/us/album/volver-a-ti/1896255736</v>
       </c>
       <c r="L81" t="str">
-        <v>Doom in Bloom - Converge</v>
+        <v>Volver a Ti - Julieta Venegas</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Only The Good I Keep</v>
+        <v>Bahamas</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/only-the-good-i-keep/1871484973</v>
+        <v>https://music.apple.com/us/song/bahamas/6764695848</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-15</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Remember The Humans</v>
+        <v>Bahamas - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>3:27</v>
+        <v>2:06</v>
       </c>
       <c r="H82" t="str">
-        <v>Broken Social Scene</v>
+        <v>LENCHO</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/broken-social-scene/6925799</v>
+        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/only-the-good-i-keep/1871484971</v>
+        <v>https://music.apple.com/us/album/bahamas/6764695847</v>
       </c>
       <c r="L82" t="str">
-        <v>Only The Good I Keep - Broken Social Scene</v>
+        <v>Bahamas - LENCHO</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Zoom 97</v>
+        <v>Same Old Song</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/zoom-97/1884970574</v>
+        <v>https://music.apple.com/us/song/same-old-song/6762860685</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-15</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Philadelphia's been good to me</v>
+        <v>Same Old Song - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>4:54</v>
+        <v>4:12</v>
       </c>
       <c r="H83" t="str">
-        <v>Kurt Vile</v>
+        <v>Lila Drew</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/kurt-vile/274234314</v>
+        <v>https://music.apple.com/us/artist/lila-drew/1439482732</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/zoom-97/1884970572</v>
+        <v>https://music.apple.com/us/album/same-old-song/1895047985</v>
       </c>
       <c r="L83" t="str">
-        <v>Zoom 97 - Kurt Vile</v>
+        <v>Same Old Song - Lila Drew</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Switch Up</v>
+        <v>gentle</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/switch-up/6764419407</v>
+        <v>https://music.apple.com/us/song/gentle/6762828356</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-15</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Switch Up - Single</v>
+        <v>gentle - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>3:35</v>
+        <v>2:48</v>
       </c>
       <c r="H84" t="str">
-        <v>Mike D</v>
+        <v>Venus Anon</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
+        <v>https://music.apple.com/us/artist/venus-anon/1635970130</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/switch-up/1895772278</v>
+        <v>https://music.apple.com/us/album/gentle/1895031896</v>
       </c>
       <c r="L84" t="str">
-        <v>Switch Up - Mike D</v>
+        <v>gentle - Venus Anon</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Surprise</v>
+        <v>Letters of Your Name</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/surprise/1894873625</v>
+        <v>https://music.apple.com/us/song/letters-of-your-name/1892919741</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-15</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Doe Or Die III</v>
+        <v>Congratulations</v>
       </c>
       <c r="G85" t="str">
-        <v>2:48</v>
+        <v>3:21</v>
       </c>
       <c r="H85" t="str">
-        <v>AZ</v>
+        <v>Jacob Ungerleider</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/az/35299</v>
+        <v>https://music.apple.com/us/artist/jacob-ungerleider/1460845591</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/surprise/1894873352</v>
+        <v>https://music.apple.com/us/album/letters-of-your-name/1892919737</v>
       </c>
       <c r="L85" t="str">
-        <v>Surprise - AZ</v>
+        <v>Letters of Your Name - Jacob Ungerleider</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Better Days</v>
+        <v>Seratonin</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/better-days/6763394083</v>
+        <v>https://music.apple.com/us/song/seratonin/6763447428</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-15</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Better Days - Single</v>
+        <v>Seratonin - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>3:22</v>
+        <v>1:55</v>
       </c>
       <c r="H86" t="str">
-        <v>Naomi Sharon</v>
+        <v>James Hype</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
+        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/better-days/1895293758</v>
+        <v>https://music.apple.com/us/album/seratonin/1895320367</v>
       </c>
       <c r="L86" t="str">
-        <v>Better Days - Naomi Sharon</v>
+        <v>Seratonin - James Hype</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Where Have All The Good Men Gone?</v>
+        <v>A Digital Touch</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/where-have-all-the-good-men-gone/6765484424</v>
+        <v>https://music.apple.com/us/song/a-digital-touch/6765592539</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-15</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Where Have All The Good Men Gone? - EP</v>
+        <v>A Digital Touch - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>3:14</v>
+        <v>2:53</v>
       </c>
       <c r="H87" t="str">
-        <v>Debbii Dawson</v>
+        <v>Evening Elephants</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
+        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/where-have-all-the-good-men-gone/1895967802</v>
+        <v>https://music.apple.com/us/album/a-digital-touch/1896003252</v>
       </c>
       <c r="L87" t="str">
-        <v>Where Have All The Good Men Gone? - Debbii Dawson</v>
+        <v>A Digital Touch - Evening Elephants</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>No Pressure</v>
+        <v>Dead Man's Dog</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/no-pressure/6763448750</v>
+        <v>https://music.apple.com/us/song/dead-mans-dog/6763447424</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-15</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>No Pressure - Single</v>
+        <v>Aiming Torches At The Sun - EP</v>
       </c>
       <c r="G88" t="str">
-        <v>3:09</v>
+        <v>4:33</v>
       </c>
       <c r="H88" t="str">
-        <v>JYT</v>
+        <v>Dermot Henry</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
+        <v>https://music.apple.com/us/artist/dermot-henry/1704074611</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/no-pressure/1895321101</v>
+        <v>https://music.apple.com/us/album/dead-mans-dog/1895320369</v>
       </c>
       <c r="L88" t="str">
-        <v>No Pressure - JYT</v>
+        <v>Dead Man's Dog - Dermot Henry</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>What's the Point!</v>
+        <v>Fault of God</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/whats-the-point/1886811061</v>
+        <v>https://music.apple.com/us/song/fault-of-god/1887702403</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-15</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Night at the Opera - EP</v>
+        <v>Active Child</v>
       </c>
       <c r="G89" t="str">
-        <v>2:43</v>
+        <v>4:13</v>
       </c>
       <c r="H89" t="str">
-        <v>Emei</v>
+        <v>Active Child</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/emei/1583968554</v>
+        <v>https://music.apple.com/us/artist/active-child/355288617</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/whats-the-point/1886811055</v>
+        <v>https://music.apple.com/us/album/fault-of-god/1887701924</v>
       </c>
       <c r="L89" t="str">
-        <v>What's the Point! - Emei</v>
+        <v>Fault of God - Active Child</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Pachamama</v>
+        <v>Zone (feat. Poppy Baskcomb)</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/pachamama/1893815453</v>
+        <v>https://music.apple.com/us/song/zone-feat-poppy-baskcomb/6763982867</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-15</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Así Es La Vida</v>
+        <v>Zone (feat. Poppy Baskcomb) - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>3:20</v>
+        <v>2:56</v>
       </c>
       <c r="H90" t="str">
-        <v>Codiciado</v>
+        <v>MK</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
+        <v>https://music.apple.com/us/artist/mk/63097617</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/pachamama/1893815448</v>
+        <v>https://music.apple.com/us/album/zone-feat-poppy-baskcomb/1895585800</v>
       </c>
       <c r="L90" t="str">
-        <v>Pachamama - Codiciado</v>
+        <v>Zone (feat. Poppy Baskcomb) - MK</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Multiplied</v>
+        <v>Word Vomit</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/multiplied/1889977459</v>
+        <v>https://music.apple.com/us/song/word-vomit/1887315297</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-15</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Multiplied - Single</v>
+        <v>Word Vomit - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>3:02</v>
+        <v>2:46</v>
       </c>
       <c r="H91" t="str">
-        <v>Luna Li</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/luna-li/1242663809</v>
+        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/multiplied/1889977458</v>
+        <v>https://music.apple.com/us/album/word-vomit/1887315294</v>
       </c>
       <c r="L91" t="str">
-        <v>Multiplied - Luna Li</v>
+        <v>Word Vomit - Baby Queen</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Six String</v>
+        <v>Evil in this House</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/six-string/1892171728</v>
+        <v>https://music.apple.com/us/song/evil-in-this-house/1892398371</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-15</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Six String - Single</v>
+        <v>Necropolitan</v>
       </c>
       <c r="G92" t="str">
-        <v>3:11</v>
+        <v>4:21</v>
       </c>
       <c r="H92" t="str">
-        <v>Lila Dupont</v>
+        <v>Green Lung</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/lila-dupont/1508792561</v>
+        <v>https://music.apple.com/us/artist/green-lung/1244071662</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/six-string/1892171725</v>
+        <v>https://music.apple.com/us/album/evil-in-this-house/1892398281</v>
       </c>
       <c r="L92" t="str">
-        <v>Six String - Lila Dupont</v>
+        <v>Evil in this House - Green Lung</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Take Heart</v>
+        <v>Heaven on High</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/take-heart/1877993013</v>
+        <v>https://music.apple.com/us/song/heaven-on-high/1881724153</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-15</v>
@@ -3909,600 +3909,30 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Harbour</v>
+        <v>A Pale White Dot</v>
       </c>
       <c r="G93" t="str">
-        <v>4:07</v>
+        <v>4:19</v>
       </c>
       <c r="H93" t="str">
-        <v>Jon Bryant</v>
+        <v>Periphery</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/jon-bryant/341294359</v>
+        <v>https://music.apple.com/us/artist/periphery/187683869</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/take-heart/1877992810</v>
+        <v>https://music.apple.com/us/album/heaven-on-high/1881724003</v>
       </c>
       <c r="L93" t="str">
-        <v>Take Heart - Jon Bryant</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="str">
-        <v>Clarion</v>
-      </c>
-      <c r="B94" t="str">
-        <v/>
-      </c>
-      <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/clarion/1887589702</v>
-      </c>
-      <c r="D94" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E94" t="str">
-        <v/>
-      </c>
-      <c r="F94" t="str">
-        <v>You Are Spring!</v>
-      </c>
-      <c r="G94" t="str">
-        <v>3:23</v>
-      </c>
-      <c r="H94" t="str">
-        <v>Tasha</v>
-      </c>
-      <c r="I94" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
-      </c>
-      <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/clarion/1887589690</v>
-      </c>
-      <c r="L94" t="str">
-        <v>Clarion - Tasha</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="str">
-        <v>Stepping Stone</v>
-      </c>
-      <c r="B95" t="str">
-        <v/>
-      </c>
-      <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/stepping-stone/1889387056</v>
-      </c>
-      <c r="D95" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E95" t="str">
-        <v/>
-      </c>
-      <c r="F95" t="str">
-        <v>Beams - Single</v>
-      </c>
-      <c r="G95" t="str">
-        <v>2:49</v>
-      </c>
-      <c r="H95" t="str">
-        <v>DERBY</v>
-      </c>
-      <c r="I95" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/derby/1772719795</v>
-      </c>
-      <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/stepping-stone/1889387054</v>
-      </c>
-      <c r="L95" t="str">
-        <v>Stepping Stone - DERBY</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="str">
-        <v>confessions part iii</v>
-      </c>
-      <c r="B96" t="str">
-        <v/>
-      </c>
-      <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/confessions-part-iii/1892181989</v>
-      </c>
-      <c r="D96" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E96" t="str">
-        <v/>
-      </c>
-      <c r="F96" t="str">
-        <v>autogratis</v>
-      </c>
-      <c r="G96" t="str">
-        <v>2:01</v>
-      </c>
-      <c r="H96" t="str">
-        <v>Chanpan</v>
-      </c>
-      <c r="I96" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/chanpan/1704417748</v>
-      </c>
-      <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/confessions-part-iii/1892181981</v>
-      </c>
-      <c r="L96" t="str">
-        <v>confessions part iii - Chanpan</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="str">
-        <v>cherry garcia</v>
-      </c>
-      <c r="B97" t="str">
-        <v/>
-      </c>
-      <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/cherry-garcia/1885000655</v>
-      </c>
-      <c r="D97" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E97" t="str">
-        <v/>
-      </c>
-      <c r="F97" t="str">
-        <v>cherry garcia - Single</v>
-      </c>
-      <c r="G97" t="str">
-        <v>2:30</v>
-      </c>
-      <c r="H97" t="str">
-        <v>supermodel*</v>
-      </c>
-      <c r="I97" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/supermodel/1817515489</v>
-      </c>
-      <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/cherry-garcia/1885000654</v>
-      </c>
-      <c r="L97" t="str">
-        <v>cherry garcia - supermodel*</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="str">
-        <v>Disco Cherry</v>
-      </c>
-      <c r="B98" t="str">
-        <v/>
-      </c>
-      <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/disco-cherry/1890195881</v>
-      </c>
-      <c r="D98" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E98" t="str">
-        <v/>
-      </c>
-      <c r="F98" t="str">
-        <v>Disco Cherry - Single</v>
-      </c>
-      <c r="G98" t="str">
-        <v>3:20</v>
-      </c>
-      <c r="H98" t="str">
-        <v>Purple Disco Machine</v>
-      </c>
-      <c r="I98" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/purple-disco-machine/357397685</v>
-      </c>
-      <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/disco-cherry/1890195880</v>
-      </c>
-      <c r="L98" t="str">
-        <v>Disco Cherry - Purple Disco Machine</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="str">
-        <v>Tal Vez</v>
-      </c>
-      <c r="B99" t="str">
-        <v/>
-      </c>
-      <c r="C99" t="str">
-        <v>https://music.apple.com/us/song/tal-vez/1894892261</v>
-      </c>
-      <c r="D99" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E99" t="str">
-        <v/>
-      </c>
-      <c r="F99" t="str">
-        <v>El Amante</v>
-      </c>
-      <c r="G99" t="str">
-        <v>2:14</v>
-      </c>
-      <c r="H99" t="str">
-        <v>Dariel Amant</v>
-      </c>
-      <c r="I99" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J99" t="str">
-        <v>https://music.apple.com/us/artist/dariel-amant/1595935945</v>
-      </c>
-      <c r="K99" t="str">
-        <v>https://music.apple.com/us/album/tal-vez/1894892257</v>
-      </c>
-      <c r="L99" t="str">
-        <v>Tal Vez - Dariel Amant</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
-        <v>The Voyager</v>
-      </c>
-      <c r="B100" t="str">
-        <v/>
-      </c>
-      <c r="C100" t="str">
-        <v>https://music.apple.com/us/song/the-voyager/6764897214</v>
-      </c>
-      <c r="D100" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E100" t="str">
-        <v/>
-      </c>
-      <c r="F100" t="str">
-        <v>The Voyager - Single</v>
-      </c>
-      <c r="G100" t="str">
-        <v>4:37</v>
-      </c>
-      <c r="H100" t="str">
-        <v>Chance Peña</v>
-      </c>
-      <c r="I100" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J100" t="str">
-        <v>https://music.apple.com/us/artist/chance-pe%C3%B1a/1042737143</v>
-      </c>
-      <c r="K100" t="str">
-        <v>https://music.apple.com/us/album/the-voyager/1895954206</v>
-      </c>
-      <c r="L100" t="str">
-        <v>The Voyager - Chance Peña</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v>Pictures of You</v>
-      </c>
-      <c r="B101" t="str">
-        <v/>
-      </c>
-      <c r="C101" t="str">
-        <v>https://music.apple.com/us/song/pictures-of-you/6764176261</v>
-      </c>
-      <c r="D101" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E101" t="str">
-        <v/>
-      </c>
-      <c r="F101" t="str">
-        <v>Pictures of You</v>
-      </c>
-      <c r="G101" t="str">
-        <v>3:34</v>
-      </c>
-      <c r="H101" t="str">
-        <v>Buffalo Traffic Jam</v>
-      </c>
-      <c r="I101" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J101" t="str">
-        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
-      </c>
-      <c r="K101" t="str">
-        <v>https://music.apple.com/us/album/pictures-of-you/1895672454</v>
-      </c>
-      <c r="L101" t="str">
-        <v>Pictures of You - Buffalo Traffic Jam</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>Buy What U Want</v>
-      </c>
-      <c r="B102" t="str">
-        <v/>
-      </c>
-      <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/buy-what-u-want/6763137223</v>
-      </c>
-      <c r="D102" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E102" t="str">
-        <v/>
-      </c>
-      <c r="F102" t="str">
-        <v>Road To Osshland: The Series</v>
-      </c>
-      <c r="G102" t="str">
-        <v>3:47</v>
-      </c>
-      <c r="H102" t="str">
-        <v>Black Fortune</v>
-      </c>
-      <c r="I102" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/black-fortune/557044567</v>
-      </c>
-      <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/buy-what-u-want/1895178841</v>
-      </c>
-      <c r="L102" t="str">
-        <v>Buy What U Want - Black Fortune</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>MOOD BRAZIL</v>
-      </c>
-      <c r="B103" t="str">
-        <v/>
-      </c>
-      <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/mood-brazil/6766985126</v>
-      </c>
-      <c r="D103" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E103" t="str">
-        <v/>
-      </c>
-      <c r="F103" t="str">
-        <v>MOOD BRAZIL - Single</v>
-      </c>
-      <c r="G103" t="str">
-        <v>2:29</v>
-      </c>
-      <c r="H103" t="str">
-        <v>Lil Naay</v>
-      </c>
-      <c r="I103" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/lil-naay/1513690516</v>
-      </c>
-      <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/mood-brazil/6766984734</v>
-      </c>
-      <c r="L103" t="str">
-        <v>MOOD BRAZIL - Lil Naay</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>high school sweetheart</v>
-      </c>
-      <c r="B104" t="str">
-        <v/>
-      </c>
-      <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/high-school-sweetheart/6763491151</v>
-      </c>
-      <c r="D104" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E104" t="str">
-        <v/>
-      </c>
-      <c r="F104" t="str">
-        <v>ashley cooke</v>
-      </c>
-      <c r="G104" t="str">
-        <v>3:11</v>
-      </c>
-      <c r="H104" t="str">
-        <v>Ashley Cooke</v>
-      </c>
-      <c r="I104" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
-      </c>
-      <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/high-school-sweetheart/1895339553</v>
-      </c>
-      <c r="L104" t="str">
-        <v>high school sweetheart - Ashley Cooke</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v>Vibe Responsibly (feat. Isaiah Rashad)</v>
-      </c>
-      <c r="B105" t="str">
-        <v/>
-      </c>
-      <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/vibe-responsibly-feat-isaiah-rashad/6766279282</v>
-      </c>
-      <c r="D105" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E105" t="str">
-        <v/>
-      </c>
-      <c r="F105" t="str">
-        <v>Vibe Responsibly (feat. Isaiah Rashad) - Single</v>
-      </c>
-      <c r="G105" t="str">
-        <v>2:55</v>
-      </c>
-      <c r="H105" t="str">
-        <v>Ray Vaughn</v>
-      </c>
-      <c r="I105" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
-      </c>
-      <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/vibe-responsibly-feat-isaiah-rashad/1896264288</v>
-      </c>
-      <c r="L105" t="str">
-        <v>Vibe Responsibly (feat. Isaiah Rashad) - Ray Vaughn</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v>big plans</v>
-      </c>
-      <c r="B106" t="str">
-        <v/>
-      </c>
-      <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/big-plans/1893684291</v>
-      </c>
-      <c r="D106" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E106" t="str">
-        <v/>
-      </c>
-      <c r="F106" t="str">
-        <v>counting horses</v>
-      </c>
-      <c r="G106" t="str">
-        <v>3:14</v>
-      </c>
-      <c r="H106" t="str">
-        <v>Tom Siletto</v>
-      </c>
-      <c r="I106" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
-      </c>
-      <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/big-plans/1893684101</v>
-      </c>
-      <c r="L106" t="str">
-        <v>big plans - Tom Siletto</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>Running</v>
-      </c>
-      <c r="B107" t="str">
-        <v/>
-      </c>
-      <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/running/6764878724</v>
-      </c>
-      <c r="D107" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E107" t="str">
-        <v/>
-      </c>
-      <c r="F107" t="str">
-        <v>Running - Single</v>
-      </c>
-      <c r="G107" t="str">
-        <v>2:38</v>
-      </c>
-      <c r="H107" t="str">
-        <v>Kameron Marlowe</v>
-      </c>
-      <c r="I107" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/kameron-marlowe/1467288596</v>
-      </c>
-      <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/running/1895947036</v>
-      </c>
-      <c r="L107" t="str">
-        <v>Running - Kameron Marlowe</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="str">
-        <v>FA-TAL!</v>
-      </c>
-      <c r="B108" t="str">
-        <v/>
-      </c>
-      <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/fa-tal/6764684234</v>
-      </c>
-      <c r="D108" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E108" t="str">
-        <v/>
-      </c>
-      <c r="F108" t="str">
-        <v>FA-TAL! - Single</v>
-      </c>
-      <c r="G108" t="str">
-        <v>2:46</v>
-      </c>
-      <c r="H108" t="str">
-        <v>ROBI</v>
-      </c>
-      <c r="I108" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/robi/1458047972</v>
-      </c>
-      <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/fa-tal/1895877867</v>
-      </c>
-      <c r="L108" t="str">
-        <v>FA-TAL! - ROBI</v>
+        <v>Heaven on High - Periphery</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L93"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week03/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/hit-the-wall/6766750846</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/ran-to-atlanta/6769568597</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/hoe-phase/6769556949</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/im-spent/6769551476</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/abracadabra-apple-music-live/6768201780</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/falling-out-of-love/1891161448</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/dai-dai/6768469976</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/tu-recuerdo/6763660843</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/traitor-roles-reversed/6767665959</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/dirty-rosie/6767044374</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/2-hard-4-the-radio/6769568610</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/cheetah-print/6769557055</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/wnba/6769551471</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/shadow-of-a-man-apple-music-live/6768201925</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/epa/6768420253</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/im-your-girl-right/6766440186</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/fu%C3%ABgo/6767661766</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/jajaja/6766341319</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/find-god-feat-dominic-fike/1894315529</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/fool-me-once-feat-leon-thomas/1891467239</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/shabang/6769568598</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/road-trips/6769557053</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/fortworth/6769551482</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/repeat-it/6764277864</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/fool-proof/1892466004</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/crisco/6763369506</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/absolution/1884987651</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/jesus-is-alive/6767694896</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/something-to-lose/6766964605</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/too-busy-missing-you/6766604915</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/f-stop-blues-4-track/1883173173</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/pa-lo-bonito/1886496944</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/lonely/6768757857</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/lockup/1894298102</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/young/6767698952</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/parachute/6764119241</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/little-things/6766351153</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/fish-hunt-golf-drink/6766651884</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/pageant-stage/6764125889</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/firestorm/1868827004</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/girl-next-door/6768077610</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/big-dog/1887197046</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/idea-of-love-a-colors-show/6767667046</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/heavy-serenade/1892154309</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/ddok-ddok-ddok/6764203482</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/shut-it-down/6763631128</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/together-feat-nikki-nair-jessy-lanza-prentiss/6763207821</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/cant-miss-you/1886810999</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/razorblades-and-runways/1888004809</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/massacre/1892127745</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/better-that-way/6766273199</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/apollo/6765602431</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/infinity-123/6763447312</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/aint-over-me-yet/6767283811</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/where-did-you-go/1877958504</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/i-love-you/6766999950</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/housekeeping/6766290834</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/surprise-surprise/6764842119</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/dog/1885967384</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/i-never-see-her/6764149225</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/no-god/1891187414</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/burden/6767688180</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/chico-raro/6767713536</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/whats-done-is-done/6763088629</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/round-and-round/1885665987</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/aint-that-deep/1882831449</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/emily/1893405442</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/hold/6767296480</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/flying-monkey/1894351228</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/anything-goes/1891118972</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/we-are/1894252873</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/its-for-the-kids/1867327679</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/pure-ecstasy/6762228978</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/something-wicked/6766252959</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/feel-the-funk/6763294007</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/everglades-remix/6767719584</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/walk/1892180098</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/volver-a-ti/6766258204</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/bahamas/6764695848</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/same-old-song/6762860685</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/gentle/6762828356</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/letters-of-your-name/1892919741</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/seratonin/6763447428</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/a-digital-touch/6765592539</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/dead-mans-dog/6763447424</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/fault-of-god/1887702403</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/zone-feat-poppy-baskcomb/6763982867</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/word-vomit/1887315297</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/evil-in-this-house/1892398371</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/heaven-on-high/1881724153</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E93" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week03/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/hit-the-wall/6766750846</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/ran-to-atlanta/6769568597</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/hoe-phase/6769556949</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/im-spent/6769551476</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/abracadabra-apple-music-live/6768201780</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/falling-out-of-love/1891161448</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/dai-dai/6768469976</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/tu-recuerdo/6763660843</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/traitor-roles-reversed/6767665959</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/dirty-rosie/6767044374</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/2-hard-4-the-radio/6769568610</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/cheetah-print/6769557055</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/wnba/6769551471</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/shadow-of-a-man-apple-music-live/6768201925</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/epa/6768420253</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/im-your-girl-right/6766440186</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/fu%C3%ABgo/6767661766</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/jajaja/6766341319</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/find-god-feat-dominic-fike/1894315529</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/fool-me-once-feat-leon-thomas/1891467239</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/shabang/6769568598</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/road-trips/6769557053</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/fortworth/6769551482</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/repeat-it/6764277864</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/fool-proof/1892466004</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/crisco/6763369506</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/absolution/1884987651</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/jesus-is-alive/6767694896</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/something-to-lose/6766964605</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/too-busy-missing-you/6766604915</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/f-stop-blues-4-track/1883173173</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/pa-lo-bonito/1886496944</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/lonely/6768757857</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/lockup/1894298102</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/young/6767698952</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/parachute/6764119241</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/little-things/6766351153</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/fish-hunt-golf-drink/6766651884</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/pageant-stage/6764125889</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/firestorm/1868827004</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/girl-next-door/6768077610</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/big-dog/1887197046</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/idea-of-love-a-colors-show/6767667046</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/heavy-serenade/1892154309</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/ddok-ddok-ddok/6764203482</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/shut-it-down/6763631128</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/together-feat-nikki-nair-jessy-lanza-prentiss/6763207821</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/cant-miss-you/1886810999</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/razorblades-and-runways/1888004809</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/massacre/1892127745</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/better-that-way/6766273199</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/apollo/6765602431</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/infinity-123/6763447312</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/aint-over-me-yet/6767283811</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/where-did-you-go/1877958504</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/i-love-you/6766999950</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/housekeeping/6766290834</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/surprise-surprise/6764842119</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/dog/1885967384</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/i-never-see-her/6764149225</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/no-god/1891187414</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/burden/6767688180</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/chico-raro/6767713536</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/whats-done-is-done/6763088629</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/round-and-round/1885665987</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/aint-that-deep/1882831449</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/emily/1893405442</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/hold/6767296480</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/flying-monkey/1894351228</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/anything-goes/1891118972</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/we-are/1894252873</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/its-for-the-kids/1867327679</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/pure-ecstasy/6762228978</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/something-wicked/6766252959</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/feel-the-funk/6763294007</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/everglades-remix/6767719584</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/walk/1892180098</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/volver-a-ti/6766258204</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/bahamas/6764695848</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/same-old-song/6762860685</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/gentle/6762828356</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/letters-of-your-name/1892919741</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/seratonin/6763447428</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/a-digital-touch/6765592539</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/dead-mans-dog/6763447424</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/fault-of-god/1887702403</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/zone-feat-poppy-baskcomb/6763982867</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/word-vomit/1887315297</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/evil-in-this-house/1892398371</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/heaven-on-high/1881724153</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E93" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week03/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/hit-the-wall/6766750846</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/ran-to-atlanta/6769568597</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/hoe-phase/6769556949</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/im-spent/6769551476</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/abracadabra-apple-music-live/6768201780</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/falling-out-of-love/1891161448</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/dai-dai/6768469976</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/tu-recuerdo/6763660843</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/traitor-roles-reversed/6767665959</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/dirty-rosie/6767044374</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/2-hard-4-the-radio/6769568610</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/cheetah-print/6769557055</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/wnba/6769551471</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/shadow-of-a-man-apple-music-live/6768201925</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/epa/6768420253</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/im-your-girl-right/6766440186</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/fu%C3%ABgo/6767661766</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/jajaja/6766341319</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/find-god-feat-dominic-fike/1894315529</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/fool-me-once-feat-leon-thomas/1891467239</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/shabang/6769568598</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/road-trips/6769557053</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/fortworth/6769551482</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/repeat-it/6764277864</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/fool-proof/1892466004</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/crisco/6763369506</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/absolution/1884987651</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/jesus-is-alive/6767694896</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/something-to-lose/6766964605</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/too-busy-missing-you/6766604915</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/f-stop-blues-4-track/1883173173</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/pa-lo-bonito/1886496944</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/lonely/6768757857</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/lockup/1894298102</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/young/6767698952</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/parachute/6764119241</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/little-things/6766351153</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/fish-hunt-golf-drink/6766651884</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/pageant-stage/6764125889</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/firestorm/1868827004</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/girl-next-door/6768077610</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/big-dog/1887197046</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/idea-of-love-a-colors-show/6767667046</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/heavy-serenade/1892154309</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/ddok-ddok-ddok/6764203482</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/shut-it-down/6763631128</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/together-feat-nikki-nair-jessy-lanza-prentiss/6763207821</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/cant-miss-you/1886810999</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/razorblades-and-runways/1888004809</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/massacre/1892127745</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/better-that-way/6766273199</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/apollo/6765602431</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/infinity-123/6763447312</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/aint-over-me-yet/6767283811</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/where-did-you-go/1877958504</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/i-love-you/6766999950</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/housekeeping/6766290834</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/surprise-surprise/6764842119</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/dog/1885967384</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/i-never-see-her/6764149225</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/no-god/1891187414</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/burden/6767688180</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/chico-raro/6767713536</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/whats-done-is-done/6763088629</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/round-and-round/1885665987</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/aint-that-deep/1882831449</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/emily/1893405442</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/hold/6767296480</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/flying-monkey/1894351228</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/anything-goes/1891118972</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/we-are/1894252873</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/its-for-the-kids/1867327679</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/pure-ecstasy/6762228978</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/something-wicked/6766252959</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/feel-the-funk/6763294007</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/everglades-remix/6767719584</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/walk/1892180098</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/volver-a-ti/6766258204</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/bahamas/6764695848</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/same-old-song/6762860685</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/gentle/6762828356</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/letters-of-your-name/1892919741</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/seratonin/6763447428</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/a-digital-touch/6765592539</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/dead-mans-dog/6763447424</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/fault-of-god/1887702403</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/zone-feat-poppy-baskcomb/6763982867</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/word-vomit/1887315297</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/evil-in-this-house/1892398371</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/heaven-on-high/1881724153</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E93" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:L94"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Hit the Wall</v>
+        <v>Ego</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/hit-the-wall/6766750846</v>
+        <v>https://music.apple.com/us/song/ego/6769207667</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-18</v>
@@ -451,36 +451,36 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>Daughter from Hell</v>
+        <v>Ego - Single</v>
       </c>
       <c r="G2" t="str">
-        <v>3:14</v>
+        <v>2:53</v>
       </c>
       <c r="H2" t="str">
-        <v>Gracie Abrams</v>
+        <v>The Warning</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/gracie-abrams/1450554836</v>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/hit-the-wall/6766750836</v>
+        <v>https://music.apple.com/us/album/ego/6769207665</v>
       </c>
       <c r="L2" t="str">
-        <v>Hit the Wall - Gracie Abrams</v>
+        <v>Ego - The Warning</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Ran To Atlanta</v>
+        <v>Hit the Wall</v>
       </c>
       <c r="B3" t="str">
         <v/>
       </c>
       <c r="C3" t="str">
-        <v>https://music.apple.com/us/song/ran-to-atlanta/6769568597</v>
+        <v>https://music.apple.com/us/song/hit-the-wall/6766750846</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-18</v>
@@ -489,36 +489,36 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>ICEMAN</v>
+        <v>Daughter from Hell</v>
       </c>
       <c r="G3" t="str">
-        <v>4:07</v>
+        <v>3:14</v>
       </c>
       <c r="H3" t="str">
-        <v>Drake</v>
+        <v>Gracie Abrams</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
-        <v>https://music.apple.com/us/artist/drake/271256</v>
+        <v>https://music.apple.com/us/artist/gracie-abrams/1450554836</v>
       </c>
       <c r="K3" t="str">
-        <v>https://music.apple.com/us/album/ran-to-atlanta/6769568449</v>
+        <v>https://music.apple.com/us/album/hit-the-wall/6766750836</v>
       </c>
       <c r="L3" t="str">
-        <v>Ran To Atlanta - Drake</v>
+        <v>Hit the Wall - Gracie Abrams</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Hoe Phase</v>
+        <v>Ran To Atlanta</v>
       </c>
       <c r="B4" t="str">
         <v/>
       </c>
       <c r="C4" t="str">
-        <v>https://music.apple.com/us/song/hoe-phase/6769556949</v>
+        <v>https://music.apple.com/us/song/ran-to-atlanta/6769568597</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-18</v>
@@ -527,10 +527,10 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>MAID OF HONOUR</v>
+        <v>ICEMAN</v>
       </c>
       <c r="G4" t="str">
-        <v>3:23</v>
+        <v>4:07</v>
       </c>
       <c r="H4" t="str">
         <v>Drake</v>
@@ -542,21 +542,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K4" t="str">
-        <v>https://music.apple.com/us/album/hoe-phase/6769556940</v>
+        <v>https://music.apple.com/us/album/ran-to-atlanta/6769568449</v>
       </c>
       <c r="L4" t="str">
-        <v>Hoe Phase - Drake</v>
+        <v>Ran To Atlanta - Drake</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>I’m Spent</v>
+        <v>Hoe Phase</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>https://music.apple.com/us/song/im-spent/6769551476</v>
+        <v>https://music.apple.com/us/song/hoe-phase/6769556949</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-18</v>
@@ -565,10 +565,10 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>HABIBTI</v>
+        <v>MAID OF HONOUR</v>
       </c>
       <c r="G5" t="str">
-        <v>2:24</v>
+        <v>3:23</v>
       </c>
       <c r="H5" t="str">
         <v>Drake</v>
@@ -580,21 +580,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K5" t="str">
-        <v>https://music.apple.com/us/album/im-spent/6769551464</v>
+        <v>https://music.apple.com/us/album/hoe-phase/6769556940</v>
       </c>
       <c r="L5" t="str">
-        <v>I’m Spent - Drake</v>
+        <v>Hoe Phase - Drake</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Abracadabra (Apple Music Live)</v>
+        <v>I’m Spent</v>
       </c>
       <c r="B6" t="str">
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>https://music.apple.com/us/song/abracadabra-apple-music-live/6768201780</v>
+        <v>https://music.apple.com/us/song/im-spent/6769551476</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-18</v>
@@ -603,36 +603,36 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>Apple Music Live: MAYHEM Requiem</v>
+        <v>HABIBTI</v>
       </c>
       <c r="G6" t="str">
-        <v>4:04</v>
+        <v>2:24</v>
       </c>
       <c r="H6" t="str">
-        <v>Lady Gaga</v>
+        <v>Drake</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
-        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K6" t="str">
-        <v>https://music.apple.com/us/album/abracadabra-apple-music-live/6768201775</v>
+        <v>https://music.apple.com/us/album/im-spent/6769551464</v>
       </c>
       <c r="L6" t="str">
-        <v>Abracadabra (Apple Music Live) - Lady Gaga</v>
+        <v>I’m Spent - Drake</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Falling out of Love</v>
+        <v>Abracadabra (Apple Music Live)</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>https://music.apple.com/us/song/falling-out-of-love/1891161448</v>
+        <v>https://music.apple.com/us/song/abracadabra-apple-music-live/6768201780</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-18</v>
@@ -641,36 +641,36 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>Reality Awaits</v>
+        <v>Apple Music Live: MAYHEM Requiem</v>
       </c>
       <c r="G7" t="str">
-        <v>6:21</v>
+        <v>4:04</v>
       </c>
       <c r="H7" t="str">
-        <v>The Strokes</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
-        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
+        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
       </c>
       <c r="K7" t="str">
-        <v>https://music.apple.com/us/album/falling-out-of-love/1891161441</v>
+        <v>https://music.apple.com/us/album/abracadabra-apple-music-live/6768201775</v>
       </c>
       <c r="L7" t="str">
-        <v>Falling out of Love - The Strokes</v>
+        <v>Abracadabra (Apple Music Live) - Lady Gaga</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Dai Dai</v>
+        <v>Falling out of Love</v>
       </c>
       <c r="B8" t="str">
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>https://music.apple.com/us/song/dai-dai/6768469976</v>
+        <v>https://music.apple.com/us/song/falling-out-of-love/1891161448</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-18</v>
@@ -679,36 +679,36 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>Dai Dai - Single</v>
+        <v>Reality Awaits</v>
       </c>
       <c r="G8" t="str">
-        <v>3:43</v>
+        <v>6:21</v>
       </c>
       <c r="H8" t="str">
-        <v>Shakira</v>
+        <v>The Strokes</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
-        <v>https://music.apple.com/us/artist/shakira/889327</v>
+        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
       </c>
       <c r="K8" t="str">
-        <v>https://music.apple.com/us/album/dai-dai/6768469975</v>
+        <v>https://music.apple.com/us/album/falling-out-of-love/1891161441</v>
       </c>
       <c r="L8" t="str">
-        <v>Dai Dai - Shakira</v>
+        <v>Falling out of Love - The Strokes</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Tu recuerdo</v>
+        <v>Dai Dai</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>https://music.apple.com/us/song/tu-recuerdo/6763660843</v>
+        <v>https://music.apple.com/us/song/dai-dai/6768469976</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-18</v>
@@ -717,36 +717,36 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>Loco X Volver</v>
+        <v>Dai Dai - Single</v>
       </c>
       <c r="G9" t="str">
-        <v>3:55</v>
+        <v>3:43</v>
       </c>
       <c r="H9" t="str">
-        <v>Maluma</v>
+        <v>Shakira</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/shakira/889327</v>
       </c>
       <c r="K9" t="str">
-        <v>https://music.apple.com/us/album/tu-recuerdo/1895423065</v>
+        <v>https://music.apple.com/us/album/dai-dai/6768469975</v>
       </c>
       <c r="L9" t="str">
-        <v>Tu recuerdo - Maluma</v>
+        <v>Dai Dai - Shakira</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Traitor (Roles Reversed)</v>
+        <v>Tu recuerdo</v>
       </c>
       <c r="B10" t="str">
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>https://music.apple.com/us/song/traitor-roles-reversed/6767665959</v>
+        <v>https://music.apple.com/us/song/tu-recuerdo/6763660843</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-18</v>
@@ -755,36 +755,36 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>Cloud 9</v>
+        <v>Loco X Volver</v>
       </c>
       <c r="G10" t="str">
-        <v>3:27</v>
+        <v>3:55</v>
       </c>
       <c r="H10" t="str">
-        <v>Megan Moroney</v>
+        <v>Maluma</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K10" t="str">
-        <v>https://music.apple.com/us/album/traitor-roles-reversed/6767665713</v>
+        <v>https://music.apple.com/us/album/tu-recuerdo/1895423065</v>
       </c>
       <c r="L10" t="str">
-        <v>Traitor (Roles Reversed) - Megan Moroney</v>
+        <v>Tu recuerdo - Maluma</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Dirty Rosie</v>
+        <v>Traitor (Roles Reversed)</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>https://music.apple.com/us/song/dirty-rosie/6767044374</v>
+        <v>https://music.apple.com/us/song/traitor-roles-reversed/6767665959</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-18</v>
@@ -793,36 +793,36 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>Little Miss Twain</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G11" t="str">
-        <v>2:46</v>
+        <v>3:27</v>
       </c>
       <c r="H11" t="str">
-        <v>Shania Twain</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
-        <v>https://music.apple.com/us/artist/shania-twain/129974</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K11" t="str">
-        <v>https://music.apple.com/us/album/dirty-rosie/1896356105</v>
+        <v>https://music.apple.com/us/album/traitor-roles-reversed/6767665713</v>
       </c>
       <c r="L11" t="str">
-        <v>Dirty Rosie - Shania Twain</v>
+        <v>Traitor (Roles Reversed) - Megan Moroney</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Like you mean it</v>
+        <v>Dirty Rosie</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
+        <v>https://music.apple.com/us/song/dirty-rosie/6767044374</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-18</v>
@@ -831,36 +831,36 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>When the lights turn on</v>
+        <v>Little Miss Twain</v>
       </c>
       <c r="G12" t="str">
-        <v>2:27</v>
+        <v>2:46</v>
       </c>
       <c r="H12" t="str">
-        <v>MICO</v>
+        <v>Shania Twain</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
-        <v>https://music.apple.com/us/artist/mico/1457367370</v>
+        <v>https://music.apple.com/us/artist/shania-twain/129974</v>
       </c>
       <c r="K12" t="str">
-        <v>https://music.apple.com/us/album/like-you-mean-it/6767024688</v>
+        <v>https://music.apple.com/us/album/dirty-rosie/1896356105</v>
       </c>
       <c r="L12" t="str">
-        <v>Like you mean it - MICO</v>
+        <v>Dirty Rosie - Shania Twain</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Hardy (feat. Clairo)</v>
+        <v>Like you mean it</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
+        <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-18</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>American Stories</v>
+        <v>When the lights turn on</v>
       </c>
       <c r="G13" t="str">
-        <v>3:53</v>
+        <v>2:27</v>
       </c>
       <c r="H13" t="str">
-        <v>Rostam</v>
+        <v>MICO</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/mico/1457367370</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/hardy-feat-clairo/1876952750</v>
+        <v>https://music.apple.com/us/album/like-you-mean-it/6767024688</v>
       </c>
       <c r="L13" t="str">
-        <v>Hardy (feat. Clairo) - Rostam</v>
+        <v>Like you mean it - MICO</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2 Hard 4 The Radio</v>
+        <v>Hardy (feat. Clairo)</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/2-hard-4-the-radio/6769568610</v>
+        <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-18</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>ICEMAN</v>
+        <v>American Stories</v>
       </c>
       <c r="G14" t="str">
-        <v>3:03</v>
+        <v>3:53</v>
       </c>
       <c r="H14" t="str">
-        <v>Drake</v>
+        <v>Rostam</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/drake/271256</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/2-hard-4-the-radio/6769568449</v>
+        <v>https://music.apple.com/us/album/hardy-feat-clairo/1876952750</v>
       </c>
       <c r="L14" t="str">
-        <v>2 Hard 4 The Radio - Drake</v>
+        <v>Hardy (feat. Clairo) - Rostam</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Cheetah Print</v>
+        <v>2 Hard 4 The Radio</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/cheetah-print/6769557055</v>
+        <v>https://music.apple.com/us/song/2-hard-4-the-radio/6769568610</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-18</v>
@@ -945,10 +945,10 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>MAID OF HONOUR</v>
+        <v>ICEMAN</v>
       </c>
       <c r="G15" t="str">
-        <v>3:22</v>
+        <v>3:03</v>
       </c>
       <c r="H15" t="str">
         <v>Drake</v>
@@ -960,21 +960,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/cheetah-print/6769556940</v>
+        <v>https://music.apple.com/us/album/2-hard-4-the-radio/6769568449</v>
       </c>
       <c r="L15" t="str">
-        <v>Cheetah Print - Drake</v>
+        <v>2 Hard 4 The Radio - Drake</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>WNBA</v>
+        <v>Cheetah Print</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/wnba/6769551471</v>
+        <v>https://music.apple.com/us/song/cheetah-print/6769557055</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-18</v>
@@ -983,10 +983,10 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>HABIBTI</v>
+        <v>MAID OF HONOUR</v>
       </c>
       <c r="G16" t="str">
-        <v>2:58</v>
+        <v>3:22</v>
       </c>
       <c r="H16" t="str">
         <v>Drake</v>
@@ -998,21 +998,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/wnba/6769551464</v>
+        <v>https://music.apple.com/us/album/cheetah-print/6769556940</v>
       </c>
       <c r="L16" t="str">
-        <v>WNBA - Drake</v>
+        <v>Cheetah Print - Drake</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Shadow Of A Man (Apple Music Live)</v>
+        <v>WNBA</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/shadow-of-a-man-apple-music-live/6768201925</v>
+        <v>https://music.apple.com/us/song/wnba/6769551471</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-18</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>Apple Music Live: MAYHEM Requiem</v>
+        <v>HABIBTI</v>
       </c>
       <c r="G17" t="str">
-        <v>3:36</v>
+        <v>2:58</v>
       </c>
       <c r="H17" t="str">
-        <v>Lady Gaga</v>
+        <v>Drake</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/shadow-of-a-man-apple-music-live/6768201775</v>
+        <v>https://music.apple.com/us/album/wnba/6769551464</v>
       </c>
       <c r="L17" t="str">
-        <v>Shadow Of A Man (Apple Music Live) - Lady Gaga</v>
+        <v>WNBA - Drake</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>EPA</v>
+        <v>Shadow Of A Man (Apple Music Live)</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/epa/6768420253</v>
+        <v>https://music.apple.com/us/song/shadow-of-a-man-apple-music-live/6768201925</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-18</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>EPA - Single</v>
+        <v>Apple Music Live: MAYHEM Requiem</v>
       </c>
       <c r="G18" t="str">
-        <v>3:22</v>
+        <v>3:36</v>
       </c>
       <c r="H18" t="str">
-        <v>Becky G</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
+        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/epa/6768420251</v>
+        <v>https://music.apple.com/us/album/shadow-of-a-man-apple-music-live/6768201775</v>
       </c>
       <c r="L18" t="str">
-        <v>EPA - Becky G</v>
+        <v>Shadow Of A Man (Apple Music Live) - Lady Gaga</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>I’m your girl right?</v>
+        <v>EPA</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/im-your-girl-right/6766440186</v>
+        <v>https://music.apple.com/us/song/epa/6768420253</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-18</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>ESTRUS</v>
+        <v>EPA - Single</v>
       </c>
       <c r="G19" t="str">
-        <v>2:49</v>
+        <v>3:22</v>
       </c>
       <c r="H19" t="str">
-        <v>Tove Lo</v>
+        <v>Becky G</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/tove-lo/570136838</v>
+        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/im-your-girl-right/6766440172</v>
+        <v>https://music.apple.com/us/album/epa/6768420251</v>
       </c>
       <c r="L19" t="str">
-        <v>I’m your girl right? - Tove Lo</v>
+        <v>EPA - Becky G</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>fuëgo</v>
+        <v>I’m your girl right?</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/fu%C3%ABgo/6767661766</v>
+        <v>https://music.apple.com/us/song/im-your-girl-right/6766440186</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-18</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>fuëgo - Single</v>
+        <v>ESTRUS</v>
       </c>
       <c r="G20" t="str">
-        <v>3:46</v>
+        <v>2:49</v>
       </c>
       <c r="H20" t="str">
-        <v>BNYX®</v>
+        <v>Tove Lo</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/bnyx/1438325287</v>
+        <v>https://music.apple.com/us/artist/tove-lo/570136838</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/fu%C3%ABgo/6767661604</v>
+        <v>https://music.apple.com/us/album/im-your-girl-right/6766440172</v>
       </c>
       <c r="L20" t="str">
-        <v>fuëgo - BNYX®</v>
+        <v>I’m your girl right? - Tove Lo</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>jajaja</v>
+        <v>fuëgo</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/jajaja/6766341319</v>
+        <v>https://music.apple.com/us/song/fu%C3%ABgo/6767661766</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-18</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>jajaja - Single</v>
+        <v>fuëgo - Single</v>
       </c>
       <c r="G21" t="str">
-        <v>2:45</v>
+        <v>3:46</v>
       </c>
       <c r="H21" t="str">
-        <v>Chino Pacas</v>
+        <v>BNYX®</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
+        <v>https://music.apple.com/us/artist/bnyx/1438325287</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/jajaja/6766341318</v>
+        <v>https://music.apple.com/us/album/fu%C3%ABgo/6767661604</v>
       </c>
       <c r="L21" t="str">
-        <v>jajaja - Chino Pacas</v>
+        <v>fuëgo - BNYX®</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>FIND GOD (feat. Dominic Fike)</v>
+        <v>jajaja</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/find-god-feat-dominic-fike/1894315529</v>
+        <v>https://music.apple.com/us/song/jajaja/6766341319</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-18</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>BULLDAWG</v>
+        <v>jajaja - Single</v>
       </c>
       <c r="G22" t="str">
-        <v>3:59</v>
+        <v>2:45</v>
       </c>
       <c r="H22" t="str">
-        <v>Kenny Mason</v>
+        <v>Chino Pacas</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/kenny-mason/79382206</v>
+        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/find-god-feat-dominic-fike/1894315301</v>
+        <v>https://music.apple.com/us/album/jajaja/6766341318</v>
       </c>
       <c r="L22" t="str">
-        <v>FIND GOD (feat. Dominic Fike) - Kenny Mason</v>
+        <v>jajaja - Chino Pacas</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>FOOL ME ONCE (feat. Leon Thomas)</v>
+        <v>FIND GOD (feat. Dominic Fike)</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/fool-me-once-feat-leon-thomas/1891467239</v>
+        <v>https://music.apple.com/us/song/find-god-feat-dominic-fike/1894315529</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-18</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>BELOVED: ACT II</v>
+        <v>BULLDAWG</v>
       </c>
       <c r="G23" t="str">
-        <v>3:18</v>
+        <v>3:59</v>
       </c>
       <c r="H23" t="str">
-        <v>GIVĒON</v>
+        <v>Kenny Mason</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/giv%C4%93on/1070668868</v>
+        <v>https://music.apple.com/us/artist/kenny-mason/79382206</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/fool-me-once-feat-leon-thomas/1891467233</v>
+        <v>https://music.apple.com/us/album/find-god-feat-dominic-fike/1894315301</v>
       </c>
       <c r="L23" t="str">
-        <v>FOOL ME ONCE (feat. Leon Thomas) - GIVĒON</v>
+        <v>FIND GOD (feat. Dominic Fike) - Kenny Mason</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Shabang</v>
+        <v>FOOL ME ONCE (feat. Leon Thomas)</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/shabang/6769568598</v>
+        <v>https://music.apple.com/us/song/fool-me-once-feat-leon-thomas/1891467239</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-18</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>ICEMAN</v>
+        <v>BELOVED: ACT II</v>
       </c>
       <c r="G24" t="str">
-        <v>3:08</v>
+        <v>3:18</v>
       </c>
       <c r="H24" t="str">
-        <v>Drake</v>
+        <v>GIVĒON</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/drake/271256</v>
+        <v>https://music.apple.com/us/artist/giv%C4%93on/1070668868</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/shabang/6769568449</v>
+        <v>https://music.apple.com/us/album/fool-me-once-feat-leon-thomas/1891467233</v>
       </c>
       <c r="L24" t="str">
-        <v>Shabang - Drake</v>
+        <v>FOOL ME ONCE (feat. Leon Thomas) - GIVĒON</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Road Trips</v>
+        <v>Shabang</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/road-trips/6769557053</v>
+        <v>https://music.apple.com/us/song/shabang/6769568598</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-18</v>
@@ -1325,10 +1325,10 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>MAID OF HONOUR</v>
+        <v>ICEMAN</v>
       </c>
       <c r="G25" t="str">
-        <v>4:03</v>
+        <v>3:08</v>
       </c>
       <c r="H25" t="str">
         <v>Drake</v>
@@ -1340,21 +1340,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/road-trips/6769556940</v>
+        <v>https://music.apple.com/us/album/shabang/6769568449</v>
       </c>
       <c r="L25" t="str">
-        <v>Road Trips - Drake</v>
+        <v>Shabang - Drake</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Fortworth</v>
+        <v>Road Trips</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/fortworth/6769551482</v>
+        <v>https://music.apple.com/us/song/road-trips/6769557053</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-18</v>
@@ -1363,10 +1363,10 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>HABIBTI</v>
+        <v>MAID OF HONOUR</v>
       </c>
       <c r="G26" t="str">
-        <v>3:51</v>
+        <v>4:03</v>
       </c>
       <c r="H26" t="str">
         <v>Drake</v>
@@ -1378,21 +1378,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/fortworth/6769551464</v>
+        <v>https://music.apple.com/us/album/road-trips/6769556940</v>
       </c>
       <c r="L26" t="str">
-        <v>Fortworth - Drake</v>
+        <v>Road Trips - Drake</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Repeat It</v>
+        <v>Fortworth</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/repeat-it/6764277864</v>
+        <v>https://music.apple.com/us/song/fortworth/6769551482</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-18</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>Repeat It - Single</v>
+        <v>HABIBTI</v>
       </c>
       <c r="G27" t="str">
-        <v>3:11</v>
+        <v>3:51</v>
       </c>
       <c r="H27" t="str">
-        <v>Martin Garrix</v>
+        <v>Drake</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/repeat-it/1895713789</v>
+        <v>https://music.apple.com/us/album/fortworth/6769551464</v>
       </c>
       <c r="L27" t="str">
-        <v>Repeat It - Martin Garrix</v>
+        <v>Fortworth - Drake</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Fool Proof</v>
+        <v>Repeat It</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/fool-proof/1892466004</v>
+        <v>https://music.apple.com/us/song/repeat-it/6764277864</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-18</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>Repeat It - Single</v>
       </c>
       <c r="G28" t="str">
-        <v>2:36</v>
+        <v>3:11</v>
       </c>
       <c r="H28" t="str">
-        <v>Cody Johnson</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/fool-proof/1892465981</v>
+        <v>https://music.apple.com/us/album/repeat-it/1895713789</v>
       </c>
       <c r="L28" t="str">
-        <v>Fool Proof - Cody Johnson</v>
+        <v>Repeat It - Martin Garrix</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Crisco</v>
+        <v>Fool Proof</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/crisco/6763369506</v>
+        <v>https://music.apple.com/us/song/fool-proof/1892466004</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-18</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>Crisco - Single</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G29" t="str">
-        <v>2:56</v>
+        <v>2:36</v>
       </c>
       <c r="H29" t="str">
-        <v>Miranda Lambert</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/miranda-lambert/18732261</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/crisco/1895284236</v>
+        <v>https://music.apple.com/us/album/fool-proof/1892465981</v>
       </c>
       <c r="L29" t="str">
-        <v>Crisco - Miranda Lambert</v>
+        <v>Fool Proof - Cody Johnson</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Absolution</v>
+        <v>Crisco</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/absolution/1884987651</v>
+        <v>https://music.apple.com/us/song/crisco/6763369506</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-18</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>Forever Now</v>
+        <v>Crisco - Single</v>
       </c>
       <c r="G30" t="str">
-        <v>4:05</v>
+        <v>2:56</v>
       </c>
       <c r="H30" t="str">
-        <v>Switchfoot</v>
+        <v>Miranda Lambert</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
+        <v>https://music.apple.com/us/artist/miranda-lambert/18732261</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/absolution/1884987638</v>
+        <v>https://music.apple.com/us/album/crisco/1895284236</v>
       </c>
       <c r="L30" t="str">
-        <v>Absolution - Switchfoot</v>
+        <v>Crisco - Miranda Lambert</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>JESUS IS ALIVE</v>
+        <v>Absolution</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/jesus-is-alive/6767694896</v>
+        <v>https://music.apple.com/us/song/absolution/1884987651</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-18</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>JESUS IS ALIVE - Single</v>
+        <v>Forever Now</v>
       </c>
       <c r="G31" t="str">
-        <v>2:08</v>
+        <v>4:05</v>
       </c>
       <c r="H31" t="str">
-        <v>Forrest Frank</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
+        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/jesus-is-alive/6767694895</v>
+        <v>https://music.apple.com/us/album/absolution/1884987638</v>
       </c>
       <c r="L31" t="str">
-        <v>JESUS IS ALIVE - Forrest Frank</v>
+        <v>Absolution - Switchfoot</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Something To Lose</v>
+        <v>JESUS IS ALIVE</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/something-to-lose/6766964605</v>
+        <v>https://music.apple.com/us/song/jesus-is-alive/6767694896</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-18</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>Is This Heaven? - EP</v>
+        <v>JESUS IS ALIVE - Single</v>
       </c>
       <c r="G32" t="str">
-        <v>2:55</v>
+        <v>2:08</v>
       </c>
       <c r="H32" t="str">
-        <v>STELLA LEFTY</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/something-to-lose/6766964604</v>
+        <v>https://music.apple.com/us/album/jesus-is-alive/6767694895</v>
       </c>
       <c r="L32" t="str">
-        <v>Something To Lose - STELLA LEFTY</v>
+        <v>JESUS IS ALIVE - Forrest Frank</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Too Busy Missing You</v>
+        <v>Something To Lose</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/too-busy-missing-you/6766604915</v>
+        <v>https://music.apple.com/us/song/something-to-lose/6766964605</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-18</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>Off Campus: The Mixtape</v>
+        <v>Is This Heaven? - EP</v>
       </c>
       <c r="G33" t="str">
-        <v>3:25</v>
+        <v>2:55</v>
       </c>
       <c r="H33" t="str">
-        <v>Asha Banks</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/too-busy-missing-you/6766604455</v>
+        <v>https://music.apple.com/us/album/something-to-lose/6766964604</v>
       </c>
       <c r="L33" t="str">
-        <v>Too Busy Missing You - Asha Banks</v>
+        <v>Something To Lose - STELLA LEFTY</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>F-Stop Blues (4-track)</v>
+        <v>Too Busy Missing You</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/f-stop-blues-4-track/1883173173</v>
+        <v>https://music.apple.com/us/song/too-busy-missing-you/6766604915</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-18</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>Off Campus: The Mixtape</v>
       </c>
       <c r="G34" t="str">
-        <v>3:00</v>
+        <v>3:25</v>
       </c>
       <c r="H34" t="str">
-        <v>Jack Johnson</v>
+        <v>Asha Banks</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/f-stop-blues-4-track/1883172879</v>
+        <v>https://music.apple.com/us/album/too-busy-missing-you/6766604455</v>
       </c>
       <c r="L34" t="str">
-        <v>F-Stop Blues (4-track) - Jack Johnson</v>
+        <v>Too Busy Missing You - Asha Banks</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>PA' LO BONITO</v>
+        <v>F-Stop Blues (4-track)</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/pa-lo-bonito/1886496944</v>
+        <v>https://music.apple.com/us/song/f-stop-blues-4-track/1883173173</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-18</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>PA' LO BONITO - Single</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G35" t="str">
-        <v>3:04</v>
+        <v>3:00</v>
       </c>
       <c r="H35" t="str">
-        <v>Lenny Tavárez</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/pa-lo-bonito/1886496943</v>
+        <v>https://music.apple.com/us/album/f-stop-blues-4-track/1883172879</v>
       </c>
       <c r="L35" t="str">
-        <v>PA' LO BONITO - Lenny Tavárez</v>
+        <v>F-Stop Blues (4-track) - Jack Johnson</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>LONELY</v>
+        <v>PA' LO BONITO</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/lonely/6768757857</v>
+        <v>https://music.apple.com/us/song/pa-lo-bonito/1886496944</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-18</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>DESEO</v>
+        <v>PA' LO BONITO - Single</v>
       </c>
       <c r="G36" t="str">
-        <v>2:58</v>
+        <v>3:04</v>
       </c>
       <c r="H36" t="str">
-        <v>Katteyes</v>
+        <v>Lenny Tavárez</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/katteyes/1648818255</v>
+        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/lonely/6768757414</v>
+        <v>https://music.apple.com/us/album/pa-lo-bonito/1886496943</v>
       </c>
       <c r="L36" t="str">
-        <v>LONELY - Katteyes</v>
+        <v>PA' LO BONITO - Lenny Tavárez</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Lockup</v>
+        <v>LONELY</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/lockup/1894298102</v>
+        <v>https://music.apple.com/us/song/lonely/6768757857</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-18</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Pure Devotion</v>
+        <v>DESEO</v>
       </c>
       <c r="G37" t="str">
-        <v>4:31</v>
+        <v>2:58</v>
       </c>
       <c r="H37" t="str">
-        <v>Overmono</v>
+        <v>Katteyes</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/overmono/1129806758</v>
+        <v>https://music.apple.com/us/artist/katteyes/1648818255</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/lockup/1894298100</v>
+        <v>https://music.apple.com/us/album/lonely/6768757414</v>
       </c>
       <c r="L37" t="str">
-        <v>Lockup - Overmono</v>
+        <v>LONELY - Katteyes</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Young</v>
+        <v>Lockup</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/young/6767698952</v>
+        <v>https://music.apple.com/us/song/lockup/1894298102</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-18</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Young</v>
+        <v>Pure Devotion</v>
       </c>
       <c r="G38" t="str">
-        <v>2:46</v>
+        <v>4:31</v>
       </c>
       <c r="H38" t="str">
-        <v>Dan + Shay</v>
+        <v>Overmono</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/dan-shay/690319057</v>
+        <v>https://music.apple.com/us/artist/overmono/1129806758</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/young/6767698951</v>
+        <v>https://music.apple.com/us/album/lockup/1894298100</v>
       </c>
       <c r="L38" t="str">
-        <v>Young - Dan + Shay</v>
+        <v>Lockup - Overmono</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Parachute</v>
+        <v>Young</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/parachute/6764119241</v>
+        <v>https://music.apple.com/us/song/young/6767698952</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-18</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>Parachute - Single</v>
+        <v>Young</v>
       </c>
       <c r="G39" t="str">
-        <v>2:52</v>
+        <v>2:46</v>
       </c>
       <c r="H39" t="str">
-        <v>Maren Morris</v>
+        <v>Dan + Shay</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/maren-morris/262260873</v>
+        <v>https://music.apple.com/us/artist/dan-shay/690319057</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/parachute/1895648983</v>
+        <v>https://music.apple.com/us/album/young/6767698951</v>
       </c>
       <c r="L39" t="str">
-        <v>Parachute - Maren Morris</v>
+        <v>Young - Dan + Shay</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Little Things</v>
+        <v>Parachute</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/little-things/6766351153</v>
+        <v>https://music.apple.com/us/song/parachute/6764119241</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-18</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Little Things - Single</v>
+        <v>Parachute - Single</v>
       </c>
       <c r="G40" t="str">
-        <v>2:55</v>
+        <v>2:52</v>
       </c>
       <c r="H40" t="str">
-        <v>Kevin Jonas</v>
+        <v>Maren Morris</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/kevin-jonas/21138190</v>
+        <v>https://music.apple.com/us/artist/maren-morris/262260873</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/little-things/6766350882</v>
+        <v>https://music.apple.com/us/album/parachute/1895648983</v>
       </c>
       <c r="L40" t="str">
-        <v>Little Things - Kevin Jonas</v>
+        <v>Parachute - Maren Morris</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Fish Hunt Golf Drink</v>
+        <v>Little Things</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/fish-hunt-golf-drink/6766651884</v>
+        <v>https://music.apple.com/us/song/little-things/6766351153</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-18</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Signs</v>
+        <v>Little Things - Single</v>
       </c>
       <c r="G41" t="str">
-        <v>2:34</v>
+        <v>2:55</v>
       </c>
       <c r="H41" t="str">
-        <v>Luke Bryan</v>
+        <v>Kevin Jonas</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
+        <v>https://music.apple.com/us/artist/kevin-jonas/21138190</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/fish-hunt-golf-drink/6766651878</v>
+        <v>https://music.apple.com/us/album/little-things/6766350882</v>
       </c>
       <c r="L41" t="str">
-        <v>Fish Hunt Golf Drink - Luke Bryan</v>
+        <v>Little Things - Kevin Jonas</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>PAGEANT STAGE</v>
+        <v>Fish Hunt Golf Drink</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/pageant-stage/6764125889</v>
+        <v>https://music.apple.com/us/song/fish-hunt-golf-drink/6766651884</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-18</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>THE EDGE</v>
+        <v>Signs</v>
       </c>
       <c r="G42" t="str">
-        <v>2:52</v>
+        <v>2:34</v>
       </c>
       <c r="H42" t="str">
-        <v>Tone Stith</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/tone-stith/1167717310</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/pageant-stage/1895651504</v>
+        <v>https://music.apple.com/us/album/fish-hunt-golf-drink/6766651878</v>
       </c>
       <c r="L42" t="str">
-        <v>PAGEANT STAGE - Tone Stith</v>
+        <v>Fish Hunt Golf Drink - Luke Bryan</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Firestorm</v>
+        <v>PAGEANT STAGE</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/firestorm/1868827004</v>
+        <v>https://music.apple.com/us/song/pageant-stage/6764125889</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-18</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Of Earth &amp; Wires</v>
+        <v>THE EDGE</v>
       </c>
       <c r="G43" t="str">
-        <v>2:29</v>
+        <v>2:52</v>
       </c>
       <c r="H43" t="str">
-        <v>Dua Saleh</v>
+        <v>Tone Stith</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
+        <v>https://music.apple.com/us/artist/tone-stith/1167717310</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/firestorm/1868826829</v>
+        <v>https://music.apple.com/us/album/pageant-stage/1895651504</v>
       </c>
       <c r="L43" t="str">
-        <v>Firestorm - Dua Saleh</v>
+        <v>PAGEANT STAGE - Tone Stith</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>girl next door</v>
+        <v>Firestorm</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/girl-next-door/6768077610</v>
+        <v>https://music.apple.com/us/song/firestorm/1868827004</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-18</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>girl next door - Single</v>
+        <v>Of Earth &amp; Wires</v>
       </c>
       <c r="G44" t="str">
-        <v>3:18</v>
+        <v>2:29</v>
       </c>
       <c r="H44" t="str">
-        <v>mgk</v>
+        <v>Dua Saleh</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/mgk/465954501</v>
+        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/girl-next-door/6768077609</v>
+        <v>https://music.apple.com/us/album/firestorm/1868826829</v>
       </c>
       <c r="L44" t="str">
-        <v>girl next door - mgk</v>
+        <v>Firestorm - Dua Saleh</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>BIG DOG</v>
+        <v>girl next door</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/big-dog/1887197046</v>
+        <v>https://music.apple.com/us/song/girl-next-door/6768077610</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-18</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
+        <v>girl next door - Single</v>
       </c>
       <c r="G45" t="str">
-        <v>3:36</v>
+        <v>3:18</v>
       </c>
       <c r="H45" t="str">
-        <v>Genesis Owusu</v>
+        <v>mgk</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
+        <v>https://music.apple.com/us/artist/mgk/465954501</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/big-dog/1887196431</v>
+        <v>https://music.apple.com/us/album/girl-next-door/6768077609</v>
       </c>
       <c r="L45" t="str">
-        <v>BIG DOG - Genesis Owusu</v>
+        <v>girl next door - mgk</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>idea of love - A COLORS SHOW</v>
+        <v>BIG DOG</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/idea-of-love-a-colors-show/6767667046</v>
+        <v>https://music.apple.com/us/song/big-dog/1887197046</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-18</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>idea of love - A COLORS SHOW - Single</v>
+        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
       </c>
       <c r="G46" t="str">
-        <v>2:34</v>
+        <v>3:36</v>
       </c>
       <c r="H46" t="str">
-        <v>kwn</v>
+        <v>Genesis Owusu</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
+        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/idea-of-love-a-colors-show/6767666835</v>
+        <v>https://music.apple.com/us/album/big-dog/1887196431</v>
       </c>
       <c r="L46" t="str">
-        <v>idea of love - A COLORS SHOW - kwn</v>
+        <v>BIG DOG - Genesis Owusu</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Heavy Serenade</v>
+        <v>idea of love - A COLORS SHOW</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/heavy-serenade/1892154309</v>
+        <v>https://music.apple.com/us/song/idea-of-love-a-colors-show/6767667046</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-18</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>Heavy Serenade - EP</v>
+        <v>idea of love - A COLORS SHOW - Single</v>
       </c>
       <c r="G47" t="str">
-        <v>3:00</v>
+        <v>2:34</v>
       </c>
       <c r="H47" t="str">
-        <v>NMIXX</v>
+        <v>kwn</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
+        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/heavy-serenade/1892154305</v>
+        <v>https://music.apple.com/us/album/idea-of-love-a-colors-show/6767666835</v>
       </c>
       <c r="L47" t="str">
-        <v>Heavy Serenade - NMIXX</v>
+        <v>idea of love - A COLORS SHOW - kwn</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ddok ddok ddok</v>
+        <v>Heavy Serenade</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/ddok-ddok-ddok/6764203482</v>
+        <v>https://music.apple.com/us/song/heavy-serenade/1892154309</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-18</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>ddok ddok ddok - Single</v>
+        <v>Heavy Serenade - EP</v>
       </c>
       <c r="G48" t="str">
-        <v>2:35</v>
+        <v>3:00</v>
       </c>
       <c r="H48" t="str">
-        <v>BOYNEXTDOOR</v>
+        <v>NMIXX</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/boynextdoor/1687612559</v>
+        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/ddok-ddok-ddok/6764203481</v>
+        <v>https://music.apple.com/us/album/heavy-serenade/1892154305</v>
       </c>
       <c r="L48" t="str">
-        <v>ddok ddok ddok - BOYNEXTDOOR</v>
+        <v>Heavy Serenade - NMIXX</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Shut It Down</v>
+        <v>ddok ddok ddok</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/shut-it-down/6763631128</v>
+        <v>https://music.apple.com/us/song/ddok-ddok-ddok/6764203482</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-18</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>Shut It Down - Single</v>
+        <v>ddok ddok ddok - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>3:32</v>
+        <v>2:35</v>
       </c>
       <c r="H49" t="str">
-        <v>Boys Noize</v>
+        <v>BOYNEXTDOOR</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/boys-noize/60393190</v>
+        <v>https://music.apple.com/us/artist/boynextdoor/1687612559</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/shut-it-down/1895408470</v>
+        <v>https://music.apple.com/us/album/ddok-ddok-ddok/6764203481</v>
       </c>
       <c r="L49" t="str">
-        <v>Shut It Down - Boys Noize</v>
+        <v>ddok ddok ddok - BOYNEXTDOOR</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss)</v>
+        <v>Shut It Down</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/together-feat-nikki-nair-jessy-lanza-prentiss/6763207821</v>
+        <v>https://music.apple.com/us/song/shut-it-down/6763631128</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-18</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss) - Single</v>
+        <v>Shut It Down - Single</v>
       </c>
       <c r="G50" t="str">
-        <v>3:18</v>
+        <v>3:32</v>
       </c>
       <c r="H50" t="str">
-        <v>The Avalanches</v>
+        <v>Boys Noize</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
+        <v>https://music.apple.com/us/artist/boys-noize/60393190</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/together-feat-nikki-nair-jessy-lanza-prentiss/1895215105</v>
+        <v>https://music.apple.com/us/album/shut-it-down/1895408470</v>
       </c>
       <c r="L50" t="str">
-        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss) - The Avalanches</v>
+        <v>Shut It Down - Boys Noize</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Can’t Miss You</v>
+        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss)</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/cant-miss-you/1886810999</v>
+        <v>https://music.apple.com/us/song/together-feat-nikki-nair-jessy-lanza-prentiss/6763207821</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-18</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss) - Single</v>
       </c>
       <c r="G51" t="str">
-        <v>2:32</v>
+        <v>3:18</v>
       </c>
       <c r="H51" t="str">
-        <v>Sublime</v>
+        <v>The Avalanches</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/sublime/63480</v>
+        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/cant-miss-you/1886810990</v>
+        <v>https://music.apple.com/us/album/together-feat-nikki-nair-jessy-lanza-prentiss/1895215105</v>
       </c>
       <c r="L51" t="str">
-        <v>Can’t Miss You - Sublime</v>
+        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss) - The Avalanches</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Razorblades And Runways</v>
+        <v>Can’t Miss You</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/razorblades-and-runways/1888004809</v>
+        <v>https://music.apple.com/us/song/cant-miss-you/1886810999</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-18</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>Get It Honest</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="G52" t="str">
-        <v>3:33</v>
+        <v>2:32</v>
       </c>
       <c r="H52" t="str">
-        <v>The Revivalists</v>
+        <v>Sublime</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
+        <v>https://music.apple.com/us/artist/sublime/63480</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/razorblades-and-runways/1888004802</v>
+        <v>https://music.apple.com/us/album/cant-miss-you/1886810990</v>
       </c>
       <c r="L52" t="str">
-        <v>Razorblades And Runways - The Revivalists</v>
+        <v>Can’t Miss You - Sublime</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Massacre</v>
+        <v>Razorblades And Runways</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/massacre/1892127745</v>
+        <v>https://music.apple.com/us/song/razorblades-and-runways/1888004809</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-18</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>Massacre - Single</v>
+        <v>Get It Honest</v>
       </c>
       <c r="G53" t="str">
-        <v>2:55</v>
+        <v>3:33</v>
       </c>
       <c r="H53" t="str">
-        <v>Murex</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/murex/1607430925</v>
+        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/massacre/1892127742</v>
+        <v>https://music.apple.com/us/album/razorblades-and-runways/1888004802</v>
       </c>
       <c r="L53" t="str">
-        <v>Massacre - Murex</v>
+        <v>Razorblades And Runways - The Revivalists</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Better That Way</v>
+        <v>Massacre</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/better-that-way/6766273199</v>
+        <v>https://music.apple.com/us/song/massacre/1892127745</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-18</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>Christian Name</v>
+        <v>Massacre - Single</v>
       </c>
       <c r="G54" t="str">
-        <v>3:45</v>
+        <v>2:55</v>
       </c>
       <c r="H54" t="str">
-        <v>Charles Wesley Godwin</v>
+        <v>Murex</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/charles-wesley-godwin/1441994025</v>
+        <v>https://music.apple.com/us/artist/murex/1607430925</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/better-that-way/1896261802</v>
+        <v>https://music.apple.com/us/album/massacre/1892127742</v>
       </c>
       <c r="L54" t="str">
-        <v>Better That Way - Charles Wesley Godwin</v>
+        <v>Massacre - Murex</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Apollo</v>
+        <v>Better That Way</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/apollo/6765602431</v>
+        <v>https://music.apple.com/us/song/better-that-way/6766273199</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-18</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Apollo - Single</v>
+        <v>Christian Name</v>
       </c>
       <c r="G55" t="str">
-        <v>3:35</v>
+        <v>3:45</v>
       </c>
       <c r="H55" t="str">
-        <v>Bryant Barnes</v>
+        <v>Charles Wesley Godwin</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
+        <v>https://music.apple.com/us/artist/charles-wesley-godwin/1441994025</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/apollo/6765602369</v>
+        <v>https://music.apple.com/us/album/better-that-way/1896261802</v>
       </c>
       <c r="L55" t="str">
-        <v>Apollo - Bryant Barnes</v>
+        <v>Better That Way - Charles Wesley Godwin</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Infinity (123)</v>
+        <v>Apollo</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/infinity-123/6763447312</v>
+        <v>https://music.apple.com/us/song/apollo/6765602431</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-18</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>Infinity (123) - Single</v>
+        <v>Apollo - Single</v>
       </c>
       <c r="G56" t="str">
-        <v>2:19</v>
+        <v>3:35</v>
       </c>
       <c r="H56" t="str">
-        <v>December 10</v>
+        <v>Bryant Barnes</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
+        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/infinity-123/1895320456</v>
+        <v>https://music.apple.com/us/album/apollo/6765602369</v>
       </c>
       <c r="L56" t="str">
-        <v>Infinity (123) - December 10</v>
+        <v>Apollo - Bryant Barnes</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Ain't Over Me Yet</v>
+        <v>Infinity (123)</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/aint-over-me-yet/6767283811</v>
+        <v>https://music.apple.com/us/song/infinity-123/6763447312</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-18</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>Cherry Valley Forever</v>
+        <v>Infinity (123) - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>3:24</v>
+        <v>2:19</v>
       </c>
       <c r="H57" t="str">
-        <v>Carter Faith</v>
+        <v>December 10</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/carter-faith/1489205896</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/aint-over-me-yet/1896458169</v>
+        <v>https://music.apple.com/us/album/infinity-123/1895320456</v>
       </c>
       <c r="L57" t="str">
-        <v>Ain't Over Me Yet - Carter Faith</v>
+        <v>Infinity (123) - December 10</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Where Did You Go</v>
+        <v>Ain't Over Me Yet</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/where-did-you-go/1877958504</v>
+        <v>https://music.apple.com/us/song/aint-over-me-yet/6767283811</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-18</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>Growing Pains (Deluxe)</v>
+        <v>Cherry Valley Forever</v>
       </c>
       <c r="G58" t="str">
-        <v>2:47</v>
+        <v>3:24</v>
       </c>
       <c r="H58" t="str">
-        <v>Trousdale</v>
+        <v>Carter Faith</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/carter-faith/1489205896</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/where-did-you-go/1877958112</v>
+        <v>https://music.apple.com/us/album/aint-over-me-yet/1896458169</v>
       </c>
       <c r="L58" t="str">
-        <v>Where Did You Go - Trousdale</v>
+        <v>Ain't Over Me Yet - Carter Faith</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>I LOVE YOU</v>
+        <v>Where Did You Go</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/i-love-you/6766999950</v>
+        <v>https://music.apple.com/us/song/where-did-you-go/1877958504</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-18</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>I LOVE YOU - Single</v>
+        <v>Growing Pains (Deluxe)</v>
       </c>
       <c r="G59" t="str">
-        <v>3:11</v>
+        <v>2:47</v>
       </c>
       <c r="H59" t="str">
-        <v>Noga Erez</v>
+        <v>Trousdale</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/noga-erez/1166657901</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/i-love-you/6766999949</v>
+        <v>https://music.apple.com/us/album/where-did-you-go/1877958112</v>
       </c>
       <c r="L59" t="str">
-        <v>I LOVE YOU - Noga Erez</v>
+        <v>Where Did You Go - Trousdale</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Housekeeping</v>
+        <v>I LOVE YOU</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/housekeeping/6766290834</v>
+        <v>https://music.apple.com/us/song/i-love-you/6766999950</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-18</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Housekeeping - Single</v>
+        <v>I LOVE YOU - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>3:25</v>
+        <v>3:11</v>
       </c>
       <c r="H60" t="str">
-        <v>Ally Salort</v>
+        <v>Noga Erez</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
+        <v>https://music.apple.com/us/artist/noga-erez/1166657901</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/housekeeping/6766290823</v>
+        <v>https://music.apple.com/us/album/i-love-you/6766999949</v>
       </c>
       <c r="L60" t="str">
-        <v>Housekeeping - Ally Salort</v>
+        <v>I LOVE YOU - Noga Erez</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Surprise Surprise</v>
+        <v>Housekeeping</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/surprise-surprise/6764842119</v>
+        <v>https://music.apple.com/us/song/housekeeping/6766290834</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-18</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Surprise Surprise - Single</v>
+        <v>Housekeeping - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>2:55</v>
+        <v>3:25</v>
       </c>
       <c r="H61" t="str">
-        <v>Chloe Qisha</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/surprise-surprise/1895934408</v>
+        <v>https://music.apple.com/us/album/housekeeping/6766290823</v>
       </c>
       <c r="L61" t="str">
-        <v>Surprise Surprise - Chloe Qisha</v>
+        <v>Housekeeping - Ally Salort</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Dog</v>
+        <v>Surprise Surprise</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/dog/1885967384</v>
+        <v>https://music.apple.com/us/song/surprise-surprise/6764842119</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-18</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Gentleman</v>
+        <v>Surprise Surprise - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>3:08</v>
+        <v>2:55</v>
       </c>
       <c r="H62" t="str">
-        <v>Towa Bird</v>
+        <v>Chloe Qisha</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
+        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/dog/1885967368</v>
+        <v>https://music.apple.com/us/album/surprise-surprise/1895934408</v>
       </c>
       <c r="L62" t="str">
-        <v>Dog - Towa Bird</v>
+        <v>Surprise Surprise - Chloe Qisha</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>I Never See Her</v>
+        <v>Dog</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/i-never-see-her/6764149225</v>
+        <v>https://music.apple.com/us/song/dog/1885967384</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-18</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>I Never See Her - Single</v>
+        <v>Gentleman</v>
       </c>
       <c r="G63" t="str">
-        <v>3:04</v>
+        <v>3:08</v>
       </c>
       <c r="H63" t="str">
-        <v>Spacey Jane</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
+        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/i-never-see-her/1895660748</v>
+        <v>https://music.apple.com/us/album/dog/1885967368</v>
       </c>
       <c r="L63" t="str">
-        <v>I Never See Her - Spacey Jane</v>
+        <v>Dog - Towa Bird</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>No God</v>
+        <v>I Never See Her</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/no-god/1891187414</v>
+        <v>https://music.apple.com/us/song/i-never-see-her/6764149225</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-18</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Alone Together</v>
+        <v>I Never See Her - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>2:45</v>
+        <v>3:04</v>
       </c>
       <c r="H64" t="str">
-        <v>Show Me the Body</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
+        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/no-god/1891187411</v>
+        <v>https://music.apple.com/us/album/i-never-see-her/1895660748</v>
       </c>
       <c r="L64" t="str">
-        <v>No God - Show Me the Body</v>
+        <v>I Never See Her - Spacey Jane</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>burden</v>
+        <v>No God</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/burden/6767688180</v>
+        <v>https://music.apple.com/us/song/no-god/1891187414</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-18</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>burden - Single</v>
+        <v>Alone Together</v>
       </c>
       <c r="G65" t="str">
-        <v>3:24</v>
+        <v>2:45</v>
       </c>
       <c r="H65" t="str">
-        <v>Abe Parker</v>
+        <v>Show Me the Body</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/abe-parker/490444584</v>
+        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/burden/6767688179</v>
+        <v>https://music.apple.com/us/album/no-god/1891187411</v>
       </c>
       <c r="L65" t="str">
-        <v>burden - Abe Parker</v>
+        <v>No God - Show Me the Body</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Chico Raro</v>
+        <v>burden</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/chico-raro/6767713536</v>
+        <v>https://music.apple.com/us/song/burden/6767688180</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-18</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Chico Raro - Single</v>
+        <v>burden - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>3:17</v>
+        <v>3:24</v>
       </c>
       <c r="H66" t="str">
-        <v>Arón Piper</v>
+        <v>Abe Parker</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/ar%C3%B3n-piper/691972942</v>
+        <v>https://music.apple.com/us/artist/abe-parker/490444584</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/chico-raro/6767713527</v>
+        <v>https://music.apple.com/us/album/burden/6767688179</v>
       </c>
       <c r="L66" t="str">
-        <v>Chico Raro - Arón Piper</v>
+        <v>burden - Abe Parker</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>What's Done Is Done</v>
+        <v>Chico Raro</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/whats-done-is-done/6763088629</v>
+        <v>https://music.apple.com/us/song/chico-raro/6767713536</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-18</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>What's Done Is Done - Single</v>
+        <v>Chico Raro - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>2:53</v>
+        <v>3:17</v>
       </c>
       <c r="H67" t="str">
-        <v>Jorja Smith</v>
+        <v>Arón Piper</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
+        <v>https://music.apple.com/us/artist/ar%C3%B3n-piper/691972942</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/whats-done-is-done/1895156626</v>
+        <v>https://music.apple.com/us/album/chico-raro/6767713527</v>
       </c>
       <c r="L67" t="str">
-        <v>What's Done Is Done - Jorja Smith</v>
+        <v>Chico Raro - Arón Piper</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>round and round</v>
+        <v>What's Done Is Done</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/round-and-round/1885665987</v>
+        <v>https://music.apple.com/us/song/whats-done-is-done/6763088629</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-18</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>round and round - Single</v>
+        <v>What's Done Is Done - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>2:47</v>
+        <v>2:53</v>
       </c>
       <c r="H68" t="str">
-        <v>bbno$</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
+        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/round-and-round/1885665982</v>
+        <v>https://music.apple.com/us/album/whats-done-is-done/1895156626</v>
       </c>
       <c r="L68" t="str">
-        <v>round and round - bbno$</v>
+        <v>What's Done Is Done - Jorja Smith</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Ain’t That Deep</v>
+        <v>round and round</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/aint-that-deep/1882831449</v>
+        <v>https://music.apple.com/us/song/round-and-round/1885665987</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-18</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>The Last Balloon</v>
+        <v>round and round - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>2:39</v>
+        <v>2:47</v>
       </c>
       <c r="H69" t="str">
-        <v>Tank and the Bangas</v>
+        <v>bbno$</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
+        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/aint-that-deep/1882831446</v>
+        <v>https://music.apple.com/us/album/round-and-round/1885665982</v>
       </c>
       <c r="L69" t="str">
-        <v>Ain’t That Deep - Tank and the Bangas</v>
+        <v>round and round - bbno$</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Emily</v>
+        <v>Ain’t That Deep</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/emily/1893405442</v>
+        <v>https://music.apple.com/us/song/aint-that-deep/1882831449</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-18</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>So Much To Say - EP</v>
+        <v>The Last Balloon</v>
       </c>
       <c r="G70" t="str">
-        <v>2:35</v>
+        <v>2:39</v>
       </c>
       <c r="H70" t="str">
-        <v>Daisy Grenade</v>
+        <v>Tank and the Bangas</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/daisy-grenade/1611437131</v>
+        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/emily/1893405440</v>
+        <v>https://music.apple.com/us/album/aint-that-deep/1882831446</v>
       </c>
       <c r="L70" t="str">
-        <v>Emily - Daisy Grenade</v>
+        <v>Ain’t That Deep - Tank and the Bangas</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Hold</v>
+        <v>Emily</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/hold/6767296480</v>
+        <v>https://music.apple.com/us/song/emily/1893405442</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-18</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Hold - Single</v>
+        <v>So Much To Say - EP</v>
       </c>
       <c r="G71" t="str">
-        <v>4:07</v>
+        <v>2:35</v>
       </c>
       <c r="H71" t="str">
-        <v>Sabrina Sterling</v>
+        <v>Daisy Grenade</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/sabrina-sterling/1577892147</v>
+        <v>https://music.apple.com/us/artist/daisy-grenade/1611437131</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/hold/1896462063</v>
+        <v>https://music.apple.com/us/album/emily/1893405440</v>
       </c>
       <c r="L71" t="str">
-        <v>Hold - Sabrina Sterling</v>
+        <v>Emily - Daisy Grenade</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Flying Monkey</v>
+        <v>Hold</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/flying-monkey/1894351228</v>
+        <v>https://music.apple.com/us/song/hold/6767296480</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-18</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Flying Monkey - Single</v>
+        <v>Hold - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>4:09</v>
+        <v>4:07</v>
       </c>
       <c r="H72" t="str">
-        <v>Blue Medusa</v>
+        <v>Sabrina Sterling</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
+        <v>https://music.apple.com/us/artist/sabrina-sterling/1577892147</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/flying-monkey/1894351227</v>
+        <v>https://music.apple.com/us/album/hold/1896462063</v>
       </c>
       <c r="L72" t="str">
-        <v>Flying Monkey - Blue Medusa</v>
+        <v>Hold - Sabrina Sterling</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Anything Goes</v>
+        <v>Flying Monkey</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/anything-goes/1891118972</v>
+        <v>https://music.apple.com/us/song/flying-monkey/1894351228</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-18</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Anything Goes</v>
+        <v>Flying Monkey - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>3:00</v>
+        <v>4:09</v>
       </c>
       <c r="H73" t="str">
-        <v>Kaleena Zanders</v>
+        <v>Blue Medusa</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/anything-goes/1891118971</v>
+        <v>https://music.apple.com/us/album/flying-monkey/1894351227</v>
       </c>
       <c r="L73" t="str">
-        <v>Anything Goes - Kaleena Zanders</v>
+        <v>Flying Monkey - Blue Medusa</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>We Are</v>
+        <v>Anything Goes</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/we-are/1894252873</v>
+        <v>https://music.apple.com/us/song/anything-goes/1891118972</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-18</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>We Are - Single</v>
+        <v>Anything Goes</v>
       </c>
       <c r="G74" t="str">
-        <v>3:33</v>
+        <v>3:00</v>
       </c>
       <c r="H74" t="str">
-        <v>Adam Ten</v>
+        <v>Kaleena Zanders</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/adam-ten/1472226854</v>
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/we-are/1894252870</v>
+        <v>https://music.apple.com/us/album/anything-goes/1891118971</v>
       </c>
       <c r="L74" t="str">
-        <v>We Are - Adam Ten</v>
+        <v>Anything Goes - Kaleena Zanders</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>It's For the Kids</v>
+        <v>We Are</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/its-for-the-kids/1867327679</v>
+        <v>https://music.apple.com/us/song/we-are/1894252873</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-18</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Cursum Perficio</v>
+        <v>We Are - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>4:20</v>
+        <v>3:33</v>
       </c>
       <c r="H75" t="str">
-        <v>Anthrax</v>
+        <v>Adam Ten</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/anthrax/80417</v>
+        <v>https://music.apple.com/us/artist/adam-ten/1472226854</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/its-for-the-kids/1867327673</v>
+        <v>https://music.apple.com/us/album/we-are/1894252870</v>
       </c>
       <c r="L75" t="str">
-        <v>It's For the Kids - Anthrax</v>
+        <v>We Are - Adam Ten</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Pure Ecstasy</v>
+        <v>It's For the Kids</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/pure-ecstasy/6762228978</v>
+        <v>https://music.apple.com/us/song/its-for-the-kids/1867327679</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-18</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Pure Ecstasy</v>
+        <v>Cursum Perficio</v>
       </c>
       <c r="G76" t="str">
-        <v>3:05</v>
+        <v>4:20</v>
       </c>
       <c r="H76" t="str">
-        <v>Beartooth</v>
+        <v>Anthrax</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
+        <v>https://music.apple.com/us/artist/anthrax/80417</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/pure-ecstasy/1893453878</v>
+        <v>https://music.apple.com/us/album/its-for-the-kids/1867327673</v>
       </c>
       <c r="L76" t="str">
-        <v>Pure Ecstasy - Beartooth</v>
+        <v>It's For the Kids - Anthrax</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Something Wicked</v>
+        <v>Pure Ecstasy</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/something-wicked/6766252959</v>
+        <v>https://music.apple.com/us/song/pure-ecstasy/6762228978</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-18</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Something Wicked - Single</v>
+        <v>Pure Ecstasy</v>
       </c>
       <c r="G77" t="str">
-        <v>3:28</v>
+        <v>3:05</v>
       </c>
       <c r="H77" t="str">
-        <v>Breaking Benjamin</v>
+        <v>Beartooth</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/breaking-benjamin/3299379</v>
+        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/something-wicked/1896253678</v>
+        <v>https://music.apple.com/us/album/pure-ecstasy/1893453878</v>
       </c>
       <c r="L77" t="str">
-        <v>Something Wicked - Breaking Benjamin</v>
+        <v>Pure Ecstasy - Beartooth</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Feel The Funk</v>
+        <v>Something Wicked</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/feel-the-funk/6763294007</v>
+        <v>https://music.apple.com/us/song/something-wicked/6766252959</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-18</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>The Funk EP - Single</v>
+        <v>Something Wicked - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>3:26</v>
+        <v>3:28</v>
       </c>
       <c r="H78" t="str">
-        <v>Riordan</v>
+        <v>Breaking Benjamin</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/riordan/1517575029</v>
+        <v>https://music.apple.com/us/artist/breaking-benjamin/3299379</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/feel-the-funk/1895251685</v>
+        <v>https://music.apple.com/us/album/something-wicked/1896253678</v>
       </c>
       <c r="L78" t="str">
-        <v>Feel The Funk - Riordan</v>
+        <v>Something Wicked - Breaking Benjamin</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Everglades (Remix)</v>
+        <v>Feel The Funk</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/everglades-remix/6767719584</v>
+        <v>https://music.apple.com/us/song/feel-the-funk/6763294007</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-18</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Everglades (Remix) - Single</v>
+        <v>The Funk EP - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>2:42</v>
+        <v>3:26</v>
       </c>
       <c r="H79" t="str">
-        <v>Aziedoesntexist</v>
+        <v>Riordan</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/aziedoesntexist/1831152556</v>
+        <v>https://music.apple.com/us/artist/riordan/1517575029</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/everglades-remix/6767719577</v>
+        <v>https://music.apple.com/us/album/feel-the-funk/1895251685</v>
       </c>
       <c r="L79" t="str">
-        <v>Everglades (Remix) - Aziedoesntexist</v>
+        <v>Feel The Funk - Riordan</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Walk</v>
+        <v>Everglades (Remix)</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/walk/1892180098</v>
+        <v>https://music.apple.com/us/song/everglades-remix/6767719584</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-18</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Walk - Single</v>
+        <v>Everglades (Remix) - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>2:25</v>
+        <v>2:42</v>
       </c>
       <c r="H80" t="str">
-        <v>Melodicb</v>
+        <v>Aziedoesntexist</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/melodicb/1440206517</v>
+        <v>https://music.apple.com/us/artist/aziedoesntexist/1831152556</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/walk/1892180097</v>
+        <v>https://music.apple.com/us/album/everglades-remix/6767719577</v>
       </c>
       <c r="L80" t="str">
-        <v>Walk - Melodicb</v>
+        <v>Everglades (Remix) - Aziedoesntexist</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Volver a Ti</v>
+        <v>Walk</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/volver-a-ti/6766258204</v>
+        <v>https://music.apple.com/us/song/walk/1892180098</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-18</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Norteña</v>
+        <v>Walk - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>3:47</v>
+        <v>2:25</v>
       </c>
       <c r="H81" t="str">
-        <v>Julieta Venegas</v>
+        <v>Melodicb</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/julieta-venegas/302960</v>
+        <v>https://music.apple.com/us/artist/melodicb/1440206517</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/volver-a-ti/1896255736</v>
+        <v>https://music.apple.com/us/album/walk/1892180097</v>
       </c>
       <c r="L81" t="str">
-        <v>Volver a Ti - Julieta Venegas</v>
+        <v>Walk - Melodicb</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Bahamas</v>
+        <v>Volver a Ti</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/bahamas/6764695848</v>
+        <v>https://music.apple.com/us/song/volver-a-ti/6766258204</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-18</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Bahamas - Single</v>
+        <v>Norteña</v>
       </c>
       <c r="G82" t="str">
-        <v>2:06</v>
+        <v>3:47</v>
       </c>
       <c r="H82" t="str">
-        <v>LENCHO</v>
+        <v>Julieta Venegas</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
+        <v>https://music.apple.com/us/artist/julieta-venegas/302960</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/bahamas/6764695847</v>
+        <v>https://music.apple.com/us/album/volver-a-ti/1896255736</v>
       </c>
       <c r="L82" t="str">
-        <v>Bahamas - LENCHO</v>
+        <v>Volver a Ti - Julieta Venegas</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Same Old Song</v>
+        <v>Bahamas</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/same-old-song/6762860685</v>
+        <v>https://music.apple.com/us/song/bahamas/6764695848</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-18</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Same Old Song - Single</v>
+        <v>Bahamas - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>4:12</v>
+        <v>2:06</v>
       </c>
       <c r="H83" t="str">
-        <v>Lila Drew</v>
+        <v>LENCHO</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/lila-drew/1439482732</v>
+        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/same-old-song/1895047985</v>
+        <v>https://music.apple.com/us/album/bahamas/6764695847</v>
       </c>
       <c r="L83" t="str">
-        <v>Same Old Song - Lila Drew</v>
+        <v>Bahamas - LENCHO</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>gentle</v>
+        <v>Same Old Song</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/gentle/6762828356</v>
+        <v>https://music.apple.com/us/song/same-old-song/6762860685</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-18</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>gentle - Single</v>
+        <v>Same Old Song - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>2:48</v>
+        <v>4:12</v>
       </c>
       <c r="H84" t="str">
-        <v>Venus Anon</v>
+        <v>Lila Drew</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/venus-anon/1635970130</v>
+        <v>https://music.apple.com/us/artist/lila-drew/1439482732</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/gentle/1895031896</v>
+        <v>https://music.apple.com/us/album/same-old-song/1895047985</v>
       </c>
       <c r="L84" t="str">
-        <v>gentle - Venus Anon</v>
+        <v>Same Old Song - Lila Drew</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Letters of Your Name</v>
+        <v>gentle</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/letters-of-your-name/1892919741</v>
+        <v>https://music.apple.com/us/song/gentle/6762828356</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-18</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Congratulations</v>
+        <v>gentle - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>3:21</v>
+        <v>2:48</v>
       </c>
       <c r="H85" t="str">
-        <v>Jacob Ungerleider</v>
+        <v>Venus Anon</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/jacob-ungerleider/1460845591</v>
+        <v>https://music.apple.com/us/artist/venus-anon/1635970130</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/letters-of-your-name/1892919737</v>
+        <v>https://music.apple.com/us/album/gentle/1895031896</v>
       </c>
       <c r="L85" t="str">
-        <v>Letters of Your Name - Jacob Ungerleider</v>
+        <v>gentle - Venus Anon</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Seratonin</v>
+        <v>Letters of Your Name</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/seratonin/6763447428</v>
+        <v>https://music.apple.com/us/song/letters-of-your-name/1892919741</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-18</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Seratonin - Single</v>
+        <v>Congratulations</v>
       </c>
       <c r="G86" t="str">
-        <v>1:55</v>
+        <v>3:21</v>
       </c>
       <c r="H86" t="str">
-        <v>James Hype</v>
+        <v>Jacob Ungerleider</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
+        <v>https://music.apple.com/us/artist/jacob-ungerleider/1460845591</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/seratonin/1895320367</v>
+        <v>https://music.apple.com/us/album/letters-of-your-name/1892919737</v>
       </c>
       <c r="L86" t="str">
-        <v>Seratonin - James Hype</v>
+        <v>Letters of Your Name - Jacob Ungerleider</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>A Digital Touch</v>
+        <v>Seratonin</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/a-digital-touch/6765592539</v>
+        <v>https://music.apple.com/us/song/seratonin/6763447428</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-18</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>A Digital Touch - Single</v>
+        <v>Seratonin - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>2:53</v>
+        <v>1:55</v>
       </c>
       <c r="H87" t="str">
-        <v>Evening Elephants</v>
+        <v>James Hype</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
+        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/a-digital-touch/1896003252</v>
+        <v>https://music.apple.com/us/album/seratonin/1895320367</v>
       </c>
       <c r="L87" t="str">
-        <v>A Digital Touch - Evening Elephants</v>
+        <v>Seratonin - James Hype</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Dead Man's Dog</v>
+        <v>A Digital Touch</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/dead-mans-dog/6763447424</v>
+        <v>https://music.apple.com/us/song/a-digital-touch/6765592539</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-18</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Aiming Torches At The Sun - EP</v>
+        <v>A Digital Touch - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>4:33</v>
+        <v>2:53</v>
       </c>
       <c r="H88" t="str">
-        <v>Dermot Henry</v>
+        <v>Evening Elephants</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/dermot-henry/1704074611</v>
+        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/dead-mans-dog/1895320369</v>
+        <v>https://music.apple.com/us/album/a-digital-touch/1896003252</v>
       </c>
       <c r="L88" t="str">
-        <v>Dead Man's Dog - Dermot Henry</v>
+        <v>A Digital Touch - Evening Elephants</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Fault of God</v>
+        <v>Dead Man's Dog</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/fault-of-god/1887702403</v>
+        <v>https://music.apple.com/us/song/dead-mans-dog/6763447424</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-18</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Active Child</v>
+        <v>Aiming Torches At The Sun - EP</v>
       </c>
       <c r="G89" t="str">
-        <v>4:13</v>
+        <v>4:33</v>
       </c>
       <c r="H89" t="str">
-        <v>Active Child</v>
+        <v>Dermot Henry</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/active-child/355288617</v>
+        <v>https://music.apple.com/us/artist/dermot-henry/1704074611</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/fault-of-god/1887701924</v>
+        <v>https://music.apple.com/us/album/dead-mans-dog/1895320369</v>
       </c>
       <c r="L89" t="str">
-        <v>Fault of God - Active Child</v>
+        <v>Dead Man's Dog - Dermot Henry</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Zone (feat. Poppy Baskcomb)</v>
+        <v>Fault of God</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/zone-feat-poppy-baskcomb/6763982867</v>
+        <v>https://music.apple.com/us/song/fault-of-god/1887702403</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-18</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Zone (feat. Poppy Baskcomb) - Single</v>
+        <v>Active Child</v>
       </c>
       <c r="G90" t="str">
-        <v>2:56</v>
+        <v>4:13</v>
       </c>
       <c r="H90" t="str">
-        <v>MK</v>
+        <v>Active Child</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/mk/63097617</v>
+        <v>https://music.apple.com/us/artist/active-child/355288617</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/zone-feat-poppy-baskcomb/1895585800</v>
+        <v>https://music.apple.com/us/album/fault-of-god/1887701924</v>
       </c>
       <c r="L90" t="str">
-        <v>Zone (feat. Poppy Baskcomb) - MK</v>
+        <v>Fault of God - Active Child</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Word Vomit</v>
+        <v>Zone (feat. Poppy Baskcomb)</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/word-vomit/1887315297</v>
+        <v>https://music.apple.com/us/song/zone-feat-poppy-baskcomb/6763982867</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-18</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Word Vomit - Single</v>
+        <v>Zone (feat. Poppy Baskcomb) - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>2:46</v>
+        <v>2:56</v>
       </c>
       <c r="H91" t="str">
-        <v>Baby Queen</v>
+        <v>MK</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
+        <v>https://music.apple.com/us/artist/mk/63097617</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/word-vomit/1887315294</v>
+        <v>https://music.apple.com/us/album/zone-feat-poppy-baskcomb/1895585800</v>
       </c>
       <c r="L91" t="str">
-        <v>Word Vomit - Baby Queen</v>
+        <v>Zone (feat. Poppy Baskcomb) - MK</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Evil in this House</v>
+        <v>Word Vomit</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/evil-in-this-house/1892398371</v>
+        <v>https://music.apple.com/us/song/word-vomit/1887315297</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-18</v>
@@ -3871,68 +3871,106 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Necropolitan</v>
+        <v>Word Vomit - Single</v>
       </c>
       <c r="G92" t="str">
-        <v>4:21</v>
+        <v>2:46</v>
       </c>
       <c r="H92" t="str">
-        <v>Green Lung</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/green-lung/1244071662</v>
+        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/evil-in-this-house/1892398281</v>
+        <v>https://music.apple.com/us/album/word-vomit/1887315294</v>
       </c>
       <c r="L92" t="str">
-        <v>Evil in this House - Green Lung</v>
+        <v>Word Vomit - Baby Queen</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
+        <v>Evil in this House</v>
+      </c>
+      <c r="B93" t="str">
+        <v/>
+      </c>
+      <c r="C93" t="str">
+        <v>https://music.apple.com/us/song/evil-in-this-house/1892398371</v>
+      </c>
+      <c r="D93" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="E93" t="str">
+        <v/>
+      </c>
+      <c r="F93" t="str">
+        <v>Necropolitan</v>
+      </c>
+      <c r="G93" t="str">
+        <v>4:21</v>
+      </c>
+      <c r="H93" t="str">
+        <v>Green Lung</v>
+      </c>
+      <c r="I93" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J93" t="str">
+        <v>https://music.apple.com/us/artist/green-lung/1244071662</v>
+      </c>
+      <c r="K93" t="str">
+        <v>https://music.apple.com/us/album/evil-in-this-house/1892398281</v>
+      </c>
+      <c r="L93" t="str">
+        <v>Evil in this House - Green Lung</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
         <v>Heaven on High</v>
       </c>
-      <c r="B93" t="str">
-        <v/>
-      </c>
-      <c r="C93" t="str">
+      <c r="B94" t="str">
+        <v/>
+      </c>
+      <c r="C94" t="str">
         <v>https://music.apple.com/us/song/heaven-on-high/1881724153</v>
       </c>
-      <c r="D93" t="str">
-        <v>2026-05-18</v>
-      </c>
-      <c r="E93" t="str">
-        <v/>
-      </c>
-      <c r="F93" t="str">
+      <c r="D94" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
         <v>A Pale White Dot</v>
       </c>
-      <c r="G93" t="str">
+      <c r="G94" t="str">
         <v>4:19</v>
       </c>
-      <c r="H93" t="str">
+      <c r="H94" t="str">
         <v>Periphery</v>
       </c>
-      <c r="I93" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J93" t="str">
+      <c r="I94" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J94" t="str">
         <v>https://music.apple.com/us/artist/periphery/187683869</v>
       </c>
-      <c r="K93" t="str">
+      <c r="K94" t="str">
         <v>https://music.apple.com/us/album/heaven-on-high/1881724003</v>
       </c>
-      <c r="L93" t="str">
+      <c r="L94" t="str">
         <v>Heaven on High - Periphery</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L93"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L94"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week03/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/ego/6769207667</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/hit-the-wall/6766750846</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/ran-to-atlanta/6769568597</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/hoe-phase/6769556949</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/im-spent/6769551476</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/abracadabra-apple-music-live/6768201780</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/falling-out-of-love/1891161448</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/dai-dai/6768469976</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/tu-recuerdo/6763660843</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/traitor-roles-reversed/6767665959</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/dirty-rosie/6767044374</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/2-hard-4-the-radio/6769568610</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/cheetah-print/6769557055</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/wnba/6769551471</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/shadow-of-a-man-apple-music-live/6768201925</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/epa/6768420253</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/im-your-girl-right/6766440186</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/fu%C3%ABgo/6767661766</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/jajaja/6766341319</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/find-god-feat-dominic-fike/1894315529</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/fool-me-once-feat-leon-thomas/1891467239</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/shabang/6769568598</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/road-trips/6769557053</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/fortworth/6769551482</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/repeat-it/6764277864</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/fool-proof/1892466004</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/crisco/6763369506</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/absolution/1884987651</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/jesus-is-alive/6767694896</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/something-to-lose/6766964605</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/too-busy-missing-you/6766604915</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/f-stop-blues-4-track/1883173173</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/pa-lo-bonito/1886496944</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/lonely/6768757857</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/lockup/1894298102</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/young/6767698952</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/parachute/6764119241</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/little-things/6766351153</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/fish-hunt-golf-drink/6766651884</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/pageant-stage/6764125889</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/firestorm/1868827004</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/girl-next-door/6768077610</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/big-dog/1887197046</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/idea-of-love-a-colors-show/6767667046</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/heavy-serenade/1892154309</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/ddok-ddok-ddok/6764203482</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/shut-it-down/6763631128</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/together-feat-nikki-nair-jessy-lanza-prentiss/6763207821</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/cant-miss-you/1886810999</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/razorblades-and-runways/1888004809</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/massacre/1892127745</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/better-that-way/6766273199</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/apollo/6765602431</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/infinity-123/6763447312</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/aint-over-me-yet/6767283811</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/where-did-you-go/1877958504</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/i-love-you/6766999950</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/housekeeping/6766290834</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/surprise-surprise/6764842119</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/dog/1885967384</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/i-never-see-her/6764149225</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/no-god/1891187414</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/burden/6767688180</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/chico-raro/6767713536</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/whats-done-is-done/6763088629</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/round-and-round/1885665987</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/aint-that-deep/1882831449</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/emily/1893405442</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/hold/6767296480</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/flying-monkey/1894351228</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/anything-goes/1891118972</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/we-are/1894252873</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/its-for-the-kids/1867327679</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/pure-ecstasy/6762228978</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/something-wicked/6766252959</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/feel-the-funk/6763294007</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/everglades-remix/6767719584</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/walk/1892180098</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/volver-a-ti/6766258204</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/bahamas/6764695848</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/same-old-song/6762860685</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/gentle/6762828356</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/letters-of-your-name/1892919741</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/seratonin/6763447428</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/a-digital-touch/6765592539</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/dead-mans-dog/6763447424</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/fault-of-god/1887702403</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/zone-feat-poppy-baskcomb/6763982867</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/word-vomit/1887315297</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/evil-in-this-house/1892398371</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/heaven-on-high/1881724153</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E94" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week03/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/ego/6769207667</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/hit-the-wall/6766750846</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/ran-to-atlanta/6769568597</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/hoe-phase/6769556949</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/im-spent/6769551476</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/abracadabra-apple-music-live/6768201780</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/falling-out-of-love/1891161448</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/dai-dai/6768469976</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/tu-recuerdo/6763660843</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/traitor-roles-reversed/6767665959</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/dirty-rosie/6767044374</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/2-hard-4-the-radio/6769568610</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/cheetah-print/6769557055</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/wnba/6769551471</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/shadow-of-a-man-apple-music-live/6768201925</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/epa/6768420253</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/im-your-girl-right/6766440186</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/fu%C3%ABgo/6767661766</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/jajaja/6766341319</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/find-god-feat-dominic-fike/1894315529</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/fool-me-once-feat-leon-thomas/1891467239</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/shabang/6769568598</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/road-trips/6769557053</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/fortworth/6769551482</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/repeat-it/6764277864</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/fool-proof/1892466004</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/crisco/6763369506</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/absolution/1884987651</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/jesus-is-alive/6767694896</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/something-to-lose/6766964605</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/too-busy-missing-you/6766604915</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/f-stop-blues-4-track/1883173173</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/pa-lo-bonito/1886496944</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/lonely/6768757857</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/lockup/1894298102</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/young/6767698952</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/parachute/6764119241</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/little-things/6766351153</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/fish-hunt-golf-drink/6766651884</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/pageant-stage/6764125889</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/firestorm/1868827004</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/girl-next-door/6768077610</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/big-dog/1887197046</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/idea-of-love-a-colors-show/6767667046</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/heavy-serenade/1892154309</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/ddok-ddok-ddok/6764203482</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/shut-it-down/6763631128</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/together-feat-nikki-nair-jessy-lanza-prentiss/6763207821</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/cant-miss-you/1886810999</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/razorblades-and-runways/1888004809</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/massacre/1892127745</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/better-that-way/6766273199</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/apollo/6765602431</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/infinity-123/6763447312</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/aint-over-me-yet/6767283811</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/where-did-you-go/1877958504</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/i-love-you/6766999950</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/housekeeping/6766290834</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/surprise-surprise/6764842119</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/dog/1885967384</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/i-never-see-her/6764149225</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/no-god/1891187414</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/burden/6767688180</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/chico-raro/6767713536</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/whats-done-is-done/6763088629</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/round-and-round/1885665987</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/aint-that-deep/1882831449</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/emily/1893405442</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/hold/6767296480</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/flying-monkey/1894351228</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/anything-goes/1891118972</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/we-are/1894252873</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/its-for-the-kids/1867327679</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/pure-ecstasy/6762228978</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/something-wicked/6766252959</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/feel-the-funk/6763294007</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/everglades-remix/6767719584</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/walk/1892180098</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/volver-a-ti/6766258204</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/bahamas/6764695848</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/same-old-song/6762860685</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/gentle/6762828356</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/letters-of-your-name/1892919741</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/seratonin/6763447428</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/a-digital-touch/6765592539</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/dead-mans-dog/6763447424</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/fault-of-god/1887702403</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/zone-feat-poppy-baskcomb/6763982867</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/word-vomit/1887315297</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/evil-in-this-house/1892398371</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/heaven-on-high/1881724153</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E94" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L94"/>
+  <dimension ref="A1:L95"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Ego</v>
+        <v>Do What You Gotta Do</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/ego/6769207667</v>
+        <v>https://music.apple.com/us/song/do-what-you-gotta-do/1887616424</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-20</v>
@@ -451,25 +451,25 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>Ego - Single</v>
+        <v>NeverAlways (Vol. 2)</v>
       </c>
       <c r="G2" t="str">
-        <v>2:53</v>
+        <v>3:26</v>
       </c>
       <c r="H2" t="str">
-        <v>The Warning</v>
+        <v>The Band CAMINO</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
+        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/ego/6769207665</v>
+        <v>https://music.apple.com/us/album/do-what-you-gotta-do/1887616173</v>
       </c>
       <c r="L2" t="str">
-        <v>Ego - The Warning</v>
+        <v>Do What You Gotta Do - The Band CAMINO</v>
       </c>
     </row>
     <row r="3">
@@ -778,13 +778,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Traitor (Roles Reversed)</v>
+        <v>Ego</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>https://music.apple.com/us/song/traitor-roles-reversed/6767665959</v>
+        <v>https://music.apple.com/us/song/ego/6769207667</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-20</v>
@@ -793,36 +793,36 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>Cloud 9</v>
+        <v>Ego - Single</v>
       </c>
       <c r="G11" t="str">
-        <v>3:27</v>
+        <v>2:53</v>
       </c>
       <c r="H11" t="str">
-        <v>Megan Moroney</v>
+        <v>The Warning</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K11" t="str">
-        <v>https://music.apple.com/us/album/traitor-roles-reversed/6767665713</v>
+        <v>https://music.apple.com/us/album/ego/6769207665</v>
       </c>
       <c r="L11" t="str">
-        <v>Traitor (Roles Reversed) - Megan Moroney</v>
+        <v>Ego - The Warning</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Dirty Rosie</v>
+        <v>Traitor (Roles Reversed)</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>https://music.apple.com/us/song/dirty-rosie/6767044374</v>
+        <v>https://music.apple.com/us/song/traitor-roles-reversed/6767665959</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-20</v>
@@ -831,36 +831,36 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>Little Miss Twain</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G12" t="str">
-        <v>2:46</v>
+        <v>3:27</v>
       </c>
       <c r="H12" t="str">
-        <v>Shania Twain</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
-        <v>https://music.apple.com/us/artist/shania-twain/129974</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K12" t="str">
-        <v>https://music.apple.com/us/album/dirty-rosie/1896356105</v>
+        <v>https://music.apple.com/us/album/traitor-roles-reversed/6767665713</v>
       </c>
       <c r="L12" t="str">
-        <v>Dirty Rosie - Shania Twain</v>
+        <v>Traitor (Roles Reversed) - Megan Moroney</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Like you mean it</v>
+        <v>Dirty Rosie</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
+        <v>https://music.apple.com/us/song/dirty-rosie/6767044374</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-20</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>When the lights turn on</v>
+        <v>Little Miss Twain</v>
       </c>
       <c r="G13" t="str">
-        <v>2:27</v>
+        <v>2:46</v>
       </c>
       <c r="H13" t="str">
-        <v>MICO</v>
+        <v>Shania Twain</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/mico/1457367370</v>
+        <v>https://music.apple.com/us/artist/shania-twain/129974</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/like-you-mean-it/6767024688</v>
+        <v>https://music.apple.com/us/album/dirty-rosie/1896356105</v>
       </c>
       <c r="L13" t="str">
-        <v>Like you mean it - MICO</v>
+        <v>Dirty Rosie - Shania Twain</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Hardy (feat. Clairo)</v>
+        <v>Like you mean it</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
+        <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-20</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>American Stories</v>
+        <v>When the lights turn on</v>
       </c>
       <c r="G14" t="str">
-        <v>3:53</v>
+        <v>2:27</v>
       </c>
       <c r="H14" t="str">
-        <v>Rostam</v>
+        <v>MICO</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/mico/1457367370</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/hardy-feat-clairo/1876952750</v>
+        <v>https://music.apple.com/us/album/like-you-mean-it/6767024688</v>
       </c>
       <c r="L14" t="str">
-        <v>Hardy (feat. Clairo) - Rostam</v>
+        <v>Like you mean it - MICO</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2 Hard 4 The Radio</v>
+        <v>Hardy (feat. Clairo)</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/2-hard-4-the-radio/6769568610</v>
+        <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-20</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>ICEMAN</v>
+        <v>American Stories</v>
       </c>
       <c r="G15" t="str">
-        <v>3:03</v>
+        <v>3:53</v>
       </c>
       <c r="H15" t="str">
-        <v>Drake</v>
+        <v>Rostam</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/drake/271256</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/2-hard-4-the-radio/6769568449</v>
+        <v>https://music.apple.com/us/album/hardy-feat-clairo/1876952750</v>
       </c>
       <c r="L15" t="str">
-        <v>2 Hard 4 The Radio - Drake</v>
+        <v>Hardy (feat. Clairo) - Rostam</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Cheetah Print</v>
+        <v>2 Hard 4 The Radio</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/cheetah-print/6769557055</v>
+        <v>https://music.apple.com/us/song/2-hard-4-the-radio/6769568610</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-20</v>
@@ -983,10 +983,10 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>MAID OF HONOUR</v>
+        <v>ICEMAN</v>
       </c>
       <c r="G16" t="str">
-        <v>3:22</v>
+        <v>3:03</v>
       </c>
       <c r="H16" t="str">
         <v>Drake</v>
@@ -998,21 +998,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/cheetah-print/6769556940</v>
+        <v>https://music.apple.com/us/album/2-hard-4-the-radio/6769568449</v>
       </c>
       <c r="L16" t="str">
-        <v>Cheetah Print - Drake</v>
+        <v>2 Hard 4 The Radio - Drake</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>WNBA</v>
+        <v>Cheetah Print</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/wnba/6769551471</v>
+        <v>https://music.apple.com/us/song/cheetah-print/6769557055</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-20</v>
@@ -1021,10 +1021,10 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>HABIBTI</v>
+        <v>MAID OF HONOUR</v>
       </c>
       <c r="G17" t="str">
-        <v>2:58</v>
+        <v>3:22</v>
       </c>
       <c r="H17" t="str">
         <v>Drake</v>
@@ -1036,21 +1036,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/wnba/6769551464</v>
+        <v>https://music.apple.com/us/album/cheetah-print/6769556940</v>
       </c>
       <c r="L17" t="str">
-        <v>WNBA - Drake</v>
+        <v>Cheetah Print - Drake</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Shadow Of A Man (Apple Music Live)</v>
+        <v>WNBA</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/shadow-of-a-man-apple-music-live/6768201925</v>
+        <v>https://music.apple.com/us/song/wnba/6769551471</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-20</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Apple Music Live: MAYHEM Requiem</v>
+        <v>HABIBTI</v>
       </c>
       <c r="G18" t="str">
-        <v>3:36</v>
+        <v>2:58</v>
       </c>
       <c r="H18" t="str">
-        <v>Lady Gaga</v>
+        <v>Drake</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/shadow-of-a-man-apple-music-live/6768201775</v>
+        <v>https://music.apple.com/us/album/wnba/6769551464</v>
       </c>
       <c r="L18" t="str">
-        <v>Shadow Of A Man (Apple Music Live) - Lady Gaga</v>
+        <v>WNBA - Drake</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>EPA</v>
+        <v>Shadow Of A Man (Apple Music Live)</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/epa/6768420253</v>
+        <v>https://music.apple.com/us/song/shadow-of-a-man-apple-music-live/6768201925</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-20</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>EPA - Single</v>
+        <v>Apple Music Live: MAYHEM Requiem</v>
       </c>
       <c r="G19" t="str">
-        <v>3:22</v>
+        <v>3:36</v>
       </c>
       <c r="H19" t="str">
-        <v>Becky G</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
+        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/epa/6768420251</v>
+        <v>https://music.apple.com/us/album/shadow-of-a-man-apple-music-live/6768201775</v>
       </c>
       <c r="L19" t="str">
-        <v>EPA - Becky G</v>
+        <v>Shadow Of A Man (Apple Music Live) - Lady Gaga</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>I’m your girl right?</v>
+        <v>EPA</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/im-your-girl-right/6766440186</v>
+        <v>https://music.apple.com/us/song/epa/6768420253</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-20</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>ESTRUS</v>
+        <v>EPA - Single</v>
       </c>
       <c r="G20" t="str">
-        <v>2:49</v>
+        <v>3:22</v>
       </c>
       <c r="H20" t="str">
-        <v>Tove Lo</v>
+        <v>Becky G</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/tove-lo/570136838</v>
+        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/im-your-girl-right/6766440172</v>
+        <v>https://music.apple.com/us/album/epa/6768420251</v>
       </c>
       <c r="L20" t="str">
-        <v>I’m your girl right? - Tove Lo</v>
+        <v>EPA - Becky G</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>fuëgo</v>
+        <v>I’m your girl right?</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/fu%C3%ABgo/6767661766</v>
+        <v>https://music.apple.com/us/song/im-your-girl-right/6766440186</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-20</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>fuëgo - Single</v>
+        <v>ESTRUS</v>
       </c>
       <c r="G21" t="str">
-        <v>3:46</v>
+        <v>2:49</v>
       </c>
       <c r="H21" t="str">
-        <v>BNYX®</v>
+        <v>Tove Lo</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/bnyx/1438325287</v>
+        <v>https://music.apple.com/us/artist/tove-lo/570136838</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/fu%C3%ABgo/6767661604</v>
+        <v>https://music.apple.com/us/album/im-your-girl-right/6766440172</v>
       </c>
       <c r="L21" t="str">
-        <v>fuëgo - BNYX®</v>
+        <v>I’m your girl right? - Tove Lo</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>jajaja</v>
+        <v>fuëgo</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/jajaja/6766341319</v>
+        <v>https://music.apple.com/us/song/fu%C3%ABgo/6767661766</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-20</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>jajaja - Single</v>
+        <v>fuëgo - Single</v>
       </c>
       <c r="G22" t="str">
-        <v>2:45</v>
+        <v>3:46</v>
       </c>
       <c r="H22" t="str">
-        <v>Chino Pacas</v>
+        <v>BNYX®</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
+        <v>https://music.apple.com/us/artist/bnyx/1438325287</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/jajaja/6766341318</v>
+        <v>https://music.apple.com/us/album/fu%C3%ABgo/6767661604</v>
       </c>
       <c r="L22" t="str">
-        <v>jajaja - Chino Pacas</v>
+        <v>fuëgo - BNYX®</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>FIND GOD (feat. Dominic Fike)</v>
+        <v>jajaja</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/find-god-feat-dominic-fike/1894315529</v>
+        <v>https://music.apple.com/us/song/jajaja/6766341319</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-20</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>BULLDAWG</v>
+        <v>jajaja - Single</v>
       </c>
       <c r="G23" t="str">
-        <v>3:59</v>
+        <v>2:45</v>
       </c>
       <c r="H23" t="str">
-        <v>Kenny Mason</v>
+        <v>Chino Pacas</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/kenny-mason/79382206</v>
+        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/find-god-feat-dominic-fike/1894315301</v>
+        <v>https://music.apple.com/us/album/jajaja/6766341318</v>
       </c>
       <c r="L23" t="str">
-        <v>FIND GOD (feat. Dominic Fike) - Kenny Mason</v>
+        <v>jajaja - Chino Pacas</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>FOOL ME ONCE (feat. Leon Thomas)</v>
+        <v>FIND GOD (feat. Dominic Fike)</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/fool-me-once-feat-leon-thomas/1891467239</v>
+        <v>https://music.apple.com/us/song/find-god-feat-dominic-fike/1894315529</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-20</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>BELOVED: ACT II</v>
+        <v>BULLDAWG</v>
       </c>
       <c r="G24" t="str">
-        <v>3:18</v>
+        <v>3:59</v>
       </c>
       <c r="H24" t="str">
-        <v>GIVĒON</v>
+        <v>Kenny Mason</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/giv%C4%93on/1070668868</v>
+        <v>https://music.apple.com/us/artist/kenny-mason/79382206</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/fool-me-once-feat-leon-thomas/1891467233</v>
+        <v>https://music.apple.com/us/album/find-god-feat-dominic-fike/1894315301</v>
       </c>
       <c r="L24" t="str">
-        <v>FOOL ME ONCE (feat. Leon Thomas) - GIVĒON</v>
+        <v>FIND GOD (feat. Dominic Fike) - Kenny Mason</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Shabang</v>
+        <v>FOOL ME ONCE (feat. Leon Thomas)</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/shabang/6769568598</v>
+        <v>https://music.apple.com/us/song/fool-me-once-feat-leon-thomas/1891467239</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-20</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>ICEMAN</v>
+        <v>BELOVED: ACT II</v>
       </c>
       <c r="G25" t="str">
-        <v>3:08</v>
+        <v>3:18</v>
       </c>
       <c r="H25" t="str">
-        <v>Drake</v>
+        <v>GIVĒON</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/drake/271256</v>
+        <v>https://music.apple.com/us/artist/giv%C4%93on/1070668868</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/shabang/6769568449</v>
+        <v>https://music.apple.com/us/album/fool-me-once-feat-leon-thomas/1891467233</v>
       </c>
       <c r="L25" t="str">
-        <v>Shabang - Drake</v>
+        <v>FOOL ME ONCE (feat. Leon Thomas) - GIVĒON</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Road Trips</v>
+        <v>Shabang</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/road-trips/6769557053</v>
+        <v>https://music.apple.com/us/song/shabang/6769568598</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-20</v>
@@ -1363,10 +1363,10 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>MAID OF HONOUR</v>
+        <v>ICEMAN</v>
       </c>
       <c r="G26" t="str">
-        <v>4:03</v>
+        <v>3:08</v>
       </c>
       <c r="H26" t="str">
         <v>Drake</v>
@@ -1378,21 +1378,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/road-trips/6769556940</v>
+        <v>https://music.apple.com/us/album/shabang/6769568449</v>
       </c>
       <c r="L26" t="str">
-        <v>Road Trips - Drake</v>
+        <v>Shabang - Drake</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Fortworth</v>
+        <v>Road Trips</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/fortworth/6769551482</v>
+        <v>https://music.apple.com/us/song/road-trips/6769557053</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-20</v>
@@ -1401,10 +1401,10 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>HABIBTI</v>
+        <v>MAID OF HONOUR</v>
       </c>
       <c r="G27" t="str">
-        <v>3:51</v>
+        <v>4:03</v>
       </c>
       <c r="H27" t="str">
         <v>Drake</v>
@@ -1416,21 +1416,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/fortworth/6769551464</v>
+        <v>https://music.apple.com/us/album/road-trips/6769556940</v>
       </c>
       <c r="L27" t="str">
-        <v>Fortworth - Drake</v>
+        <v>Road Trips - Drake</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Repeat It</v>
+        <v>Fortworth</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/repeat-it/6764277864</v>
+        <v>https://music.apple.com/us/song/fortworth/6769551482</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-20</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>Repeat It - Single</v>
+        <v>HABIBTI</v>
       </c>
       <c r="G28" t="str">
-        <v>3:11</v>
+        <v>3:51</v>
       </c>
       <c r="H28" t="str">
-        <v>Martin Garrix</v>
+        <v>Drake</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/repeat-it/1895713789</v>
+        <v>https://music.apple.com/us/album/fortworth/6769551464</v>
       </c>
       <c r="L28" t="str">
-        <v>Repeat It - Martin Garrix</v>
+        <v>Fortworth - Drake</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Fool Proof</v>
+        <v>Repeat It</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/fool-proof/1892466004</v>
+        <v>https://music.apple.com/us/song/repeat-it/6764277864</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-20</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>Repeat It - Single</v>
       </c>
       <c r="G29" t="str">
-        <v>2:36</v>
+        <v>3:11</v>
       </c>
       <c r="H29" t="str">
-        <v>Cody Johnson</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/fool-proof/1892465981</v>
+        <v>https://music.apple.com/us/album/repeat-it/1895713789</v>
       </c>
       <c r="L29" t="str">
-        <v>Fool Proof - Cody Johnson</v>
+        <v>Repeat It - Martin Garrix</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Crisco</v>
+        <v>Fool Proof</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/crisco/6763369506</v>
+        <v>https://music.apple.com/us/song/fool-proof/1892466004</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-20</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>Crisco - Single</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G30" t="str">
-        <v>2:56</v>
+        <v>2:36</v>
       </c>
       <c r="H30" t="str">
-        <v>Miranda Lambert</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/miranda-lambert/18732261</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/crisco/1895284236</v>
+        <v>https://music.apple.com/us/album/fool-proof/1892465981</v>
       </c>
       <c r="L30" t="str">
-        <v>Crisco - Miranda Lambert</v>
+        <v>Fool Proof - Cody Johnson</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Absolution</v>
+        <v>Crisco</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/absolution/1884987651</v>
+        <v>https://music.apple.com/us/song/crisco/6763369506</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-20</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>Forever Now</v>
+        <v>Crisco - Single</v>
       </c>
       <c r="G31" t="str">
-        <v>4:05</v>
+        <v>2:56</v>
       </c>
       <c r="H31" t="str">
-        <v>Switchfoot</v>
+        <v>Miranda Lambert</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
+        <v>https://music.apple.com/us/artist/miranda-lambert/18732261</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/absolution/1884987638</v>
+        <v>https://music.apple.com/us/album/crisco/1895284236</v>
       </c>
       <c r="L31" t="str">
-        <v>Absolution - Switchfoot</v>
+        <v>Crisco - Miranda Lambert</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>JESUS IS ALIVE</v>
+        <v>Absolution</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/jesus-is-alive/6767694896</v>
+        <v>https://music.apple.com/us/song/absolution/1884987651</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-20</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>JESUS IS ALIVE - Single</v>
+        <v>Forever Now</v>
       </c>
       <c r="G32" t="str">
-        <v>2:08</v>
+        <v>4:05</v>
       </c>
       <c r="H32" t="str">
-        <v>Forrest Frank</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
+        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/jesus-is-alive/6767694895</v>
+        <v>https://music.apple.com/us/album/absolution/1884987638</v>
       </c>
       <c r="L32" t="str">
-        <v>JESUS IS ALIVE - Forrest Frank</v>
+        <v>Absolution - Switchfoot</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Something To Lose</v>
+        <v>JESUS IS ALIVE</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/something-to-lose/6766964605</v>
+        <v>https://music.apple.com/us/song/jesus-is-alive/6767694896</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-20</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>Is This Heaven? - EP</v>
+        <v>JESUS IS ALIVE - Single</v>
       </c>
       <c r="G33" t="str">
-        <v>2:55</v>
+        <v>2:08</v>
       </c>
       <c r="H33" t="str">
-        <v>STELLA LEFTY</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/something-to-lose/6766964604</v>
+        <v>https://music.apple.com/us/album/jesus-is-alive/6767694895</v>
       </c>
       <c r="L33" t="str">
-        <v>Something To Lose - STELLA LEFTY</v>
+        <v>JESUS IS ALIVE - Forrest Frank</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Too Busy Missing You</v>
+        <v>Something To Lose</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/too-busy-missing-you/6766604915</v>
+        <v>https://music.apple.com/us/song/something-to-lose/6766964605</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-20</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>Off Campus: The Mixtape</v>
+        <v>Is This Heaven? - EP</v>
       </c>
       <c r="G34" t="str">
-        <v>3:25</v>
+        <v>2:55</v>
       </c>
       <c r="H34" t="str">
-        <v>Asha Banks</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/too-busy-missing-you/6766604455</v>
+        <v>https://music.apple.com/us/album/something-to-lose/6766964604</v>
       </c>
       <c r="L34" t="str">
-        <v>Too Busy Missing You - Asha Banks</v>
+        <v>Something To Lose - STELLA LEFTY</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>F-Stop Blues (4-track)</v>
+        <v>Too Busy Missing You</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/f-stop-blues-4-track/1883173173</v>
+        <v>https://music.apple.com/us/song/too-busy-missing-you/6766604915</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-20</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>Off Campus: The Mixtape</v>
       </c>
       <c r="G35" t="str">
-        <v>3:00</v>
+        <v>3:25</v>
       </c>
       <c r="H35" t="str">
-        <v>Jack Johnson</v>
+        <v>Asha Banks</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/f-stop-blues-4-track/1883172879</v>
+        <v>https://music.apple.com/us/album/too-busy-missing-you/6766604455</v>
       </c>
       <c r="L35" t="str">
-        <v>F-Stop Blues (4-track) - Jack Johnson</v>
+        <v>Too Busy Missing You - Asha Banks</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>PA' LO BONITO</v>
+        <v>F-Stop Blues (4-track)</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/pa-lo-bonito/1886496944</v>
+        <v>https://music.apple.com/us/song/f-stop-blues-4-track/1883173173</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-20</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>PA' LO BONITO - Single</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G36" t="str">
-        <v>3:04</v>
+        <v>3:00</v>
       </c>
       <c r="H36" t="str">
-        <v>Lenny Tavárez</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/pa-lo-bonito/1886496943</v>
+        <v>https://music.apple.com/us/album/f-stop-blues-4-track/1883172879</v>
       </c>
       <c r="L36" t="str">
-        <v>PA' LO BONITO - Lenny Tavárez</v>
+        <v>F-Stop Blues (4-track) - Jack Johnson</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>LONELY</v>
+        <v>PA' LO BONITO</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/lonely/6768757857</v>
+        <v>https://music.apple.com/us/song/pa-lo-bonito/1886496944</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-20</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>DESEO</v>
+        <v>PA' LO BONITO - Single</v>
       </c>
       <c r="G37" t="str">
-        <v>2:58</v>
+        <v>3:04</v>
       </c>
       <c r="H37" t="str">
-        <v>Katteyes</v>
+        <v>Lenny Tavárez</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/katteyes/1648818255</v>
+        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/lonely/6768757414</v>
+        <v>https://music.apple.com/us/album/pa-lo-bonito/1886496943</v>
       </c>
       <c r="L37" t="str">
-        <v>LONELY - Katteyes</v>
+        <v>PA' LO BONITO - Lenny Tavárez</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Lockup</v>
+        <v>LONELY</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/lockup/1894298102</v>
+        <v>https://music.apple.com/us/song/lonely/6768757857</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-20</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Pure Devotion</v>
+        <v>DESEO</v>
       </c>
       <c r="G38" t="str">
-        <v>4:31</v>
+        <v>2:58</v>
       </c>
       <c r="H38" t="str">
-        <v>Overmono</v>
+        <v>Katteyes</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/overmono/1129806758</v>
+        <v>https://music.apple.com/us/artist/katteyes/1648818255</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/lockup/1894298100</v>
+        <v>https://music.apple.com/us/album/lonely/6768757414</v>
       </c>
       <c r="L38" t="str">
-        <v>Lockup - Overmono</v>
+        <v>LONELY - Katteyes</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Young</v>
+        <v>Lockup</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/young/6767698952</v>
+        <v>https://music.apple.com/us/song/lockup/1894298102</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-20</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>Young</v>
+        <v>Pure Devotion</v>
       </c>
       <c r="G39" t="str">
-        <v>2:46</v>
+        <v>4:31</v>
       </c>
       <c r="H39" t="str">
-        <v>Dan + Shay</v>
+        <v>Overmono</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/dan-shay/690319057</v>
+        <v>https://music.apple.com/us/artist/overmono/1129806758</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/young/6767698951</v>
+        <v>https://music.apple.com/us/album/lockup/1894298100</v>
       </c>
       <c r="L39" t="str">
-        <v>Young - Dan + Shay</v>
+        <v>Lockup - Overmono</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Parachute</v>
+        <v>Young</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/parachute/6764119241</v>
+        <v>https://music.apple.com/us/song/young/6767698952</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-20</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Parachute - Single</v>
+        <v>Young</v>
       </c>
       <c r="G40" t="str">
-        <v>2:52</v>
+        <v>2:46</v>
       </c>
       <c r="H40" t="str">
-        <v>Maren Morris</v>
+        <v>Dan + Shay</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/maren-morris/262260873</v>
+        <v>https://music.apple.com/us/artist/dan-shay/690319057</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/parachute/1895648983</v>
+        <v>https://music.apple.com/us/album/young/6767698951</v>
       </c>
       <c r="L40" t="str">
-        <v>Parachute - Maren Morris</v>
+        <v>Young - Dan + Shay</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Little Things</v>
+        <v>Parachute</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/little-things/6766351153</v>
+        <v>https://music.apple.com/us/song/parachute/6764119241</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-20</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Little Things - Single</v>
+        <v>Parachute - Single</v>
       </c>
       <c r="G41" t="str">
-        <v>2:55</v>
+        <v>2:52</v>
       </c>
       <c r="H41" t="str">
-        <v>Kevin Jonas</v>
+        <v>Maren Morris</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/kevin-jonas/21138190</v>
+        <v>https://music.apple.com/us/artist/maren-morris/262260873</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/little-things/6766350882</v>
+        <v>https://music.apple.com/us/album/parachute/1895648983</v>
       </c>
       <c r="L41" t="str">
-        <v>Little Things - Kevin Jonas</v>
+        <v>Parachute - Maren Morris</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Fish Hunt Golf Drink</v>
+        <v>Little Things</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/fish-hunt-golf-drink/6766651884</v>
+        <v>https://music.apple.com/us/song/little-things/6766351153</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-20</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Signs</v>
+        <v>Little Things - Single</v>
       </c>
       <c r="G42" t="str">
-        <v>2:34</v>
+        <v>2:55</v>
       </c>
       <c r="H42" t="str">
-        <v>Luke Bryan</v>
+        <v>Kevin Jonas</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
+        <v>https://music.apple.com/us/artist/kevin-jonas/21138190</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/fish-hunt-golf-drink/6766651878</v>
+        <v>https://music.apple.com/us/album/little-things/6766350882</v>
       </c>
       <c r="L42" t="str">
-        <v>Fish Hunt Golf Drink - Luke Bryan</v>
+        <v>Little Things - Kevin Jonas</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>PAGEANT STAGE</v>
+        <v>Fish Hunt Golf Drink</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/pageant-stage/6764125889</v>
+        <v>https://music.apple.com/us/song/fish-hunt-golf-drink/6766651884</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-20</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>THE EDGE</v>
+        <v>Signs</v>
       </c>
       <c r="G43" t="str">
-        <v>2:52</v>
+        <v>2:34</v>
       </c>
       <c r="H43" t="str">
-        <v>Tone Stith</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/tone-stith/1167717310</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/pageant-stage/1895651504</v>
+        <v>https://music.apple.com/us/album/fish-hunt-golf-drink/6766651878</v>
       </c>
       <c r="L43" t="str">
-        <v>PAGEANT STAGE - Tone Stith</v>
+        <v>Fish Hunt Golf Drink - Luke Bryan</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Firestorm</v>
+        <v>PAGEANT STAGE</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/firestorm/1868827004</v>
+        <v>https://music.apple.com/us/song/pageant-stage/6764125889</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-20</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>Of Earth &amp; Wires</v>
+        <v>THE EDGE</v>
       </c>
       <c r="G44" t="str">
-        <v>2:29</v>
+        <v>2:52</v>
       </c>
       <c r="H44" t="str">
-        <v>Dua Saleh</v>
+        <v>Tone Stith</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
+        <v>https://music.apple.com/us/artist/tone-stith/1167717310</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/firestorm/1868826829</v>
+        <v>https://music.apple.com/us/album/pageant-stage/1895651504</v>
       </c>
       <c r="L44" t="str">
-        <v>Firestorm - Dua Saleh</v>
+        <v>PAGEANT STAGE - Tone Stith</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>girl next door</v>
+        <v>Firestorm</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/girl-next-door/6768077610</v>
+        <v>https://music.apple.com/us/song/firestorm/1868827004</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-20</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>girl next door - Single</v>
+        <v>Of Earth &amp; Wires</v>
       </c>
       <c r="G45" t="str">
-        <v>3:18</v>
+        <v>2:29</v>
       </c>
       <c r="H45" t="str">
-        <v>mgk</v>
+        <v>Dua Saleh</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/mgk/465954501</v>
+        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/girl-next-door/6768077609</v>
+        <v>https://music.apple.com/us/album/firestorm/1868826829</v>
       </c>
       <c r="L45" t="str">
-        <v>girl next door - mgk</v>
+        <v>Firestorm - Dua Saleh</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>BIG DOG</v>
+        <v>girl next door</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/big-dog/1887197046</v>
+        <v>https://music.apple.com/us/song/girl-next-door/6768077610</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-20</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
+        <v>girl next door - Single</v>
       </c>
       <c r="G46" t="str">
-        <v>3:36</v>
+        <v>3:18</v>
       </c>
       <c r="H46" t="str">
-        <v>Genesis Owusu</v>
+        <v>mgk</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
+        <v>https://music.apple.com/us/artist/mgk/465954501</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/big-dog/1887196431</v>
+        <v>https://music.apple.com/us/album/girl-next-door/6768077609</v>
       </c>
       <c r="L46" t="str">
-        <v>BIG DOG - Genesis Owusu</v>
+        <v>girl next door - mgk</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>idea of love - A COLORS SHOW</v>
+        <v>BIG DOG</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/idea-of-love-a-colors-show/6767667046</v>
+        <v>https://music.apple.com/us/song/big-dog/1887197046</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-20</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>idea of love - A COLORS SHOW - Single</v>
+        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
       </c>
       <c r="G47" t="str">
-        <v>2:34</v>
+        <v>3:36</v>
       </c>
       <c r="H47" t="str">
-        <v>kwn</v>
+        <v>Genesis Owusu</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
+        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/idea-of-love-a-colors-show/6767666835</v>
+        <v>https://music.apple.com/us/album/big-dog/1887196431</v>
       </c>
       <c r="L47" t="str">
-        <v>idea of love - A COLORS SHOW - kwn</v>
+        <v>BIG DOG - Genesis Owusu</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Heavy Serenade</v>
+        <v>idea of love - A COLORS SHOW</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/heavy-serenade/1892154309</v>
+        <v>https://music.apple.com/us/song/idea-of-love-a-colors-show/6767667046</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-20</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>Heavy Serenade - EP</v>
+        <v>idea of love - A COLORS SHOW - Single</v>
       </c>
       <c r="G48" t="str">
-        <v>3:00</v>
+        <v>2:34</v>
       </c>
       <c r="H48" t="str">
-        <v>NMIXX</v>
+        <v>kwn</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
+        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/heavy-serenade/1892154305</v>
+        <v>https://music.apple.com/us/album/idea-of-love-a-colors-show/6767666835</v>
       </c>
       <c r="L48" t="str">
-        <v>Heavy Serenade - NMIXX</v>
+        <v>idea of love - A COLORS SHOW - kwn</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ddok ddok ddok</v>
+        <v>Heavy Serenade</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/ddok-ddok-ddok/6764203482</v>
+        <v>https://music.apple.com/us/song/heavy-serenade/1892154309</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-20</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>ddok ddok ddok - Single</v>
+        <v>Heavy Serenade - EP</v>
       </c>
       <c r="G49" t="str">
-        <v>2:35</v>
+        <v>3:00</v>
       </c>
       <c r="H49" t="str">
-        <v>BOYNEXTDOOR</v>
+        <v>NMIXX</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/boynextdoor/1687612559</v>
+        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/ddok-ddok-ddok/6764203481</v>
+        <v>https://music.apple.com/us/album/heavy-serenade/1892154305</v>
       </c>
       <c r="L49" t="str">
-        <v>ddok ddok ddok - BOYNEXTDOOR</v>
+        <v>Heavy Serenade - NMIXX</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Shut It Down</v>
+        <v>ddok ddok ddok</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/shut-it-down/6763631128</v>
+        <v>https://music.apple.com/us/song/ddok-ddok-ddok/6764203482</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-20</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Shut It Down - Single</v>
+        <v>ddok ddok ddok - Single</v>
       </c>
       <c r="G50" t="str">
-        <v>3:32</v>
+        <v>2:35</v>
       </c>
       <c r="H50" t="str">
-        <v>Boys Noize</v>
+        <v>BOYNEXTDOOR</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/boys-noize/60393190</v>
+        <v>https://music.apple.com/us/artist/boynextdoor/1687612559</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/shut-it-down/1895408470</v>
+        <v>https://music.apple.com/us/album/ddok-ddok-ddok/6764203481</v>
       </c>
       <c r="L50" t="str">
-        <v>Shut It Down - Boys Noize</v>
+        <v>ddok ddok ddok - BOYNEXTDOOR</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss)</v>
+        <v>Shut It Down</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/together-feat-nikki-nair-jessy-lanza-prentiss/6763207821</v>
+        <v>https://music.apple.com/us/song/shut-it-down/6763631128</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-20</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss) - Single</v>
+        <v>Shut It Down - Single</v>
       </c>
       <c r="G51" t="str">
-        <v>3:18</v>
+        <v>3:32</v>
       </c>
       <c r="H51" t="str">
-        <v>The Avalanches</v>
+        <v>Boys Noize</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
+        <v>https://music.apple.com/us/artist/boys-noize/60393190</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/together-feat-nikki-nair-jessy-lanza-prentiss/1895215105</v>
+        <v>https://music.apple.com/us/album/shut-it-down/1895408470</v>
       </c>
       <c r="L51" t="str">
-        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss) - The Avalanches</v>
+        <v>Shut It Down - Boys Noize</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Can’t Miss You</v>
+        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss)</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/cant-miss-you/1886810999</v>
+        <v>https://music.apple.com/us/song/together-feat-nikki-nair-jessy-lanza-prentiss/6763207821</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-20</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss) - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>2:32</v>
+        <v>3:18</v>
       </c>
       <c r="H52" t="str">
-        <v>Sublime</v>
+        <v>The Avalanches</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/sublime/63480</v>
+        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/cant-miss-you/1886810990</v>
+        <v>https://music.apple.com/us/album/together-feat-nikki-nair-jessy-lanza-prentiss/1895215105</v>
       </c>
       <c r="L52" t="str">
-        <v>Can’t Miss You - Sublime</v>
+        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss) - The Avalanches</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Razorblades And Runways</v>
+        <v>Can’t Miss You</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/razorblades-and-runways/1888004809</v>
+        <v>https://music.apple.com/us/song/cant-miss-you/1886810999</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-20</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>Get It Honest</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="G53" t="str">
-        <v>3:33</v>
+        <v>2:32</v>
       </c>
       <c r="H53" t="str">
-        <v>The Revivalists</v>
+        <v>Sublime</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
+        <v>https://music.apple.com/us/artist/sublime/63480</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/razorblades-and-runways/1888004802</v>
+        <v>https://music.apple.com/us/album/cant-miss-you/1886810990</v>
       </c>
       <c r="L53" t="str">
-        <v>Razorblades And Runways - The Revivalists</v>
+        <v>Can’t Miss You - Sublime</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Massacre</v>
+        <v>Razorblades And Runways</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/massacre/1892127745</v>
+        <v>https://music.apple.com/us/song/razorblades-and-runways/1888004809</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-20</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>Massacre - Single</v>
+        <v>Get It Honest</v>
       </c>
       <c r="G54" t="str">
-        <v>2:55</v>
+        <v>3:33</v>
       </c>
       <c r="H54" t="str">
-        <v>Murex</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/murex/1607430925</v>
+        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/massacre/1892127742</v>
+        <v>https://music.apple.com/us/album/razorblades-and-runways/1888004802</v>
       </c>
       <c r="L54" t="str">
-        <v>Massacre - Murex</v>
+        <v>Razorblades And Runways - The Revivalists</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Better That Way</v>
+        <v>Massacre</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/better-that-way/6766273199</v>
+        <v>https://music.apple.com/us/song/massacre/1892127745</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-20</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Christian Name</v>
+        <v>Massacre - Single</v>
       </c>
       <c r="G55" t="str">
-        <v>3:45</v>
+        <v>2:55</v>
       </c>
       <c r="H55" t="str">
-        <v>Charles Wesley Godwin</v>
+        <v>Murex</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/charles-wesley-godwin/1441994025</v>
+        <v>https://music.apple.com/us/artist/murex/1607430925</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/better-that-way/1896261802</v>
+        <v>https://music.apple.com/us/album/massacre/1892127742</v>
       </c>
       <c r="L55" t="str">
-        <v>Better That Way - Charles Wesley Godwin</v>
+        <v>Massacre - Murex</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Apollo</v>
+        <v>Better That Way</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/apollo/6765602431</v>
+        <v>https://music.apple.com/us/song/better-that-way/6766273199</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-20</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>Apollo - Single</v>
+        <v>Christian Name</v>
       </c>
       <c r="G56" t="str">
-        <v>3:35</v>
+        <v>3:45</v>
       </c>
       <c r="H56" t="str">
-        <v>Bryant Barnes</v>
+        <v>Charles Wesley Godwin</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
+        <v>https://music.apple.com/us/artist/charles-wesley-godwin/1441994025</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/apollo/6765602369</v>
+        <v>https://music.apple.com/us/album/better-that-way/1896261802</v>
       </c>
       <c r="L56" t="str">
-        <v>Apollo - Bryant Barnes</v>
+        <v>Better That Way - Charles Wesley Godwin</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Infinity (123)</v>
+        <v>Apollo</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/infinity-123/6763447312</v>
+        <v>https://music.apple.com/us/song/apollo/6765602431</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-20</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>Infinity (123) - Single</v>
+        <v>Apollo - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>2:19</v>
+        <v>3:35</v>
       </c>
       <c r="H57" t="str">
-        <v>December 10</v>
+        <v>Bryant Barnes</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
+        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/infinity-123/1895320456</v>
+        <v>https://music.apple.com/us/album/apollo/6765602369</v>
       </c>
       <c r="L57" t="str">
-        <v>Infinity (123) - December 10</v>
+        <v>Apollo - Bryant Barnes</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Ain't Over Me Yet</v>
+        <v>Infinity (123)</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/aint-over-me-yet/6767283811</v>
+        <v>https://music.apple.com/us/song/infinity-123/6763447312</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-20</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>Cherry Valley Forever</v>
+        <v>Infinity (123) - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>3:24</v>
+        <v>2:19</v>
       </c>
       <c r="H58" t="str">
-        <v>Carter Faith</v>
+        <v>December 10</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/carter-faith/1489205896</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/aint-over-me-yet/1896458169</v>
+        <v>https://music.apple.com/us/album/infinity-123/1895320456</v>
       </c>
       <c r="L58" t="str">
-        <v>Ain't Over Me Yet - Carter Faith</v>
+        <v>Infinity (123) - December 10</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Where Did You Go</v>
+        <v>Ain't Over Me Yet</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/where-did-you-go/1877958504</v>
+        <v>https://music.apple.com/us/song/aint-over-me-yet/6767283811</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-20</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>Growing Pains (Deluxe)</v>
+        <v>Cherry Valley Forever</v>
       </c>
       <c r="G59" t="str">
-        <v>2:47</v>
+        <v>3:24</v>
       </c>
       <c r="H59" t="str">
-        <v>Trousdale</v>
+        <v>Carter Faith</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/carter-faith/1489205896</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/where-did-you-go/1877958112</v>
+        <v>https://music.apple.com/us/album/aint-over-me-yet/1896458169</v>
       </c>
       <c r="L59" t="str">
-        <v>Where Did You Go - Trousdale</v>
+        <v>Ain't Over Me Yet - Carter Faith</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>I LOVE YOU</v>
+        <v>Where Did You Go</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/i-love-you/6766999950</v>
+        <v>https://music.apple.com/us/song/where-did-you-go/1877958504</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-20</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>I LOVE YOU - Single</v>
+        <v>Growing Pains (Deluxe)</v>
       </c>
       <c r="G60" t="str">
-        <v>3:11</v>
+        <v>2:47</v>
       </c>
       <c r="H60" t="str">
-        <v>Noga Erez</v>
+        <v>Trousdale</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/noga-erez/1166657901</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/i-love-you/6766999949</v>
+        <v>https://music.apple.com/us/album/where-did-you-go/1877958112</v>
       </c>
       <c r="L60" t="str">
-        <v>I LOVE YOU - Noga Erez</v>
+        <v>Where Did You Go - Trousdale</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Housekeeping</v>
+        <v>I LOVE YOU</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/housekeeping/6766290834</v>
+        <v>https://music.apple.com/us/song/i-love-you/6766999950</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-20</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Housekeeping - Single</v>
+        <v>I LOVE YOU - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>3:25</v>
+        <v>3:11</v>
       </c>
       <c r="H61" t="str">
-        <v>Ally Salort</v>
+        <v>Noga Erez</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
+        <v>https://music.apple.com/us/artist/noga-erez/1166657901</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/housekeeping/6766290823</v>
+        <v>https://music.apple.com/us/album/i-love-you/6766999949</v>
       </c>
       <c r="L61" t="str">
-        <v>Housekeeping - Ally Salort</v>
+        <v>I LOVE YOU - Noga Erez</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Surprise Surprise</v>
+        <v>Housekeeping</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/surprise-surprise/6764842119</v>
+        <v>https://music.apple.com/us/song/housekeeping/6766290834</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-20</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Surprise Surprise - Single</v>
+        <v>Housekeeping - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>2:55</v>
+        <v>3:25</v>
       </c>
       <c r="H62" t="str">
-        <v>Chloe Qisha</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/surprise-surprise/1895934408</v>
+        <v>https://music.apple.com/us/album/housekeeping/6766290823</v>
       </c>
       <c r="L62" t="str">
-        <v>Surprise Surprise - Chloe Qisha</v>
+        <v>Housekeeping - Ally Salort</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Dog</v>
+        <v>Surprise Surprise</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/dog/1885967384</v>
+        <v>https://music.apple.com/us/song/surprise-surprise/6764842119</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-20</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Gentleman</v>
+        <v>Surprise Surprise - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>3:08</v>
+        <v>2:55</v>
       </c>
       <c r="H63" t="str">
-        <v>Towa Bird</v>
+        <v>Chloe Qisha</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
+        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/dog/1885967368</v>
+        <v>https://music.apple.com/us/album/surprise-surprise/1895934408</v>
       </c>
       <c r="L63" t="str">
-        <v>Dog - Towa Bird</v>
+        <v>Surprise Surprise - Chloe Qisha</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>I Never See Her</v>
+        <v>Dog</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/i-never-see-her/6764149225</v>
+        <v>https://music.apple.com/us/song/dog/1885967384</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-20</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>I Never See Her - Single</v>
+        <v>Gentleman</v>
       </c>
       <c r="G64" t="str">
-        <v>3:04</v>
+        <v>3:08</v>
       </c>
       <c r="H64" t="str">
-        <v>Spacey Jane</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
+        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/i-never-see-her/1895660748</v>
+        <v>https://music.apple.com/us/album/dog/1885967368</v>
       </c>
       <c r="L64" t="str">
-        <v>I Never See Her - Spacey Jane</v>
+        <v>Dog - Towa Bird</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>No God</v>
+        <v>I Never See Her</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/no-god/1891187414</v>
+        <v>https://music.apple.com/us/song/i-never-see-her/6764149225</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-20</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Alone Together</v>
+        <v>I Never See Her - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>2:45</v>
+        <v>3:04</v>
       </c>
       <c r="H65" t="str">
-        <v>Show Me the Body</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
+        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/no-god/1891187411</v>
+        <v>https://music.apple.com/us/album/i-never-see-her/1895660748</v>
       </c>
       <c r="L65" t="str">
-        <v>No God - Show Me the Body</v>
+        <v>I Never See Her - Spacey Jane</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>burden</v>
+        <v>No God</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/burden/6767688180</v>
+        <v>https://music.apple.com/us/song/no-god/1891187414</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-20</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>burden - Single</v>
+        <v>Alone Together</v>
       </c>
       <c r="G66" t="str">
-        <v>3:24</v>
+        <v>2:45</v>
       </c>
       <c r="H66" t="str">
-        <v>Abe Parker</v>
+        <v>Show Me the Body</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/abe-parker/490444584</v>
+        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/burden/6767688179</v>
+        <v>https://music.apple.com/us/album/no-god/1891187411</v>
       </c>
       <c r="L66" t="str">
-        <v>burden - Abe Parker</v>
+        <v>No God - Show Me the Body</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Chico Raro</v>
+        <v>burden</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/chico-raro/6767713536</v>
+        <v>https://music.apple.com/us/song/burden/6767688180</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-20</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Chico Raro - Single</v>
+        <v>burden - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>3:17</v>
+        <v>3:24</v>
       </c>
       <c r="H67" t="str">
-        <v>Arón Piper</v>
+        <v>Abe Parker</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/ar%C3%B3n-piper/691972942</v>
+        <v>https://music.apple.com/us/artist/abe-parker/490444584</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/chico-raro/6767713527</v>
+        <v>https://music.apple.com/us/album/burden/6767688179</v>
       </c>
       <c r="L67" t="str">
-        <v>Chico Raro - Arón Piper</v>
+        <v>burden - Abe Parker</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>What's Done Is Done</v>
+        <v>Chico Raro</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/whats-done-is-done/6763088629</v>
+        <v>https://music.apple.com/us/song/chico-raro/6767713536</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-20</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>What's Done Is Done - Single</v>
+        <v>Chico Raro - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>2:53</v>
+        <v>3:17</v>
       </c>
       <c r="H68" t="str">
-        <v>Jorja Smith</v>
+        <v>Arón Piper</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
+        <v>https://music.apple.com/us/artist/ar%C3%B3n-piper/691972942</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/whats-done-is-done/1895156626</v>
+        <v>https://music.apple.com/us/album/chico-raro/6767713527</v>
       </c>
       <c r="L68" t="str">
-        <v>What's Done Is Done - Jorja Smith</v>
+        <v>Chico Raro - Arón Piper</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>round and round</v>
+        <v>What's Done Is Done</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/round-and-round/1885665987</v>
+        <v>https://music.apple.com/us/song/whats-done-is-done/6763088629</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-20</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>round and round - Single</v>
+        <v>What's Done Is Done - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>2:47</v>
+        <v>2:53</v>
       </c>
       <c r="H69" t="str">
-        <v>bbno$</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
+        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/round-and-round/1885665982</v>
+        <v>https://music.apple.com/us/album/whats-done-is-done/1895156626</v>
       </c>
       <c r="L69" t="str">
-        <v>round and round - bbno$</v>
+        <v>What's Done Is Done - Jorja Smith</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Ain’t That Deep</v>
+        <v>round and round</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/aint-that-deep/1882831449</v>
+        <v>https://music.apple.com/us/song/round-and-round/1885665987</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-20</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>The Last Balloon</v>
+        <v>round and round - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>2:39</v>
+        <v>2:47</v>
       </c>
       <c r="H70" t="str">
-        <v>Tank and the Bangas</v>
+        <v>bbno$</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
+        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/aint-that-deep/1882831446</v>
+        <v>https://music.apple.com/us/album/round-and-round/1885665982</v>
       </c>
       <c r="L70" t="str">
-        <v>Ain’t That Deep - Tank and the Bangas</v>
+        <v>round and round - bbno$</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Emily</v>
+        <v>Ain’t That Deep</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/emily/1893405442</v>
+        <v>https://music.apple.com/us/song/aint-that-deep/1882831449</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-20</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>So Much To Say - EP</v>
+        <v>The Last Balloon</v>
       </c>
       <c r="G71" t="str">
-        <v>2:35</v>
+        <v>2:39</v>
       </c>
       <c r="H71" t="str">
-        <v>Daisy Grenade</v>
+        <v>Tank and the Bangas</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/daisy-grenade/1611437131</v>
+        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/emily/1893405440</v>
+        <v>https://music.apple.com/us/album/aint-that-deep/1882831446</v>
       </c>
       <c r="L71" t="str">
-        <v>Emily - Daisy Grenade</v>
+        <v>Ain’t That Deep - Tank and the Bangas</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Hold</v>
+        <v>Emily</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/hold/6767296480</v>
+        <v>https://music.apple.com/us/song/emily/1893405442</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-20</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Hold - Single</v>
+        <v>So Much To Say - EP</v>
       </c>
       <c r="G72" t="str">
-        <v>4:07</v>
+        <v>2:35</v>
       </c>
       <c r="H72" t="str">
-        <v>Sabrina Sterling</v>
+        <v>Daisy Grenade</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/sabrina-sterling/1577892147</v>
+        <v>https://music.apple.com/us/artist/daisy-grenade/1611437131</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/hold/1896462063</v>
+        <v>https://music.apple.com/us/album/emily/1893405440</v>
       </c>
       <c r="L72" t="str">
-        <v>Hold - Sabrina Sterling</v>
+        <v>Emily - Daisy Grenade</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Flying Monkey</v>
+        <v>Hold</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/flying-monkey/1894351228</v>
+        <v>https://music.apple.com/us/song/hold/6767296480</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-20</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Flying Monkey - Single</v>
+        <v>Hold - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>4:09</v>
+        <v>4:07</v>
       </c>
       <c r="H73" t="str">
-        <v>Blue Medusa</v>
+        <v>Sabrina Sterling</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
+        <v>https://music.apple.com/us/artist/sabrina-sterling/1577892147</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/flying-monkey/1894351227</v>
+        <v>https://music.apple.com/us/album/hold/1896462063</v>
       </c>
       <c r="L73" t="str">
-        <v>Flying Monkey - Blue Medusa</v>
+        <v>Hold - Sabrina Sterling</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Anything Goes</v>
+        <v>Flying Monkey</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/anything-goes/1891118972</v>
+        <v>https://music.apple.com/us/song/flying-monkey/1894351228</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-20</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>Anything Goes</v>
+        <v>Flying Monkey - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>3:00</v>
+        <v>4:09</v>
       </c>
       <c r="H74" t="str">
-        <v>Kaleena Zanders</v>
+        <v>Blue Medusa</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/anything-goes/1891118971</v>
+        <v>https://music.apple.com/us/album/flying-monkey/1894351227</v>
       </c>
       <c r="L74" t="str">
-        <v>Anything Goes - Kaleena Zanders</v>
+        <v>Flying Monkey - Blue Medusa</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>We Are</v>
+        <v>Anything Goes</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/we-are/1894252873</v>
+        <v>https://music.apple.com/us/song/anything-goes/1891118972</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-20</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>We Are - Single</v>
+        <v>Anything Goes</v>
       </c>
       <c r="G75" t="str">
-        <v>3:33</v>
+        <v>3:00</v>
       </c>
       <c r="H75" t="str">
-        <v>Adam Ten</v>
+        <v>Kaleena Zanders</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/adam-ten/1472226854</v>
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/we-are/1894252870</v>
+        <v>https://music.apple.com/us/album/anything-goes/1891118971</v>
       </c>
       <c r="L75" t="str">
-        <v>We Are - Adam Ten</v>
+        <v>Anything Goes - Kaleena Zanders</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>It's For the Kids</v>
+        <v>We Are</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/its-for-the-kids/1867327679</v>
+        <v>https://music.apple.com/us/song/we-are/1894252873</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-20</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Cursum Perficio</v>
+        <v>We Are - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>4:20</v>
+        <v>3:33</v>
       </c>
       <c r="H76" t="str">
-        <v>Anthrax</v>
+        <v>Adam Ten</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/anthrax/80417</v>
+        <v>https://music.apple.com/us/artist/adam-ten/1472226854</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/its-for-the-kids/1867327673</v>
+        <v>https://music.apple.com/us/album/we-are/1894252870</v>
       </c>
       <c r="L76" t="str">
-        <v>It's For the Kids - Anthrax</v>
+        <v>We Are - Adam Ten</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Pure Ecstasy</v>
+        <v>It's For the Kids</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/pure-ecstasy/6762228978</v>
+        <v>https://music.apple.com/us/song/its-for-the-kids/1867327679</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-20</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Pure Ecstasy</v>
+        <v>Cursum Perficio</v>
       </c>
       <c r="G77" t="str">
-        <v>3:05</v>
+        <v>4:20</v>
       </c>
       <c r="H77" t="str">
-        <v>Beartooth</v>
+        <v>Anthrax</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
+        <v>https://music.apple.com/us/artist/anthrax/80417</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/pure-ecstasy/1893453878</v>
+        <v>https://music.apple.com/us/album/its-for-the-kids/1867327673</v>
       </c>
       <c r="L77" t="str">
-        <v>Pure Ecstasy - Beartooth</v>
+        <v>It's For the Kids - Anthrax</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Something Wicked</v>
+        <v>Pure Ecstasy</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/something-wicked/6766252959</v>
+        <v>https://music.apple.com/us/song/pure-ecstasy/6762228978</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-20</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Something Wicked - Single</v>
+        <v>Pure Ecstasy</v>
       </c>
       <c r="G78" t="str">
-        <v>3:28</v>
+        <v>3:05</v>
       </c>
       <c r="H78" t="str">
-        <v>Breaking Benjamin</v>
+        <v>Beartooth</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/breaking-benjamin/3299379</v>
+        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/something-wicked/1896253678</v>
+        <v>https://music.apple.com/us/album/pure-ecstasy/1893453878</v>
       </c>
       <c r="L78" t="str">
-        <v>Something Wicked - Breaking Benjamin</v>
+        <v>Pure Ecstasy - Beartooth</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Feel The Funk</v>
+        <v>Something Wicked</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/feel-the-funk/6763294007</v>
+        <v>https://music.apple.com/us/song/something-wicked/6766252959</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-20</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>The Funk EP - Single</v>
+        <v>Something Wicked - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>3:26</v>
+        <v>3:28</v>
       </c>
       <c r="H79" t="str">
-        <v>Riordan</v>
+        <v>Breaking Benjamin</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/riordan/1517575029</v>
+        <v>https://music.apple.com/us/artist/breaking-benjamin/3299379</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/feel-the-funk/1895251685</v>
+        <v>https://music.apple.com/us/album/something-wicked/1896253678</v>
       </c>
       <c r="L79" t="str">
-        <v>Feel The Funk - Riordan</v>
+        <v>Something Wicked - Breaking Benjamin</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Everglades (Remix)</v>
+        <v>Feel The Funk</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/everglades-remix/6767719584</v>
+        <v>https://music.apple.com/us/song/feel-the-funk/6763294007</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-20</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Everglades (Remix) - Single</v>
+        <v>The Funk EP - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>2:42</v>
+        <v>3:26</v>
       </c>
       <c r="H80" t="str">
-        <v>Aziedoesntexist</v>
+        <v>Riordan</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/aziedoesntexist/1831152556</v>
+        <v>https://music.apple.com/us/artist/riordan/1517575029</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/everglades-remix/6767719577</v>
+        <v>https://music.apple.com/us/album/feel-the-funk/1895251685</v>
       </c>
       <c r="L80" t="str">
-        <v>Everglades (Remix) - Aziedoesntexist</v>
+        <v>Feel The Funk - Riordan</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Walk</v>
+        <v>Everglades (Remix)</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/walk/1892180098</v>
+        <v>https://music.apple.com/us/song/everglades-remix/6767719584</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-20</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Walk - Single</v>
+        <v>Everglades (Remix) - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>2:25</v>
+        <v>2:42</v>
       </c>
       <c r="H81" t="str">
-        <v>Melodicb</v>
+        <v>Aziedoesntexist</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/melodicb/1440206517</v>
+        <v>https://music.apple.com/us/artist/aziedoesntexist/1831152556</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/walk/1892180097</v>
+        <v>https://music.apple.com/us/album/everglades-remix/6767719577</v>
       </c>
       <c r="L81" t="str">
-        <v>Walk - Melodicb</v>
+        <v>Everglades (Remix) - Aziedoesntexist</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Volver a Ti</v>
+        <v>Walk</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/volver-a-ti/6766258204</v>
+        <v>https://music.apple.com/us/song/walk/1892180098</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-20</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Norteña</v>
+        <v>Walk - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>3:47</v>
+        <v>2:25</v>
       </c>
       <c r="H82" t="str">
-        <v>Julieta Venegas</v>
+        <v>Melodicb</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/julieta-venegas/302960</v>
+        <v>https://music.apple.com/us/artist/melodicb/1440206517</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/volver-a-ti/1896255736</v>
+        <v>https://music.apple.com/us/album/walk/1892180097</v>
       </c>
       <c r="L82" t="str">
-        <v>Volver a Ti - Julieta Venegas</v>
+        <v>Walk - Melodicb</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Bahamas</v>
+        <v>Volver a Ti</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/bahamas/6764695848</v>
+        <v>https://music.apple.com/us/song/volver-a-ti/6766258204</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-20</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Bahamas - Single</v>
+        <v>Norteña</v>
       </c>
       <c r="G83" t="str">
-        <v>2:06</v>
+        <v>3:47</v>
       </c>
       <c r="H83" t="str">
-        <v>LENCHO</v>
+        <v>Julieta Venegas</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
+        <v>https://music.apple.com/us/artist/julieta-venegas/302960</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/bahamas/6764695847</v>
+        <v>https://music.apple.com/us/album/volver-a-ti/1896255736</v>
       </c>
       <c r="L83" t="str">
-        <v>Bahamas - LENCHO</v>
+        <v>Volver a Ti - Julieta Venegas</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Same Old Song</v>
+        <v>Bahamas</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/same-old-song/6762860685</v>
+        <v>https://music.apple.com/us/song/bahamas/6764695848</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-20</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Same Old Song - Single</v>
+        <v>Bahamas - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>4:12</v>
+        <v>2:06</v>
       </c>
       <c r="H84" t="str">
-        <v>Lila Drew</v>
+        <v>LENCHO</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/lila-drew/1439482732</v>
+        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/same-old-song/1895047985</v>
+        <v>https://music.apple.com/us/album/bahamas/6764695847</v>
       </c>
       <c r="L84" t="str">
-        <v>Same Old Song - Lila Drew</v>
+        <v>Bahamas - LENCHO</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>gentle</v>
+        <v>Same Old Song</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/gentle/6762828356</v>
+        <v>https://music.apple.com/us/song/same-old-song/6762860685</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-20</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>gentle - Single</v>
+        <v>Same Old Song - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>2:48</v>
+        <v>4:12</v>
       </c>
       <c r="H85" t="str">
-        <v>Venus Anon</v>
+        <v>Lila Drew</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/venus-anon/1635970130</v>
+        <v>https://music.apple.com/us/artist/lila-drew/1439482732</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/gentle/1895031896</v>
+        <v>https://music.apple.com/us/album/same-old-song/1895047985</v>
       </c>
       <c r="L85" t="str">
-        <v>gentle - Venus Anon</v>
+        <v>Same Old Song - Lila Drew</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Letters of Your Name</v>
+        <v>gentle</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/letters-of-your-name/1892919741</v>
+        <v>https://music.apple.com/us/song/gentle/6762828356</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-20</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Congratulations</v>
+        <v>gentle - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>3:21</v>
+        <v>2:48</v>
       </c>
       <c r="H86" t="str">
-        <v>Jacob Ungerleider</v>
+        <v>Venus Anon</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/jacob-ungerleider/1460845591</v>
+        <v>https://music.apple.com/us/artist/venus-anon/1635970130</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/letters-of-your-name/1892919737</v>
+        <v>https://music.apple.com/us/album/gentle/1895031896</v>
       </c>
       <c r="L86" t="str">
-        <v>Letters of Your Name - Jacob Ungerleider</v>
+        <v>gentle - Venus Anon</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Seratonin</v>
+        <v>Letters of Your Name</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/seratonin/6763447428</v>
+        <v>https://music.apple.com/us/song/letters-of-your-name/1892919741</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-20</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Seratonin - Single</v>
+        <v>Congratulations</v>
       </c>
       <c r="G87" t="str">
-        <v>1:55</v>
+        <v>3:21</v>
       </c>
       <c r="H87" t="str">
-        <v>James Hype</v>
+        <v>Jacob Ungerleider</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
+        <v>https://music.apple.com/us/artist/jacob-ungerleider/1460845591</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/seratonin/1895320367</v>
+        <v>https://music.apple.com/us/album/letters-of-your-name/1892919737</v>
       </c>
       <c r="L87" t="str">
-        <v>Seratonin - James Hype</v>
+        <v>Letters of Your Name - Jacob Ungerleider</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>A Digital Touch</v>
+        <v>Seratonin</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/a-digital-touch/6765592539</v>
+        <v>https://music.apple.com/us/song/seratonin/6763447428</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-20</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>A Digital Touch - Single</v>
+        <v>Seratonin - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>2:53</v>
+        <v>1:55</v>
       </c>
       <c r="H88" t="str">
-        <v>Evening Elephants</v>
+        <v>James Hype</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
+        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/a-digital-touch/1896003252</v>
+        <v>https://music.apple.com/us/album/seratonin/1895320367</v>
       </c>
       <c r="L88" t="str">
-        <v>A Digital Touch - Evening Elephants</v>
+        <v>Seratonin - James Hype</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Dead Man's Dog</v>
+        <v>A Digital Touch</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/dead-mans-dog/6763447424</v>
+        <v>https://music.apple.com/us/song/a-digital-touch/6765592539</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-20</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Aiming Torches At The Sun - EP</v>
+        <v>A Digital Touch - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>4:33</v>
+        <v>2:53</v>
       </c>
       <c r="H89" t="str">
-        <v>Dermot Henry</v>
+        <v>Evening Elephants</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/dermot-henry/1704074611</v>
+        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/dead-mans-dog/1895320369</v>
+        <v>https://music.apple.com/us/album/a-digital-touch/1896003252</v>
       </c>
       <c r="L89" t="str">
-        <v>Dead Man's Dog - Dermot Henry</v>
+        <v>A Digital Touch - Evening Elephants</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Fault of God</v>
+        <v>Dead Man's Dog</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/fault-of-god/1887702403</v>
+        <v>https://music.apple.com/us/song/dead-mans-dog/6763447424</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-20</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Active Child</v>
+        <v>Aiming Torches At The Sun - EP</v>
       </c>
       <c r="G90" t="str">
-        <v>4:13</v>
+        <v>4:33</v>
       </c>
       <c r="H90" t="str">
-        <v>Active Child</v>
+        <v>Dermot Henry</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/active-child/355288617</v>
+        <v>https://music.apple.com/us/artist/dermot-henry/1704074611</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/fault-of-god/1887701924</v>
+        <v>https://music.apple.com/us/album/dead-mans-dog/1895320369</v>
       </c>
       <c r="L90" t="str">
-        <v>Fault of God - Active Child</v>
+        <v>Dead Man's Dog - Dermot Henry</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Zone (feat. Poppy Baskcomb)</v>
+        <v>Fault of God</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/zone-feat-poppy-baskcomb/6763982867</v>
+        <v>https://music.apple.com/us/song/fault-of-god/1887702403</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-20</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Zone (feat. Poppy Baskcomb) - Single</v>
+        <v>Active Child</v>
       </c>
       <c r="G91" t="str">
-        <v>2:56</v>
+        <v>4:13</v>
       </c>
       <c r="H91" t="str">
-        <v>MK</v>
+        <v>Active Child</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/mk/63097617</v>
+        <v>https://music.apple.com/us/artist/active-child/355288617</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/zone-feat-poppy-baskcomb/1895585800</v>
+        <v>https://music.apple.com/us/album/fault-of-god/1887701924</v>
       </c>
       <c r="L91" t="str">
-        <v>Zone (feat. Poppy Baskcomb) - MK</v>
+        <v>Fault of God - Active Child</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Word Vomit</v>
+        <v>Zone (feat. Poppy Baskcomb)</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/word-vomit/1887315297</v>
+        <v>https://music.apple.com/us/song/zone-feat-poppy-baskcomb/6763982867</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-20</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Word Vomit - Single</v>
+        <v>Zone (feat. Poppy Baskcomb) - Single</v>
       </c>
       <c r="G92" t="str">
-        <v>2:46</v>
+        <v>2:56</v>
       </c>
       <c r="H92" t="str">
-        <v>Baby Queen</v>
+        <v>MK</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
+        <v>https://music.apple.com/us/artist/mk/63097617</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/word-vomit/1887315294</v>
+        <v>https://music.apple.com/us/album/zone-feat-poppy-baskcomb/1895585800</v>
       </c>
       <c r="L92" t="str">
-        <v>Word Vomit - Baby Queen</v>
+        <v>Zone (feat. Poppy Baskcomb) - MK</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Evil in this House</v>
+        <v>Word Vomit</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/evil-in-this-house/1892398371</v>
+        <v>https://music.apple.com/us/song/word-vomit/1887315297</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-20</v>
@@ -3909,68 +3909,106 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Necropolitan</v>
+        <v>Word Vomit - Single</v>
       </c>
       <c r="G93" t="str">
-        <v>4:21</v>
+        <v>2:46</v>
       </c>
       <c r="H93" t="str">
-        <v>Green Lung</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/green-lung/1244071662</v>
+        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/evil-in-this-house/1892398281</v>
+        <v>https://music.apple.com/us/album/word-vomit/1887315294</v>
       </c>
       <c r="L93" t="str">
-        <v>Evil in this House - Green Lung</v>
+        <v>Word Vomit - Baby Queen</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
+        <v>Evil in this House</v>
+      </c>
+      <c r="B94" t="str">
+        <v/>
+      </c>
+      <c r="C94" t="str">
+        <v>https://music.apple.com/us/song/evil-in-this-house/1892398371</v>
+      </c>
+      <c r="D94" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
+        <v>Necropolitan</v>
+      </c>
+      <c r="G94" t="str">
+        <v>4:21</v>
+      </c>
+      <c r="H94" t="str">
+        <v>Green Lung</v>
+      </c>
+      <c r="I94" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J94" t="str">
+        <v>https://music.apple.com/us/artist/green-lung/1244071662</v>
+      </c>
+      <c r="K94" t="str">
+        <v>https://music.apple.com/us/album/evil-in-this-house/1892398281</v>
+      </c>
+      <c r="L94" t="str">
+        <v>Evil in this House - Green Lung</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
         <v>Heaven on High</v>
       </c>
-      <c r="B94" t="str">
-        <v/>
-      </c>
-      <c r="C94" t="str">
+      <c r="B95" t="str">
+        <v/>
+      </c>
+      <c r="C95" t="str">
         <v>https://music.apple.com/us/song/heaven-on-high/1881724153</v>
       </c>
-      <c r="D94" t="str">
-        <v>2026-05-20</v>
-      </c>
-      <c r="E94" t="str">
-        <v/>
-      </c>
-      <c r="F94" t="str">
+      <c r="D95" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
         <v>A Pale White Dot</v>
       </c>
-      <c r="G94" t="str">
+      <c r="G95" t="str">
         <v>4:19</v>
       </c>
-      <c r="H94" t="str">
+      <c r="H95" t="str">
         <v>Periphery</v>
       </c>
-      <c r="I94" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J94" t="str">
+      <c r="I95" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J95" t="str">
         <v>https://music.apple.com/us/artist/periphery/187683869</v>
       </c>
-      <c r="K94" t="str">
+      <c r="K95" t="str">
         <v>https://music.apple.com/us/album/heaven-on-high/1881724003</v>
       </c>
-      <c r="L94" t="str">
+      <c r="L95" t="str">
         <v>Heaven on High - Periphery</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L94"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L95"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week03/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/do-what-you-gotta-do/1887616424</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/hit-the-wall/6766750846</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/ran-to-atlanta/6769568597</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/hoe-phase/6769556949</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/im-spent/6769551476</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/abracadabra-apple-music-live/6768201780</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/falling-out-of-love/1891161448</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/dai-dai/6768469976</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/tu-recuerdo/6763660843</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/ego/6769207667</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/traitor-roles-reversed/6767665959</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/dirty-rosie/6767044374</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/2-hard-4-the-radio/6769568610</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/cheetah-print/6769557055</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/wnba/6769551471</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/shadow-of-a-man-apple-music-live/6768201925</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/epa/6768420253</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/im-your-girl-right/6766440186</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/fu%C3%ABgo/6767661766</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/jajaja/6766341319</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/find-god-feat-dominic-fike/1894315529</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/fool-me-once-feat-leon-thomas/1891467239</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/shabang/6769568598</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/road-trips/6769557053</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/fortworth/6769551482</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/repeat-it/6764277864</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/fool-proof/1892466004</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/crisco/6763369506</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/absolution/1884987651</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/jesus-is-alive/6767694896</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/something-to-lose/6766964605</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/too-busy-missing-you/6766604915</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/f-stop-blues-4-track/1883173173</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/pa-lo-bonito/1886496944</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/lonely/6768757857</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/lockup/1894298102</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/young/6767698952</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/parachute/6764119241</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/little-things/6766351153</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/fish-hunt-golf-drink/6766651884</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/pageant-stage/6764125889</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/firestorm/1868827004</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/girl-next-door/6768077610</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/big-dog/1887197046</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/idea-of-love-a-colors-show/6767667046</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/heavy-serenade/1892154309</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/ddok-ddok-ddok/6764203482</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/shut-it-down/6763631128</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/together-feat-nikki-nair-jessy-lanza-prentiss/6763207821</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/cant-miss-you/1886810999</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/razorblades-and-runways/1888004809</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/massacre/1892127745</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/better-that-way/6766273199</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/apollo/6765602431</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/infinity-123/6763447312</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/aint-over-me-yet/6767283811</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/where-did-you-go/1877958504</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/i-love-you/6766999950</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/housekeeping/6766290834</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/surprise-surprise/6764842119</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/dog/1885967384</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/i-never-see-her/6764149225</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/no-god/1891187414</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/burden/6767688180</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/chico-raro/6767713536</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/whats-done-is-done/6763088629</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/round-and-round/1885665987</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/aint-that-deep/1882831449</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/emily/1893405442</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/hold/6767296480</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/flying-monkey/1894351228</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/anything-goes/1891118972</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/we-are/1894252873</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/its-for-the-kids/1867327679</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/pure-ecstasy/6762228978</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/something-wicked/6766252959</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/feel-the-funk/6763294007</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/everglades-remix/6767719584</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/walk/1892180098</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/volver-a-ti/6766258204</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/bahamas/6764695848</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/same-old-song/6762860685</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/gentle/6762828356</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/letters-of-your-name/1892919741</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/seratonin/6763447428</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/a-digital-touch/6765592539</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/dead-mans-dog/6763447424</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/fault-of-god/1887702403</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/zone-feat-poppy-baskcomb/6763982867</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/word-vomit/1887315297</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/evil-in-this-house/1892398371</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/heaven-on-high/1881724153</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E95" t="str">
         <v/>
